--- a/dimensiones/dimensiones_puestos.xlsx
+++ b/dimensiones/dimensiones_puestos.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="830">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="836">
   <si>
     <t xml:space="preserve">DIMENSIONES POR PUESTO</t>
   </si>
@@ -452,21 +452,33 @@
     <t xml:space="preserve">Plataforma y alto: ficha SJG3.0-1.6</t>
   </si>
   <si>
-    <t xml:space="preserve">   Carro FCEP10520 desarrollos manuales → marcado</t>
+    <t xml:space="preserve">   Carro de desarrollos manuales → marcado 1</t>
   </si>
   <si>
     <t xml:space="preserve">Manuales</t>
   </si>
   <si>
-    <t xml:space="preserve">carro de estantes Storage Compat; detalle en hojas Pulmones y Estantes y carros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Carro FCEP10520 piezas de carros → marcado 2</t>
+    <t xml:space="preserve">1 carro de tránsito, el estante del marcado es el pulmón; detalle en hojas Pulmones y Estantes y carros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pulmones pide carro porta-bandejas 1,3 × 0,7 m con 3 bandejas; el plano dibuja un FCEP10520 de 1,065 × 0,70 m sin bandejas. Uno solo: la G2 corta por tanda y el estante del marcado es el pulmón (Word de manuales decía 2 alternados)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Carro de cajas: piezas de accesorios de carros → 8.1</t>
   </si>
   <si>
     <t xml:space="preserve">Carros</t>
   </si>
   <si>
+    <t xml:space="preserve">FCEP10520 1.065 × 700 mm, 500 kg; una caja por pieza; 8.1 lo busca 1 vez por día; detalle en hojas Pulmones y Estantes y carros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plano · Word</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El plano dice «piezas de carros → marcado 2», pero los cuerpos de carros no van en carro: pasan de la rampa de la G2 a la mesa de marcado 2.1 (Word de carros). Es el mismo carro de cajas que el plano dibuja también en 8.1: hay uno solo</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Carro de scrap (retazos)</t>
   </si>
   <si>
@@ -476,9 +488,6 @@
     <t xml:space="preserve">montada en columna sobre banco</t>
   </si>
   <si>
-    <t xml:space="preserve">Plano · Word</t>
-  </si>
-  <si>
     <t xml:space="preserve">   Mesa FMT ME500</t>
   </si>
   <si>
@@ -587,7 +596,13 @@
     <t xml:space="preserve">Secado — Carros 10 · 1 máq. · 1 turno</t>
   </si>
   <si>
-    <t xml:space="preserve">   Carro de carros que se seca</t>
+    <t xml:space="preserve">   Secadora Melisam MR011 + lugar del matafuego rodante que se seca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">secadora ≈ 0,6 × 0,5 m; el recipiente se para frente a ella en 1,2 × 1,0 m con la lanza en la boca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alto de la secadora. El Word suma 0,6 + 1,2 = 1,8 m de largo y el plano dibuja 1,6 × 1,0 m</t>
   </si>
   <si>
     <t xml:space="preserve">   Estantería A: 4 col. × 4 niv. = 16 pos. (manuales → M13)</t>
@@ -1242,6 +1257,9 @@
   </si>
   <si>
     <t xml:space="preserve">   Carro de cajas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es el mismo carro de cajas que espera detrás de la G2 (hoja Compartidos, corte): hay uno solo según el Word de carros</t>
   </si>
   <si>
     <t xml:space="preserve">   Carro de kits</t>
@@ -4204,7 +4222,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
         <v>141</v>
       </c>
@@ -4231,16 +4249,18 @@
         <v>143</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="J15" s="13"/>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>139</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>1</v>
@@ -4259,16 +4279,18 @@
         <v>0.763</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="J16" s="13"/>
+        <v>148</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>116</v>
@@ -4316,7 +4338,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>142</v>
@@ -4338,16 +4360,16 @@
         <v>1.33</v>
       </c>
       <c r="H20" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="J20" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>142</v>
@@ -4376,7 +4398,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>142</v>
@@ -4398,7 +4420,7 @@
         <v>0.654</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>123</v>
@@ -4407,7 +4429,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>142</v>
@@ -4429,7 +4451,7 @@
         <v>0.6322</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>123</v>
@@ -4438,7 +4460,7 @@
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B24" s="14" t="s">
         <v>142</v>
@@ -4460,7 +4482,7 @@
         <v>2.16</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="I24" s="14" t="s">
         <v>139</v>
@@ -4488,10 +4510,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>1</v>
@@ -4517,10 +4539,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>1</v>
@@ -4546,10 +4568,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C29" s="14" t="n">
         <v>1</v>
@@ -4568,7 +4590,7 @@
         <v>0.5</v>
       </c>
       <c r="H29" s="14" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I29" s="14" t="s">
         <v>123</v>
@@ -4596,7 +4618,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
@@ -4612,7 +4634,7 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>142</v>
@@ -4635,15 +4657,15 @@
       </c>
       <c r="H33" s="2"/>
       <c r="I33" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="J33" s="13" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>142</v>
@@ -4666,15 +4688,15 @@
       </c>
       <c r="H34" s="2"/>
       <c r="I34" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>142</v>
@@ -4696,7 +4718,7 @@
         <v>2.76</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>139</v>
@@ -4705,7 +4727,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>116</v>
@@ -4734,7 +4756,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>116</v>
@@ -4756,7 +4778,7 @@
         <v>1.96</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>123</v>
@@ -4765,7 +4787,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>116</v>
@@ -4791,12 +4813,12 @@
         <v>123</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
@@ -4812,7 +4834,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>142</v>
@@ -4834,7 +4856,7 @@
         <v>1.4</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>123</v>
@@ -4843,7 +4865,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>116</v>
@@ -4872,7 +4894,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>116</v>
@@ -4901,7 +4923,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>116</v>
@@ -4930,7 +4952,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>116</v>
@@ -4959,7 +4981,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>116</v>
@@ -4988,7 +5010,7 @@
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>142</v>
@@ -5010,7 +5032,7 @@
         <v>2.88</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>139</v>
@@ -5019,7 +5041,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
@@ -5035,10 +5057,10 @@
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>1</v>
@@ -5058,18 +5080,18 @@
       </c>
       <c r="H48" s="2"/>
       <c r="I48" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="J48" s="13" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>1</v>
@@ -5089,15 +5111,15 @@
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="J49" s="13" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B50" s="12"/>
       <c r="C50" s="12"/>
@@ -5111,12 +5133,12 @@
       </c>
       <c r="J50" s="12"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="14" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C51" s="14" t="n">
         <v>1</v>
@@ -5134,11 +5156,15 @@
         <f aca="false">D51*E51</f>
         <v>1.6</v>
       </c>
-      <c r="H51" s="14"/>
+      <c r="H51" s="14" t="s">
+        <v>190</v>
+      </c>
       <c r="I51" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="J51" s="16"/>
+        <v>148</v>
+      </c>
+      <c r="J51" s="16" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="s">
@@ -5161,7 +5187,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>142</v>
@@ -5183,7 +5209,7 @@
         <v>5.335</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>123</v>
@@ -5192,10 +5218,10 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="14" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C55" s="14" t="n">
         <v>2</v>
@@ -5214,7 +5240,7 @@
         <v>2.86</v>
       </c>
       <c r="H55" s="14" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="I55" s="14" t="s">
         <v>123</v>
@@ -5251,7 +5277,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5308,7 +5334,7 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
@@ -5327,18 +5353,18 @@
         <v>2.55</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
@@ -5358,15 +5384,15 @@
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
@@ -5386,15 +5412,15 @@
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
@@ -5417,12 +5443,12 @@
         <v>123</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
@@ -5448,7 +5474,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
@@ -5467,7 +5493,7 @@
         <v>1.955</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>123</v>
@@ -5476,7 +5502,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>1</v>
@@ -5495,7 +5521,7 @@
         <v>2</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>123</v>
@@ -5504,7 +5530,7 @@
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>2</v>
@@ -5523,18 +5549,18 @@
         <v>6.48</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>139</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
@@ -5553,7 +5579,7 @@
         <v>0.96</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>123</v>
@@ -5562,7 +5588,7 @@
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B15" s="14" t="n">
         <v>1</v>
@@ -5581,7 +5607,7 @@
         <v>0.96</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="H15" s="14" t="s">
         <v>123</v>
@@ -5608,7 +5634,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
@@ -5627,18 +5653,18 @@
         <v>0.45</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
@@ -5657,18 +5683,18 @@
         <v>0.45</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>2</v>
@@ -5687,7 +5713,7 @@
         <v>1.44</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>139</v>
@@ -5696,7 +5722,7 @@
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B21" s="14" t="n">
         <v>1</v>
@@ -5715,7 +5741,7 @@
         <v>0.91</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="H21" s="14" t="s">
         <v>123</v>
@@ -5742,7 +5768,7 @@
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
@@ -5762,15 +5788,15 @@
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
@@ -5789,7 +5815,7 @@
         <v>0.91</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>123</v>
@@ -5798,7 +5824,7 @@
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B26" s="14" t="n">
         <v>1</v>
@@ -5817,7 +5843,7 @@
         <v>0.91</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="H26" s="14" t="s">
         <v>123</v>
@@ -5844,7 +5870,7 @@
     </row>
     <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>1</v>
@@ -5864,15 +5890,15 @@
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
@@ -5891,7 +5917,7 @@
         <v>0.96</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>139</v>
@@ -5900,7 +5926,7 @@
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
@@ -5919,7 +5945,7 @@
         <v>0.91</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>123</v>
@@ -5928,7 +5954,7 @@
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B32" s="14" t="n">
         <v>1</v>
@@ -5947,7 +5973,7 @@
         <v>0.91</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="H32" s="14" t="s">
         <v>123</v>
@@ -5974,7 +6000,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>1</v>
@@ -6000,7 +6026,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
@@ -6023,12 +6049,12 @@
         <v>123</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>2</v>
@@ -6047,7 +6073,7 @@
         <v>1.44</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>139</v>
@@ -6056,7 +6082,7 @@
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>2</v>
@@ -6075,7 +6101,7 @@
         <v>1.44</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>139</v>
@@ -6084,7 +6110,7 @@
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>2</v>
@@ -6103,7 +6129,7 @@
         <v>1.44</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>139</v>
@@ -6112,7 +6138,7 @@
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B40" s="14" t="n">
         <v>1</v>
@@ -6131,13 +6157,13 @@
         <v>0.91</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="H40" s="14" t="s">
         <v>139</v>
       </c>
       <c r="I40" s="16" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6160,7 +6186,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>1</v>
@@ -6186,7 +6212,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>1</v>
@@ -6209,12 +6235,12 @@
         <v>123</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>1</v>
@@ -6233,7 +6259,7 @@
         <v>0.72</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>139</v>
@@ -6242,7 +6268,7 @@
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="14" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B46" s="14" t="n">
         <v>1</v>
@@ -6261,7 +6287,7 @@
         <v>0.91</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="H46" s="14" t="s">
         <v>123</v>
@@ -6288,7 +6314,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>1</v>
@@ -6307,7 +6333,7 @@
         <v>1.68</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>123</v>
@@ -6316,7 +6342,7 @@
     </row>
     <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>3</v>
@@ -6335,7 +6361,7 @@
         <v>2.16</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>139</v>
@@ -6344,7 +6370,7 @@
     </row>
     <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>1</v>
@@ -6363,7 +6389,7 @@
         <v>0.72</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>139</v>
@@ -6372,7 +6398,7 @@
     </row>
     <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>2</v>
@@ -6391,7 +6417,7 @@
         <v>1.44</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>139</v>
@@ -6400,7 +6426,7 @@
     </row>
     <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="14" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B53" s="14" t="n">
         <v>1</v>
@@ -6419,7 +6445,7 @@
         <v>0.91</v>
       </c>
       <c r="G53" s="14" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="H53" s="14" t="s">
         <v>123</v>
@@ -6446,7 +6472,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>1</v>
@@ -6472,7 +6498,7 @@
     </row>
     <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>1</v>
@@ -6491,18 +6517,18 @@
         <v>2.7</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>139</v>
       </c>
       <c r="I57" s="13" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="14" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B58" s="14" t="n">
         <v>1</v>
@@ -6521,7 +6547,7 @@
         <v>0.91</v>
       </c>
       <c r="G58" s="14" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="H58" s="14" t="s">
         <v>123</v>
@@ -6548,7 +6574,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>1</v>
@@ -6567,7 +6593,7 @@
         <v>3</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>123</v>
@@ -6576,7 +6602,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B62" s="2" t="n">
         <v>1</v>
@@ -6595,7 +6621,7 @@
         <v>3</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>123</v>
@@ -6604,7 +6630,7 @@
     </row>
     <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>3</v>
@@ -6623,7 +6649,7 @@
         <v>2.16</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>139</v>
@@ -6632,7 +6658,7 @@
     </row>
     <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>2</v>
@@ -6651,7 +6677,7 @@
         <v>1.44</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>139</v>
@@ -6660,7 +6686,7 @@
     </row>
     <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>2</v>
@@ -6679,7 +6705,7 @@
         <v>1.44</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>139</v>
@@ -6688,7 +6714,7 @@
     </row>
     <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>1</v>
@@ -6707,7 +6733,7 @@
         <v>0.72</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>139</v>
@@ -6716,7 +6742,7 @@
     </row>
     <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="14" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B67" s="14" t="n">
         <v>1</v>
@@ -6735,7 +6761,7 @@
         <v>0.91</v>
       </c>
       <c r="G67" s="14" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="H67" s="14" t="s">
         <v>123</v>
@@ -6762,7 +6788,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>1</v>
@@ -6788,7 +6814,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="14" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B71" s="14" t="n">
         <v>1</v>
@@ -6807,7 +6833,7 @@
         <v>0.8</v>
       </c>
       <c r="G71" s="14" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="H71" s="14" t="s">
         <v>123</v>
@@ -6834,7 +6860,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B74" s="12"/>
       <c r="C74" s="12"/>
@@ -6849,7 +6875,7 @@
     </row>
     <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>1</v>
@@ -6869,15 +6895,15 @@
       </c>
       <c r="G75" s="2"/>
       <c r="H75" s="2" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I75" s="13" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B76" s="2" t="n">
         <v>1</v>
@@ -6903,7 +6929,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>1</v>
@@ -6929,7 +6955,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B78" s="2" t="n">
         <v>1</v>
@@ -6955,7 +6981,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>1</v>
@@ -6981,7 +7007,7 @@
     </row>
     <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>3</v>
@@ -7000,7 +7026,7 @@
         <v>3.16</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>139</v>
@@ -7009,7 +7035,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B81" s="2" t="n">
         <v>1</v>
@@ -7028,7 +7054,7 @@
         <v>2.76</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>123</v>
@@ -7037,7 +7063,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="12" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B82" s="12"/>
       <c r="C82" s="12"/>
@@ -7052,7 +7078,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B83" s="2" t="n">
         <v>1</v>
@@ -7078,7 +7104,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>1</v>
@@ -7104,7 +7130,7 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>1</v>
@@ -7130,7 +7156,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B86" s="2" t="n">
         <v>1</v>
@@ -7156,7 +7182,7 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="12" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B87" s="12"/>
       <c r="C87" s="12"/>
@@ -7171,7 +7197,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="14" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B88" s="14" t="n">
         <v>1</v>
@@ -7215,7 +7241,7 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B91" s="2" t="n">
         <v>1</v>
@@ -7241,7 +7267,7 @@
     </row>
     <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B92" s="2" t="n">
         <v>1</v>
@@ -7260,18 +7286,18 @@
         <v>14.8</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="I92" s="13" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B93" s="2" t="n">
         <v>1</v>
@@ -7290,18 +7316,18 @@
         <v>14.8</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="I93" s="13" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B94" s="2" t="n">
         <v>1</v>
@@ -7320,18 +7346,18 @@
         <v>25.2</v>
       </c>
       <c r="G94" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="I94" s="13" t="s">
         <v>300</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="I94" s="13" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B95" s="2" t="n">
         <v>1</v>
@@ -7357,7 +7383,7 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B96" s="2" t="n">
         <v>1</v>
@@ -7383,7 +7409,7 @@
     </row>
     <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B97" s="2" t="n">
         <v>2</v>
@@ -7402,7 +7428,7 @@
         <v>1.44</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>139</v>
@@ -7411,7 +7437,7 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="14" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B98" s="14" t="n">
         <v>1</v>
@@ -7430,13 +7456,13 @@
         <v>0.91</v>
       </c>
       <c r="G98" s="14" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="H98" s="14" t="s">
         <v>139</v>
       </c>
       <c r="I98" s="16" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7459,7 +7485,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B101" s="2" t="n">
         <v>1</v>
@@ -7478,18 +7504,18 @@
         <v>2.85</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>123</v>
       </c>
       <c r="I101" s="13" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B102" s="2" t="n">
         <v>1</v>
@@ -7509,15 +7535,15 @@
       </c>
       <c r="G102" s="2"/>
       <c r="H102" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I102" s="13" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B103" s="2" t="n">
         <v>1</v>
@@ -7543,7 +7569,7 @@
     </row>
     <row r="104" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B104" s="2" t="n">
         <v>3</v>
@@ -7562,7 +7588,7 @@
         <v>2.16</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>139</v>
@@ -7571,7 +7597,7 @@
     </row>
     <row r="105" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="14" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B105" s="14" t="n">
         <v>1</v>
@@ -7590,7 +7616,7 @@
         <v>0.72</v>
       </c>
       <c r="G105" s="14" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H105" s="14" t="s">
         <v>139</v>
@@ -7617,7 +7643,7 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B108" s="2" t="n">
         <v>1</v>
@@ -7643,7 +7669,7 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B109" s="2" t="n">
         <v>1</v>
@@ -7669,7 +7695,7 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B110" s="2" t="n">
         <v>1</v>
@@ -7695,7 +7721,7 @@
     </row>
     <row r="111" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B111" s="2" t="n">
         <v>3</v>
@@ -7714,7 +7740,7 @@
         <v>2.16</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>139</v>
@@ -7723,7 +7749,7 @@
     </row>
     <row r="112" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="14" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B112" s="14" t="n">
         <v>1</v>
@@ -7742,7 +7768,7 @@
         <v>0.91</v>
       </c>
       <c r="G112" s="14" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="H112" s="14" t="s">
         <v>123</v>
@@ -7769,7 +7795,7 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B115" s="2" t="n">
         <v>1</v>
@@ -7795,7 +7821,7 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B116" s="2" t="n">
         <v>1</v>
@@ -7821,7 +7847,7 @@
     </row>
     <row r="117" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="14" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B117" s="14" t="n">
         <v>3</v>
@@ -7840,7 +7866,7 @@
         <v>2.16</v>
       </c>
       <c r="G117" s="14" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H117" s="14" t="s">
         <v>139</v>
@@ -7867,7 +7893,7 @@
     </row>
     <row r="120" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B120" s="2" t="n">
         <v>1</v>
@@ -7886,18 +7912,18 @@
         <v>1.6</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I120" s="13" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B121" s="2" t="n">
         <v>1</v>
@@ -7923,7 +7949,7 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B122" s="2" t="n">
         <v>1</v>
@@ -7949,7 +7975,7 @@
     </row>
     <row r="123" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="14" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B123" s="14" t="n">
         <v>1</v>
@@ -7968,7 +7994,7 @@
         <v>0.72</v>
       </c>
       <c r="G123" s="14" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H123" s="14" t="s">
         <v>139</v>
@@ -7995,7 +8021,7 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B126" s="2" t="n">
         <v>1</v>
@@ -8014,7 +8040,7 @@
         <v>1.2</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>123</v>
@@ -8023,7 +8049,7 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B127" s="2" t="n">
         <v>1</v>
@@ -8049,7 +8075,7 @@
     </row>
     <row r="128" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B128" s="2" t="n">
         <v>3</v>
@@ -8068,7 +8094,7 @@
         <v>2.16</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>139</v>
@@ -8077,7 +8103,7 @@
     </row>
     <row r="129" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="14" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B129" s="14" t="n">
         <v>1</v>
@@ -8096,7 +8122,7 @@
         <v>0.91</v>
       </c>
       <c r="G129" s="14" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="H129" s="14" t="s">
         <v>123</v>
@@ -8123,7 +8149,7 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="2" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B132" s="2" t="n">
         <v>1</v>
@@ -8149,7 +8175,7 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B133" s="2" t="n">
         <v>1</v>
@@ -8175,7 +8201,7 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="14" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B134" s="14" t="n">
         <v>1</v>
@@ -8219,7 +8245,7 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="2" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B137" s="2" t="n">
         <v>1</v>
@@ -8238,7 +8264,7 @@
         <v>1.84</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>123</v>
@@ -8247,7 +8273,7 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B138" s="2" t="n">
         <v>1</v>
@@ -8266,7 +8292,7 @@
         <v>2.28</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>123</v>
@@ -8275,7 +8301,7 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B139" s="2" t="n">
         <v>1</v>
@@ -8301,7 +8327,7 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B140" s="2" t="n">
         <v>1</v>
@@ -8327,7 +8353,7 @@
     </row>
     <row r="141" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="2" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B141" s="2" t="n">
         <v>1</v>
@@ -8346,18 +8372,18 @@
         <v>2.56</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="I141" s="13" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="2" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B142" s="2" t="n">
         <v>2</v>
@@ -8376,7 +8402,7 @@
         <v>1.44</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>139</v>
@@ -8385,7 +8411,7 @@
     </row>
     <row r="143" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="14" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B143" s="14" t="n">
         <v>1</v>
@@ -8404,13 +8430,13 @@
         <v>1.54</v>
       </c>
       <c r="G143" s="14" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="H143" s="14" t="s">
         <v>139</v>
       </c>
       <c r="I143" s="16" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8433,7 +8459,7 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B146" s="2" t="n">
         <v>1</v>
@@ -8459,7 +8485,7 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="2" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B147" s="2" t="n">
         <v>1</v>
@@ -8485,7 +8511,7 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B148" s="2" t="n">
         <v>1</v>
@@ -8511,7 +8537,7 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="2" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B149" s="2" t="n">
         <v>1</v>
@@ -8537,7 +8563,7 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="14" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B150" s="14" t="n">
         <v>1</v>
@@ -8591,7 +8617,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8648,7 +8674,7 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B6" s="14" t="n">
         <v>52</v>
@@ -8667,13 +8693,13 @@
         <v>5.27</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="H6" s="14" t="s">
         <v>139</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8696,7 +8722,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
@@ -8715,7 +8741,7 @@
         <v>4.48</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>123</v>
@@ -8724,7 +8750,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
@@ -8750,7 +8776,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
@@ -8776,7 +8802,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B12" s="14" t="n">
         <v>1</v>
@@ -8820,7 +8846,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>1</v>
@@ -8846,7 +8872,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>1</v>
@@ -8872,7 +8898,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
@@ -8898,7 +8924,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
@@ -8924,7 +8950,7 @@
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>2</v>
@@ -8943,7 +8969,7 @@
         <v>2.07</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>139</v>
@@ -8952,7 +8978,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B20" s="14" t="n">
         <v>1</v>
@@ -8971,7 +8997,7 @@
         <v>1.92</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="H20" s="14" t="s">
         <v>123</v>
@@ -8998,7 +9024,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
@@ -9024,7 +9050,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
@@ -9050,7 +9076,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
@@ -9076,7 +9102,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
@@ -9102,7 +9128,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="B27" s="14" t="n">
         <v>1</v>
@@ -9146,7 +9172,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
@@ -9172,7 +9198,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
@@ -9198,7 +9224,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>1</v>
@@ -9224,7 +9250,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
@@ -9250,7 +9276,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>1</v>
@@ -9276,7 +9302,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>1</v>
@@ -9302,7 +9328,7 @@
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B36" s="14" t="n">
         <v>13</v>
@@ -9321,7 +9347,7 @@
         <v>0.77</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="H36" s="14" t="s">
         <v>139</v>
@@ -9348,7 +9374,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
@@ -9374,7 +9400,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
@@ -9400,7 +9426,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>1</v>
@@ -9426,7 +9452,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>1</v>
@@ -9452,7 +9478,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>1</v>
@@ -9478,7 +9504,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>1</v>
@@ -9504,7 +9530,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>1</v>
@@ -9530,7 +9556,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>1</v>
@@ -9556,7 +9582,7 @@
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="14" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B47" s="14" t="n">
         <v>11</v>
@@ -9575,7 +9601,7 @@
         <v>3.15</v>
       </c>
       <c r="G47" s="14" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="H47" s="14" t="s">
         <v>139</v>
@@ -9602,7 +9628,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>1</v>
@@ -9628,7 +9654,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>1</v>
@@ -9654,7 +9680,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>1</v>
@@ -9680,7 +9706,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>1</v>
@@ -9706,7 +9732,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>1</v>
@@ -9732,7 +9758,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>1</v>
@@ -9758,7 +9784,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>1</v>
@@ -9784,7 +9810,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>1</v>
@@ -9810,7 +9836,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B58" s="2" t="n">
         <v>1</v>
@@ -9836,7 +9862,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>1</v>
@@ -9862,7 +9888,7 @@
     </row>
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="14" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="B60" s="14" t="n">
         <v>1</v>
@@ -9881,7 +9907,7 @@
         <v>0.36</v>
       </c>
       <c r="G60" s="14" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="H60" s="14" t="s">
         <v>139</v>
@@ -9908,7 +9934,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>1</v>
@@ -9927,18 +9953,18 @@
         <v>3.9</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>123</v>
       </c>
       <c r="I63" s="13" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>1</v>
@@ -9957,7 +9983,7 @@
         <v>3.9</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>123</v>
@@ -9966,7 +9992,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>1</v>
@@ -9992,7 +10018,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>1</v>
@@ -10018,7 +10044,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>1</v>
@@ -10044,7 +10070,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>1</v>
@@ -10063,7 +10089,7 @@
         <v>0.9</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>123</v>
@@ -10072,7 +10098,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>1</v>
@@ -10096,9 +10122,9 @@
       </c>
       <c r="I69" s="13"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>1</v>
@@ -10120,11 +10146,13 @@
       <c r="H70" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="I70" s="13"/>
+      <c r="I70" s="13" t="s">
+        <v>410</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="14" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B71" s="14" t="n">
         <v>1</v>
@@ -10168,7 +10196,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>3</v>
@@ -10187,7 +10215,7 @@
         <v>1.82</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>123</v>
@@ -10196,7 +10224,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="14" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B75" s="14" t="n">
         <v>1</v>
@@ -10240,7 +10268,7 @@
     </row>
     <row r="78" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="B78" s="2" t="n">
         <v>29</v>
@@ -10259,7 +10287,7 @@
         <v>9.6668</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>139</v>
@@ -10268,7 +10296,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="14" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="B79" s="14" t="n">
         <v>18</v>
@@ -10287,7 +10315,7 @@
         <v>7.852</v>
       </c>
       <c r="G79" s="14" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="H79" s="14" t="s">
         <v>123</v>
@@ -10314,7 +10342,7 @@
     </row>
     <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="B82" s="2" t="n">
         <v>29</v>
@@ -10333,7 +10361,7 @@
         <v>17.885</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>139</v>
@@ -10342,7 +10370,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="B83" s="2" t="n">
         <v>1</v>
@@ -10368,7 +10396,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>1</v>
@@ -10394,7 +10422,7 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>1</v>
@@ -10420,7 +10448,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="14" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="B86" s="14" t="n">
         <v>1</v>
@@ -10464,7 +10492,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="12" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="B89" s="12"/>
       <c r="C89" s="12"/>
@@ -10479,7 +10507,7 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="B90" s="2" t="n">
         <v>1</v>
@@ -10498,18 +10526,18 @@
         <v>1.84</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>123</v>
       </c>
       <c r="I90" s="13" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B91" s="2" t="n">
         <v>1</v>
@@ -10529,15 +10557,15 @@
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I91" s="13" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="12" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="B92" s="12"/>
       <c r="C92" s="12"/>
@@ -10552,7 +10580,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="B93" s="2" t="n">
         <v>1</v>
@@ -10578,7 +10606,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="B94" s="2" t="n">
         <v>1</v>
@@ -10604,7 +10632,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="14" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="B95" s="14" t="n">
         <v>1</v>
@@ -10648,7 +10676,7 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="B98" s="2" t="n">
         <v>1</v>
@@ -10674,7 +10702,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="14" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="B99" s="14" t="n">
         <v>1</v>
@@ -10718,7 +10746,7 @@
     </row>
     <row r="102" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="12" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="B102" s="12"/>
       <c r="C102" s="12"/>
@@ -10733,7 +10761,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="B103" s="2" t="n">
         <v>1</v>
@@ -10759,7 +10787,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="B104" s="2" t="n">
         <v>1</v>
@@ -10785,7 +10813,7 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="B105" s="2" t="n">
         <v>1</v>
@@ -10804,7 +10832,7 @@
         <v>0.8</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>123</v>
@@ -10813,7 +10841,7 @@
     </row>
     <row r="106" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="12" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="B106" s="12"/>
       <c r="C106" s="12"/>
@@ -10828,7 +10856,7 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="B107" s="2" t="n">
         <v>1</v>
@@ -10854,7 +10882,7 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="14" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="B108" s="14" t="n">
         <v>1</v>
@@ -10898,7 +10926,7 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="B111" s="2" t="n">
         <v>1</v>
@@ -10924,7 +10952,7 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="2" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B112" s="2" t="n">
         <v>1</v>
@@ -10950,7 +10978,7 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="B113" s="2" t="n">
         <v>1</v>
@@ -10976,7 +11004,7 @@
     </row>
     <row r="114" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="B114" s="2" t="n">
         <v>5</v>
@@ -10995,7 +11023,7 @@
         <v>3.91</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>123</v>
@@ -11004,7 +11032,7 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="B115" s="2" t="n">
         <v>1</v>
@@ -11023,7 +11051,7 @@
         <v>3.5875</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>123</v>
@@ -11032,7 +11060,7 @@
     </row>
     <row r="116" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="14" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="B116" s="14"/>
       <c r="C116" s="15"/>
@@ -11042,13 +11070,13 @@
       </c>
       <c r="F116" s="17"/>
       <c r="G116" s="14" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="H116" s="14" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="I116" s="16" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11071,7 +11099,7 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="B119" s="2" t="n">
         <v>1</v>
@@ -11097,7 +11125,7 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="B120" s="2" t="n">
         <v>1</v>
@@ -11123,7 +11151,7 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="14" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="B121" s="14" t="n">
         <v>1</v>
@@ -11177,7 +11205,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11234,7 +11262,7 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
@@ -11253,18 +11281,18 @@
         <v>0.7875</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>123</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
@@ -11283,7 +11311,7 @@
         <v>0.35</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>123</v>
@@ -11292,7 +11320,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="B8" s="14" t="n">
         <v>1</v>
@@ -11336,7 +11364,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
@@ -11362,7 +11390,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>1</v>
@@ -11388,7 +11416,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>1</v>
@@ -11414,7 +11442,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
@@ -11440,7 +11468,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="B15" s="14" t="n">
         <v>1</v>
@@ -11484,7 +11512,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="B18" s="14" t="n">
         <v>1</v>
@@ -11528,7 +11556,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
@@ -11547,7 +11575,7 @@
         <v>0.36</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>123</v>
@@ -11556,7 +11584,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="B22" s="14" t="n">
         <v>1</v>
@@ -11575,7 +11603,7 @@
         <v>0.36</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="H22" s="14" t="s">
         <v>123</v>
@@ -11602,7 +11630,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="B25" s="14" t="n">
         <v>1</v>
@@ -11621,7 +11649,7 @@
         <v>1.54</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="H25" s="14" t="s">
         <v>123</v>
@@ -11648,7 +11676,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
@@ -11667,7 +11695,7 @@
         <v>1.05</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>123</v>
@@ -11676,7 +11704,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>1</v>
@@ -11695,7 +11723,7 @@
         <v>1.05</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>123</v>
@@ -11704,7 +11732,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
@@ -11723,18 +11751,18 @@
         <v>0.49</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>123</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
@@ -11753,18 +11781,18 @@
         <v>0.3136</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>123</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>1</v>
@@ -11783,7 +11811,7 @@
         <v>0.64</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>123</v>
@@ -11792,7 +11820,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
@@ -11818,7 +11846,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>1</v>
@@ -11844,7 +11872,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>1</v>
@@ -11870,7 +11898,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="B36" s="14" t="n">
         <v>1</v>
@@ -11914,7 +11942,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
@@ -11940,7 +11968,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
@@ -11966,7 +11994,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="B41" s="14" t="n">
         <v>4</v>
@@ -11985,7 +12013,7 @@
         <v>0.48</v>
       </c>
       <c r="G41" s="14" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="H41" s="14" t="s">
         <v>123</v>
@@ -12012,7 +12040,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>1</v>
@@ -12038,7 +12066,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>1</v>
@@ -12064,7 +12092,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="14" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="B46" s="14" t="n">
         <v>3</v>
@@ -12083,7 +12111,7 @@
         <v>0.3</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="H46" s="14" t="s">
         <v>123</v>
@@ -12110,7 +12138,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>1</v>
@@ -12136,7 +12164,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>1</v>
@@ -12162,7 +12190,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="14" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B51" s="14" t="n">
         <v>1</v>
@@ -12181,13 +12209,13 @@
         <v>0.21</v>
       </c>
       <c r="G51" s="14" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="H51" s="14" t="s">
         <v>123</v>
       </c>
       <c r="I51" s="16" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12210,7 +12238,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>1</v>
@@ -12236,7 +12264,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>1</v>
@@ -12262,7 +12290,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="14" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="B56" s="14" t="n">
         <v>1</v>
@@ -12306,7 +12334,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>1</v>
@@ -12332,7 +12360,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="B60" s="2" t="n">
         <v>1</v>
@@ -12358,7 +12386,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>1</v>
@@ -12384,7 +12412,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="B62" s="2" t="n">
         <v>1</v>
@@ -12403,7 +12431,7 @@
         <v>1.05</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>123</v>
@@ -12412,7 +12440,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>1</v>
@@ -12438,7 +12466,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="14" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="B64" s="14" t="n">
         <v>1</v>
@@ -12461,7 +12489,7 @@
         <v>123</v>
       </c>
       <c r="I64" s="16" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12484,7 +12512,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="12" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="B67" s="12"/>
       <c r="C67" s="12"/>
@@ -12492,18 +12520,18 @@
       <c r="E67" s="12"/>
       <c r="F67" s="12"/>
       <c r="G67" s="12" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="H67" s="12" t="s">
         <v>114</v>
       </c>
       <c r="I67" s="18" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>1</v>
@@ -12522,18 +12550,18 @@
         <v>1.26</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I68" s="13" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>1</v>
@@ -12552,7 +12580,7 @@
         <v>0.2916</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>123</v>
@@ -12561,7 +12589,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="12" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="B70" s="12"/>
       <c r="C70" s="12"/>
@@ -12569,18 +12597,18 @@
       <c r="E70" s="12"/>
       <c r="F70" s="12"/>
       <c r="G70" s="12" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="H70" s="12" t="s">
         <v>114</v>
       </c>
       <c r="I70" s="18" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="14" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="B71" s="14" t="n">
         <v>1</v>
@@ -12624,7 +12652,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="B74" s="12"/>
       <c r="C74" s="12"/>
@@ -12632,18 +12660,18 @@
       <c r="E74" s="12"/>
       <c r="F74" s="12"/>
       <c r="G74" s="12" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="H74" s="12" t="s">
         <v>114</v>
       </c>
       <c r="I74" s="18" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>1</v>
@@ -12662,7 +12690,7 @@
         <v>0.9</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>123</v>
@@ -12671,7 +12699,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="B76" s="12"/>
       <c r="C76" s="12"/>
@@ -12679,18 +12707,18 @@
       <c r="E76" s="12"/>
       <c r="F76" s="12"/>
       <c r="G76" s="12" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="H76" s="12" t="s">
         <v>114</v>
       </c>
       <c r="I76" s="18" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="14" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="B77" s="14" t="n">
         <v>1</v>
@@ -12734,7 +12762,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>1</v>
@@ -12753,7 +12781,7 @@
         <v>0.2916</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>123</v>
@@ -12762,7 +12790,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B81" s="2" t="n">
         <v>1</v>
@@ -12781,7 +12809,7 @@
         <v>0.2916</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>123</v>
@@ -12790,7 +12818,7 @@
     </row>
     <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="14" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B82" s="14"/>
       <c r="C82" s="15"/>
@@ -12800,13 +12828,13 @@
       </c>
       <c r="F82" s="17"/>
       <c r="G82" s="14" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="H82" s="14" t="s">
         <v>123</v>
       </c>
       <c r="I82" s="16" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12829,7 +12857,7 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>1</v>
@@ -12849,15 +12877,15 @@
       </c>
       <c r="G85" s="2"/>
       <c r="H85" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I85" s="13" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="B86" s="2" t="n">
         <v>1</v>
@@ -12877,15 +12905,15 @@
       </c>
       <c r="G86" s="2"/>
       <c r="H86" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I86" s="13" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>1</v>
@@ -12911,7 +12939,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="B88" s="2" t="n">
         <v>1</v>
@@ -12937,7 +12965,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="14" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="B89" s="14" t="n">
         <v>1</v>
@@ -12956,13 +12984,13 @@
         <v>0.21</v>
       </c>
       <c r="G89" s="14" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="H89" s="14" t="s">
         <v>123</v>
       </c>
       <c r="I89" s="16" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12985,7 +13013,7 @@
     </row>
     <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="12" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="B92" s="12"/>
       <c r="C92" s="12"/>
@@ -12993,18 +13021,18 @@
       <c r="E92" s="12"/>
       <c r="F92" s="12"/>
       <c r="G92" s="12" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="H92" s="12" t="s">
         <v>114</v>
       </c>
       <c r="I92" s="18" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="B93" s="2" t="n">
         <v>1</v>
@@ -13023,7 +13051,7 @@
         <v>0.48</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>123</v>
@@ -13032,7 +13060,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B94" s="2" t="n">
         <v>1</v>
@@ -13058,7 +13086,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="B95" s="2" t="n">
         <v>1</v>
@@ -13084,7 +13112,7 @@
     </row>
     <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="12" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="B96" s="12"/>
       <c r="C96" s="12"/>
@@ -13092,18 +13120,18 @@
       <c r="E96" s="12"/>
       <c r="F96" s="12"/>
       <c r="G96" s="12" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="H96" s="12" t="s">
         <v>114</v>
       </c>
       <c r="I96" s="18" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="14" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="B97" s="14" t="n">
         <v>1</v>
@@ -13122,7 +13150,7 @@
         <v>0.36</v>
       </c>
       <c r="G97" s="14" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="H97" s="14" t="s">
         <v>123</v>
@@ -13149,7 +13177,7 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="B100" s="2" t="n">
         <v>1</v>
@@ -13175,7 +13203,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="14" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="B101" s="14" t="n">
         <v>1</v>
@@ -13219,7 +13247,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="B104" s="2" t="n">
         <v>1</v>
@@ -13245,7 +13273,7 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="14" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="B105" s="14" t="n">
         <v>1</v>
@@ -13264,13 +13292,13 @@
         <v>0.21</v>
       </c>
       <c r="G105" s="14" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="H105" s="14" t="s">
         <v>123</v>
       </c>
       <c r="I105" s="16" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13293,7 +13321,7 @@
     </row>
     <row r="108" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="12" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="B108" s="12"/>
       <c r="C108" s="12"/>
@@ -13301,18 +13329,18 @@
       <c r="E108" s="12"/>
       <c r="F108" s="12"/>
       <c r="G108" s="12" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="H108" s="12" t="s">
         <v>114</v>
       </c>
       <c r="I108" s="18" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="B109" s="2" t="n">
         <v>1</v>
@@ -13338,7 +13366,7 @@
     </row>
     <row r="110" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="12" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="B110" s="12"/>
       <c r="C110" s="12"/>
@@ -13346,18 +13374,18 @@
       <c r="E110" s="12"/>
       <c r="F110" s="12"/>
       <c r="G110" s="12" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="H110" s="12" t="s">
         <v>114</v>
       </c>
       <c r="I110" s="18" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="14" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="B111" s="14" t="n">
         <v>1</v>
@@ -13401,7 +13429,7 @@
     </row>
     <row r="114" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="B114" s="2" t="n">
         <v>1</v>
@@ -13421,15 +13449,15 @@
       </c>
       <c r="G114" s="2"/>
       <c r="H114" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I114" s="13" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="B115" s="2" t="n">
         <v>1</v>
@@ -13449,15 +13477,15 @@
       </c>
       <c r="G115" s="2"/>
       <c r="H115" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I115" s="13" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="B116" s="2" t="n">
         <v>1</v>
@@ -13483,7 +13511,7 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="14" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="B117" s="14" t="n">
         <v>1</v>
@@ -13527,7 +13555,7 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="B120" s="2" t="n">
         <v>1</v>
@@ -13553,7 +13581,7 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="B121" s="2" t="n">
         <v>1</v>
@@ -13579,7 +13607,7 @@
     </row>
     <row r="122" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="14" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="B122" s="14" t="n">
         <v>1</v>
@@ -13598,13 +13626,13 @@
         <v>0.7125</v>
       </c>
       <c r="G122" s="14" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="H122" s="14" t="s">
         <v>123</v>
       </c>
       <c r="I122" s="16" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13627,7 +13655,7 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="B125" s="2" t="n">
         <v>1</v>
@@ -13653,7 +13681,7 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B126" s="2" t="n">
         <v>1</v>
@@ -13679,7 +13707,7 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="B127" s="2" t="n">
         <v>1</v>
@@ -13705,7 +13733,7 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="B128" s="2" t="n">
         <v>1</v>
@@ -13731,7 +13759,7 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="14" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="B129" s="14" t="n">
         <v>1</v>
@@ -13775,7 +13803,7 @@
     </row>
     <row r="132" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="2" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="B132" s="2" t="n">
         <v>1</v>
@@ -13794,18 +13822,18 @@
         <v>0.75</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>123</v>
       </c>
       <c r="I132" s="13" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="14" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="B133" s="14" t="n">
         <v>1</v>
@@ -13824,13 +13852,13 @@
         <v>0.75</v>
       </c>
       <c r="G133" s="14" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="H133" s="14" t="s">
         <v>123</v>
       </c>
       <c r="I133" s="16" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13853,7 +13881,7 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="B136" s="2" t="n">
         <v>1</v>
@@ -13876,12 +13904,12 @@
         <v>123</v>
       </c>
       <c r="I136" s="13" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="14" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="B137" s="14" t="n">
         <v>1</v>
@@ -13900,13 +13928,13 @@
         <v>0.4675</v>
       </c>
       <c r="G137" s="14" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="H137" s="14" t="s">
         <v>123</v>
       </c>
       <c r="I137" s="16" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13929,7 +13957,7 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="B140" s="2" t="n">
         <v>1</v>
@@ -13955,7 +13983,7 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="14" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="B141" s="14" t="n">
         <v>1</v>
@@ -13999,7 +14027,7 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="14" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="B144" s="14" t="n">
         <v>1</v>
@@ -14043,7 +14071,7 @@
     </row>
     <row r="147" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="14" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="B147" s="14" t="n">
         <v>16</v>
@@ -14062,13 +14090,13 @@
         <v>20.04</v>
       </c>
       <c r="G147" s="14" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="H147" s="14" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="I147" s="16" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14091,7 +14119,7 @@
     </row>
     <row r="150" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="14" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="B150" s="14" t="n">
         <v>16</v>
@@ -14110,13 +14138,13 @@
         <v>20.04</v>
       </c>
       <c r="G150" s="14" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="H150" s="14" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="I150" s="16" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14139,7 +14167,7 @@
     </row>
     <row r="153" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="14" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="B153" s="14" t="n">
         <v>2</v>
@@ -14158,7 +14186,7 @@
         <v>2.4</v>
       </c>
       <c r="G153" s="14" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="H153" s="14" t="s">
         <v>123</v>
@@ -14185,7 +14213,7 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="B156" s="2" t="n">
         <v>1</v>
@@ -14211,7 +14239,7 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="B157" s="2" t="n">
         <v>1</v>
@@ -14237,7 +14265,7 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="14" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="B158" s="14" t="n">
         <v>1</v>
@@ -14293,12 +14321,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="19" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -14315,43 +14343,43 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14373,19 +14401,19 @@
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="D6" s="20" t="n">
         <v>90</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="F6" s="20" t="n">
         <v>0</v>
@@ -14397,7 +14425,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="J6" s="8" t="n">
         <v>0</v>
@@ -14413,19 +14441,19 @@
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="D7" s="20" t="n">
         <v>1505</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="F7" s="20" t="n">
         <v>15</v>
@@ -14437,7 +14465,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="J7" s="8" t="n">
         <v>5.32</v>
@@ -14453,19 +14481,19 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="D8" s="20" t="n">
         <v>607</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="F8" s="20" t="n">
         <v>20</v>
@@ -14477,7 +14505,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="J8" s="8" t="n">
         <v>11.08</v>
@@ -14493,19 +14521,19 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="D9" s="20" t="n">
         <v>405</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="F9" s="20" t="n">
         <v>10</v>
@@ -14517,7 +14545,7 @@
         <v>2</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="J9" s="8" t="n">
         <v>6.76</v>
@@ -14530,24 +14558,24 @@
         <v>6.76</v>
       </c>
       <c r="M9" s="13" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="D10" s="20" t="n">
         <v>6609</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="F10" s="20" t="n">
         <v>65</v>
@@ -14559,7 +14587,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="J10" s="8" t="n">
         <v>11.38</v>
@@ -14575,19 +14603,19 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="D11" s="20" t="n">
         <v>6765</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="F11" s="20" t="n">
         <v>80</v>
@@ -14599,7 +14627,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="J11" s="8" t="n">
         <v>12.31</v>
@@ -14615,19 +14643,19 @@
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="D12" s="20" t="n">
         <v>201</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="F12" s="20" t="n">
         <v>0</v>
@@ -14639,7 +14667,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="J12" s="8" t="n">
         <v>0</v>
@@ -14655,19 +14683,19 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="D13" s="20" t="n">
         <v>407</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="F13" s="20" t="n">
         <v>9</v>
@@ -14679,7 +14707,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="J13" s="8" t="n">
         <v>2.44</v>
@@ -14695,19 +14723,19 @@
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="D14" s="20" t="n">
         <v>315</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="F14" s="20" t="n">
         <v>3</v>
@@ -14719,7 +14747,7 @@
         <v>2</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="J14" s="8" t="n">
         <v>2</v>
@@ -14732,24 +14760,24 @@
         <v>1</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="D15" s="20" t="n">
         <v>691</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="F15" s="20" t="n">
         <v>21</v>
@@ -14761,7 +14789,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="J15" s="8" t="n">
         <v>11.08</v>
@@ -14777,19 +14805,19 @@
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="D16" s="20" t="n">
         <v>371</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="F16" s="20" t="n">
         <v>11</v>
@@ -14801,7 +14829,7 @@
         <v>5</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="J16" s="8" t="n">
         <v>5</v>
@@ -14814,24 +14842,24 @@
         <v>5</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="D17" s="20" t="n">
         <v>346</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="F17" s="20" t="n">
         <v>5</v>
@@ -14843,7 +14871,7 @@
         <v>3</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="J17" s="8" t="n">
         <v>3</v>
@@ -14856,24 +14884,24 @@
         <v>3</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="D18" s="20" t="n">
         <v>336</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="F18" s="20" t="n">
         <v>6</v>
@@ -14885,7 +14913,7 @@
         <v>3</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="J18" s="8" t="n">
         <v>3</v>
@@ -14898,24 +14926,24 @@
         <v>3</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="D19" s="20" t="n">
         <v>488</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="F19" s="20" t="n">
         <v>7</v>
@@ -14927,7 +14955,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="J19" s="8" t="n">
         <v>3.88</v>
@@ -14943,19 +14971,19 @@
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="D20" s="20" t="n">
         <v>421</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="F20" s="20" t="n">
         <v>5</v>
@@ -14967,7 +14995,7 @@
         <v>2</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="J20" s="8" t="n">
         <v>3.88</v>
@@ -14980,24 +15008,24 @@
         <v>3.88</v>
       </c>
       <c r="M20" s="13" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="D21" s="20" t="n">
         <v>330</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="F21" s="20" t="n">
         <v>11</v>
@@ -15009,7 +15037,7 @@
         <v>2</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="J21" s="8" t="n">
         <v>6.76</v>
@@ -15022,24 +15050,24 @@
         <v>6.76</v>
       </c>
       <c r="M21" s="13" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="D22" s="20" t="n">
         <v>183</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="F22" s="20" t="n">
         <v>9</v>
@@ -15051,7 +15079,7 @@
         <v>1</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="J22" s="8" t="n">
         <v>5.32</v>
@@ -15067,19 +15095,19 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="D23" s="20" t="n">
         <v>168</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="F23" s="20" t="n">
         <v>7</v>
@@ -15091,7 +15119,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="J23" s="8" t="n">
         <v>5.32</v>
@@ -15107,19 +15135,19 @@
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="D24" s="20" t="n">
         <v>161</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="F24" s="20" t="n">
         <v>3</v>
@@ -15131,7 +15159,7 @@
         <v>1</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="J24" s="8" t="n">
         <v>2.44</v>
@@ -15147,19 +15175,19 @@
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="D25" s="20" t="n">
         <v>241</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="F25" s="20" t="n">
         <v>8</v>
@@ -15171,7 +15199,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="J25" s="8" t="n">
         <v>5.32</v>
@@ -15187,19 +15215,19 @@
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="D26" s="20" t="n">
         <v>161</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="F26" s="20" t="n">
         <v>3</v>
@@ -15211,7 +15239,7 @@
         <v>2</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="J26" s="8" t="n">
         <v>2</v>
@@ -15224,12 +15252,12 @@
         <v>1</v>
       </c>
       <c r="M26" s="13" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="F27" s="21" t="n">
         <f aca="false">SUM(F6:F26)</f>
@@ -15258,7 +15286,7 @@
     </row>
     <row r="28" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="22" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15280,22 +15308,22 @@
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="D31" s="20" t="n">
         <v>52</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="J31" s="8" t="n">
         <v>7.36</v>
@@ -15307,22 +15335,22 @@
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="D32" s="20" t="n">
         <v>2</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="J32" s="8" t="n">
         <v>0.49</v>
@@ -15334,22 +15362,22 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="D33" s="20" t="n">
         <v>11</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="J33" s="8" t="n">
         <v>3.07</v>
@@ -15361,22 +15389,22 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="D34" s="20" t="n">
         <v>13</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="J34" s="8" t="n">
         <v>0.66</v>
@@ -15388,22 +15416,22 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="D35" s="20" t="n">
         <v>1</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="J35" s="8" t="n">
         <v>0.25</v>
@@ -15415,22 +15443,22 @@
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="D36" s="20" t="n">
         <v>29</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="J36" s="8" t="n">
         <v>17.71</v>
@@ -15442,22 +15470,22 @@
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="D37" s="20" t="n">
         <v>29</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="J37" s="8" t="n">
         <v>17.71</v>
@@ -15469,7 +15497,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="J38" s="10" t="n">
         <f aca="false">SUM(J31:J37)</f>
@@ -15482,7 +15510,7 @@
     </row>
     <row r="39" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="22" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15504,25 +15532,25 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="D42" s="20" t="n">
         <v>238</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="F42" s="20" t="n">
         <v>25</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="J42" s="8" t="n">
         <v>60</v>
@@ -15532,30 +15560,30 @@
         <v>60</v>
       </c>
       <c r="M42" s="13" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="D43" s="20" t="n">
         <v>271</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="F43" s="20" t="n">
         <v>10</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="J43" s="8" t="n">
         <v>24</v>
@@ -15565,30 +15593,30 @@
         <v>24</v>
       </c>
       <c r="M43" s="13" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="D44" s="20" t="n">
         <v>271</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="F44" s="20" t="n">
         <v>10</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="J44" s="8" t="n">
         <v>24</v>
@@ -15598,12 +15626,12 @@
         <v>24</v>
       </c>
       <c r="M44" s="13" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="J45" s="10" t="n">
         <f aca="false">SUM(J42:J44)</f>
@@ -15650,35 +15678,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>11</v>
@@ -15686,7 +15714,7 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1200</v>
@@ -15698,21 +15726,21 @@
         <v>2000</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>1200</v>
@@ -15727,18 +15755,18 @@
         <v>121</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>600</v>
@@ -15753,18 +15781,18 @@
         <v>121</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1300</v>
@@ -15776,21 +15804,21 @@
         <v>125</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>1300</v>
@@ -15802,21 +15830,21 @@
         <v>125</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>1200</v>
@@ -15828,21 +15856,21 @@
         <v>125</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>2700</v>
@@ -15854,21 +15882,21 @@
         <v>125</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>1200</v>
@@ -15880,21 +15908,21 @@
         <v>1045</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>1200</v>
@@ -15906,50 +15934,50 @@
         <v>125</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>111</v>
@@ -15957,13 +15985,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="D17" s="20" t="n">
         <v>254</v>
@@ -15975,7 +16003,7 @@
         <v>229</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="H17" s="20" t="n">
         <v>1270</v>
@@ -15987,10 +16015,10 @@
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="D18" s="20" t="n">
         <v>147</v>
@@ -16002,7 +16030,7 @@
         <v>184</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="H18" s="20" t="n">
         <v>735</v>
@@ -16014,10 +16042,10 @@
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="D19" s="20" t="n">
         <v>76</v>
@@ -16029,7 +16057,7 @@
         <v>122</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="H19" s="20" t="n">
         <v>456</v>
@@ -16041,10 +16069,10 @@
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14"/>
       <c r="B20" s="14" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>34</v>
@@ -16056,7 +16084,7 @@
         <v>68</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>796</v>
+        <v>802</v>
       </c>
       <c r="H20" s="24" t="n">
         <v>272</v>
@@ -16067,13 +16095,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="D21" s="20" t="n">
         <v>105</v>
@@ -16085,7 +16113,7 @@
         <v>297.5</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="H21" s="20" t="n">
         <v>420</v>
@@ -16097,10 +16125,10 @@
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="D22" s="20" t="n">
         <v>36</v>
@@ -16112,7 +16140,7 @@
         <v>333</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="H22" s="20" t="n">
         <v>144</v>
@@ -16124,10 +16152,10 @@
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="D23" s="20" t="n">
         <v>21</v>
@@ -16139,7 +16167,7 @@
         <v>414</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="H23" s="20" t="n">
         <v>63</v>
@@ -16151,10 +16179,10 @@
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="14"/>
       <c r="B24" s="14" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>18</v>
@@ -16166,7 +16194,7 @@
         <v>582</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="H24" s="24" t="n">
         <v>54</v>
@@ -16177,13 +16205,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="D25" s="20" t="n">
         <v>105</v>
@@ -16195,7 +16223,7 @@
         <v>297.5</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="H25" s="20" t="n">
         <v>420</v>
@@ -16207,10 +16235,10 @@
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
       <c r="B26" s="2" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="D26" s="20" t="n">
         <v>36</v>
@@ -16222,7 +16250,7 @@
         <v>333</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="H26" s="20" t="n">
         <v>144</v>
@@ -16234,10 +16262,10 @@
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="D27" s="20" t="n">
         <v>21</v>
@@ -16249,7 +16277,7 @@
         <v>414</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="H27" s="20" t="n">
         <v>63</v>
@@ -16261,10 +16289,10 @@
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="14"/>
       <c r="B28" s="14" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="D28" s="24" t="n">
         <v>18</v>
@@ -16276,7 +16304,7 @@
         <v>582</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="H28" s="24" t="n">
         <v>54</v>
@@ -16287,13 +16315,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="D29" s="20" t="n">
         <v>72</v>
@@ -16305,7 +16333,7 @@
         <v>390</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="H29" s="20" t="n">
         <v>216</v>
@@ -16317,10 +16345,10 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="D30" s="20" t="n">
         <v>34</v>
@@ -16332,7 +16360,7 @@
         <v>415</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="H30" s="20" t="n">
         <v>102</v>
@@ -16344,10 +16372,10 @@
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="D31" s="20" t="n">
         <v>18</v>
@@ -16359,7 +16387,7 @@
         <v>495</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="H31" s="20" t="n">
         <v>54</v>
@@ -16371,10 +16399,10 @@
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="14"/>
       <c r="B32" s="14" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="D32" s="24" t="n">
         <v>9</v>
@@ -16386,7 +16414,7 @@
         <v>665</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="H32" s="24" t="n">
         <v>18</v>
@@ -16395,18 +16423,18 @@
         <v>27</v>
       </c>
       <c r="J32" s="13" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="D33" s="20" t="n">
         <v>288</v>
@@ -16418,7 +16446,7 @@
         <v>300</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="H33" s="20" t="n">
         <v>3456</v>
@@ -16430,10 +16458,10 @@
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2"/>
       <c r="B34" s="2" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="D34" s="20" t="n">
         <v>88</v>
@@ -16445,7 +16473,7 @@
         <v>300</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="H34" s="20" t="n">
         <v>1056</v>
@@ -16457,10 +16485,10 @@
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2"/>
       <c r="B35" s="2" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="D35" s="20" t="n">
         <v>48</v>
@@ -16472,7 +16500,7 @@
         <v>300</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="H35" s="20" t="n">
         <v>576</v>
@@ -16484,10 +16512,10 @@
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14"/>
       <c r="B36" s="14" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="D36" s="24" t="n">
         <v>27</v>
@@ -16499,7 +16527,7 @@
         <v>300</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="H36" s="24" t="n">
         <v>324</v>
@@ -16510,13 +16538,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="D37" s="20" t="n">
         <v>288</v>
@@ -16528,7 +16556,7 @@
         <v>300</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="H37" s="20" t="n">
         <v>3456</v>
@@ -16540,10 +16568,10 @@
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2"/>
       <c r="B38" s="2" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="D38" s="20" t="n">
         <v>80</v>
@@ -16555,7 +16583,7 @@
         <v>300</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="H38" s="20" t="n">
         <v>960</v>
@@ -16567,10 +16595,10 @@
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2"/>
       <c r="B39" s="2" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="D39" s="20" t="n">
         <v>36</v>
@@ -16582,7 +16610,7 @@
         <v>300</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="H39" s="20" t="n">
         <v>432</v>
@@ -16594,10 +16622,10 @@
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14"/>
       <c r="B40" s="14" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="D40" s="24" t="n">
         <v>21</v>
@@ -16609,7 +16637,7 @@
         <v>300</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="H40" s="24" t="n">
         <v>252</v>
@@ -16620,13 +16648,13 @@
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="D41" s="20" t="n">
         <v>100</v>
@@ -16638,7 +16666,7 @@
         <v>300</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="H41" s="20" t="n">
         <v>1200</v>
@@ -16650,10 +16678,10 @@
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2"/>
       <c r="B42" s="2" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="D42" s="20" t="n">
         <v>40</v>
@@ -16665,7 +16693,7 @@
         <v>300</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="H42" s="20" t="n">
         <v>480</v>
@@ -16677,10 +16705,10 @@
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2"/>
       <c r="B43" s="2" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="D43" s="20" t="n">
         <v>30</v>
@@ -16692,7 +16720,7 @@
         <v>300</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="H43" s="20" t="n">
         <v>360</v>
@@ -16704,10 +16732,10 @@
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="14"/>
       <c r="B44" s="14" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="D44" s="24" t="n">
         <v>19</v>
@@ -16719,7 +16747,7 @@
         <v>300</v>
       </c>
       <c r="G44" s="14" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="H44" s="24" t="n">
         <v>228</v>
@@ -16730,7 +16758,7 @@
     </row>
     <row r="46" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="22" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
     </row>
   </sheetData>

--- a/dimensiones/dimensiones_puestos.xlsx
+++ b/dimensiones/dimensiones_puestos.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="690">
   <si>
     <t xml:space="preserve">DIMENSIONES POR PUESTO</t>
   </si>
@@ -41,7 +41,13 @@
     <t xml:space="preserve">Fuentes</t>
   </si>
   <si>
-    <t xml:space="preserve">Solo dos: los Excel de Fran (Balanceo y Pulmones, sin la carpeta EXTRA) y las cotizaciones de Drive (Cotizaciones/Maquinaria). No se usan el plano ni los Word de proceso.</t>
+    <t xml:space="preserve">Los Excel de la carpeta EXTRA FRAN (Balanceo-FLAMA2035.xlsx y PULMONES-FLAMA2035.xlsx) y las cotizaciones de Drive (Cotizaciones/Maquinaria). No se usan el plano ni los Word de proceso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cómo leer la fuente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Archivo › hoja celda (valor)». Ej.: PULMONES-FLAMA2035 › Parametros B7 (frente 1.200) = el frente del estante está en esa celda. La fila gris de cada puesto cita de dónde salen las máquinas y los turnos.</t>
   </si>
   <si>
     <t xml:space="preserve">Qué sale de cada una</t>
@@ -332,6 +338,9 @@
     <t xml:space="preserve">A confirmar</t>
   </si>
   <si>
+    <t xml:space="preserve">Manuales: Balanceo-FLAMA2035 › Carga R35 (máq.) y S35 (turnos) · Carros: Carga M75 (máq.) y N75 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Guillotina 1</t>
   </si>
   <si>
@@ -347,6 +356,9 @@
     <t xml:space="preserve">Molinari no da medidas; CENA y Machcenter son imágenes que no se pueden leer</t>
   </si>
   <si>
+    <t xml:space="preserve">Manuales: Balanceo-FLAMA2035 › Carga R36 (máq.) y S36 (turnos) · Carros: Carga M75 (máq.) y N75 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Guillotina 2</t>
   </si>
   <si>
@@ -362,7 +374,7 @@
     <t xml:space="preserve">90 franjas como máximo (2 hojas)</t>
   </si>
   <si>
-    <t xml:space="preserve">Balanceo, Parametros (N_HOJAS_FRANJA); Pulmones fila 6</t>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Parametros B38 (2 hojas) · PULMONES-FLAMA2035 › Pulmones H6 (90 franjas)</t>
   </si>
   <si>
     <t xml:space="preserve">Sin medidas en las fuentes</t>
@@ -374,12 +386,15 @@
     <t xml:space="preserve">3 bandejas 1.200 × 600, hasta 450 kg; espera en el origen</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B37 y B42; Pulmones fila 7</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros A42:B42 (lugar de 1 m² del carro de 1,3 × 0,7 m) y B37 (3 bandejas) · cantidad: Pulmones S7 (¿puede parar el que entrega?: Z7)</t>
   </si>
   <si>
     <t xml:space="preserve">Alto del carro (3 niveles a la altura del estante)</t>
   </si>
   <si>
+    <t xml:space="preserve">Manuales: Balanceo-FLAMA2035 › Carga R39 (máq.) y S39 (turnos) · Carros: Carga M76 (máq.) y N76 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Marcadora</t>
   </si>
   <si>
@@ -398,7 +413,10 @@
     <t xml:space="preserve">Estante: pilas por modelo sobre bandejas; máx. 1505 u en 15 bandejas o cajones</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B7:B9; Pulmones fila 7</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros B7 (frente 1.200), B8 (fondo 600) y B9 (alto 2.000) · módulos: Pulmones O7 · máximo: H7 · bandejas: N7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manuales: Balanceo-FLAMA2035 › Carga R48 (máq.) y S48 (turnos) · Carros: Carga M84 (máq.) y N84 (turnos)</t>
   </si>
   <si>
     <t xml:space="preserve">   Máquina de PH Yukon M-000200 (manuales)</t>
@@ -422,7 +440,10 @@
     <t xml:space="preserve">   Carro porta-bandejas: cilindros mojados → secado</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B37 y B42; Pulmones fila 17</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros A42:B42 (lugar de 1 m² del carro de 1,3 × 0,7 m) y B37 (3 bandejas) · cantidad: Pulmones S17 (¿puede parar el que entrega?: Z17)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manuales: Balanceo-FLAMA2035 › Carga R49 (máq.) y S49 (turnos) · Carros: Carga M85 (máq.) y N85 (turnos)</t>
   </si>
   <si>
     <t xml:space="preserve">   Secadora (manuales)</t>
@@ -437,12 +458,15 @@
     <t xml:space="preserve">   Carro porta-bandejas: cilindros secos → granallado</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B37 y B42; Pulmones fila 18</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros A42:B42 (lugar de 1 m² del carro de 1,3 × 0,7 m) y B37 (3 bandejas) · cantidad: Pulmones S18 (¿puede parar el que entrega?: Z18)</t>
   </si>
   <si>
     <t xml:space="preserve">MANUALES — lo que va dentro de cada puesto</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga R37 (máq.) y S37 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Prensa de embutido</t>
   </si>
   <si>
@@ -473,7 +497,7 @@
     <t xml:space="preserve">vano de 2,7 m × 3 niveles, 3 pallets 1.200 × 800 por nivel; 17 pallets de 12 cajones</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B53:B57 y Equipos fila 11; Pulmones filas 10 y 11</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros B56 (vano 2,7 m), B57 (fondo 1,2 m), B54 (3 niveles), B55 (3 pallets por nivel) · vanos: Equipos B12 · pallets: Equipos B13</t>
   </si>
   <si>
     <t xml:space="preserve">Alto del rack (primer nivel a 400 mm, pallet de 1.045 mm de alto)</t>
@@ -485,7 +509,7 @@
     <t xml:space="preserve">4 niveles de 3 cajones 600 × 400 × 300</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B38; Pulmones fila 10</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros B38 (12 cajones en 4 niveles); medidas = carro de A42 (1,3 × 0,7 m) · cantidad: Pulmones S10</t>
   </si>
   <si>
     <t xml:space="preserve">Fran pide confirmar que el carro tenga 4 niveles de 3 cajones; si no, se pide igual al porta-bandejas (1,3 × 0,7 m) con 4 niveles. Alto del carro</t>
@@ -494,12 +518,18 @@
     <t xml:space="preserve">   Carro de 12 cajones: cúpulas</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B38; Pulmones fila 11</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros B38 (12 cajones en 4 niveles); medidas = carro de A42 (1,3 × 0,7 m) · cantidad: Pulmones S11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga R38 (máq.) y S38 (turnos)</t>
   </si>
   <si>
     <t xml:space="preserve">   Prensa de muesca del cuello</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga R40 (máq.) y S40 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Soldadora de cuello</t>
   </si>
   <si>
@@ -518,13 +548,16 @@
     <t xml:space="preserve">Rack de pallets al lado de la prensa (la tanda) + estante en el puesto con la ola de mañana; máx. 6765 u en 80 bandejas o cajones</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B7:B9; Pulmones fila 11</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros B7 (frente 1.200), B8 (fondo 600) y B9 (alto 2.000) · módulos: Pulmones O11 · máximo: H11 · bandejas: N11</t>
   </si>
   <si>
     <t xml:space="preserve">   Carro de 12 cajones: cúpulas con cuello</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B38; Pulmones fila 13</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros B38 (12 cajones en 4 niveles); medidas = carro de A42 (1,3 × 0,7 m) · cantidad: Pulmones S13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga R41 (máq.) y S41 (turnos)</t>
   </si>
   <si>
     <t xml:space="preserve">   Roladora (cilindradora de manuales)</t>
@@ -542,7 +575,10 @@
     <t xml:space="preserve">   Carro porta-bandejas: virolas → soldadura longitudinal</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B37 y B42; Pulmones fila 8</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros A42:B42 (lugar de 1 m² del carro de 1,3 × 0,7 m) y B37 (3 bandejas) · cantidad: Pulmones S8 (¿puede parar el que entrega?: Z8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga R42 (máq.) y S42 (turnos)</t>
   </si>
   <si>
     <t xml:space="preserve">   Soldadora longitudinal 2,5 a 10 kg</t>
@@ -560,24 +596,30 @@
     <t xml:space="preserve">Estante: parados en bandejas, un modelo por bandeja; máx. 607 u en 20 bandejas o cajones</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B7:B9; Pulmones fila 8</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros B7 (frente 1.200), B8 (fondo 600) y B9 (alto 2.000) · módulos: Pulmones O8 · máximo: H8 · bandejas: N8</t>
   </si>
   <si>
     <t xml:space="preserve">   Carro porta-bandejas: cuerpos soldados → encastre de fondo</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B37 y B42; Pulmones fila 9</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros A42:B42 (lugar de 1 m² del carro de 1,3 × 0,7 m) y B37 (3 bandejas) · cantidad: Pulmones S9 (¿puede parar el que entrega?: Z9)</t>
   </si>
   <si>
     <t xml:space="preserve">Pulmones da 2; propuesta 1 + soporte fijo para la bandeja en llenado (con tandas no hace falta el segundo). alto del carro (3 niveles a la altura del estante)</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga R43 (máq.) y S43 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Soldadora longitudinal TIG 1 kg</t>
   </si>
   <si>
     <t xml:space="preserve">Cotización Firesafer (TIG)</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga R44 (máq.) y S44 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Prensa de encastre de fondo 30 t</t>
   </si>
   <si>
@@ -596,7 +638,7 @@
     <t xml:space="preserve">Estante: parados en bandejas, un modelo por bandeja; máx. 405 u en 10 bandejas o cajones</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B7:B9; Pulmones fila 9</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros B7 (frente 1.200), B8 (fondo 600) y B9 (alto 2.000) · módulos: Pulmones O9 · máximo: H9 · bandejas: N9</t>
   </si>
   <si>
     <t xml:space="preserve">   Estante: fondos (pulmón)</t>
@@ -605,13 +647,16 @@
     <t xml:space="preserve">Rack de pallets al lado de la prensa (la tanda) + estante en el puesto con la ola de mañana; máx. 6609 u en 65 bandejas o cajones</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B7:B9; Pulmones fila 10</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros B7 (frente 1.200), B8 (fondo 600) y B9 (alto 2.000) · módulos: Pulmones O10 · máximo: H10 · bandejas: N10</t>
   </si>
   <si>
     <t xml:space="preserve">   Carro porta-bandejas: cuerpos con fondo → bordoneado</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B37 y B42; Pulmones fila 14</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros A42:B42 (lugar de 1 m² del carro de 1,3 × 0,7 m) y B37 (3 bandejas) · cantidad: Pulmones S14 (¿puede parar el que entrega?: Z14)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga R45 (máq.) y S45 (turnos)</t>
   </si>
   <si>
     <t xml:space="preserve">   Bordoneadora</t>
@@ -623,7 +668,10 @@
     <t xml:space="preserve">   Carro porta-bandejas: cuerpos bordoneados → soldadura circunferencial de cúpula y fondo</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B37 y B42; Pulmones fila 15</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros A42:B42 (lugar de 1 m² del carro de 1,3 × 0,7 m) y B37 (3 bandejas) · cantidad: Pulmones S15 (¿puede parar el que entrega?: Z15)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga R46 (máq.) y S46 (turnos)</t>
   </si>
   <si>
     <t xml:space="preserve">   Soldadora circunferencial</t>
@@ -644,7 +692,7 @@
     <t xml:space="preserve">Estante de cajones al pie de la soldadura circunferencial; máx. 407 u en 9 bandejas o cajones</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B7:B9; Pulmones fila 13</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros B7 (frente 1.200), B8 (fondo 600) y B9 (alto 2.000) · módulos: Pulmones O13 · máximo: H13 · bandejas: N13</t>
   </si>
   <si>
     <t xml:space="preserve">   Estante: cuerpos bordoneados (pulmón)</t>
@@ -653,18 +701,24 @@
     <t xml:space="preserve">Estante: parados en bandejas, un modelo por bandeja; máx. 691 u en 21 bandejas o cajones</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B7:B9; Pulmones fila 15</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros B7 (frente 1.200), B8 (fondo 600) y B9 (alto 2.000) · módulos: Pulmones O15 · máximo: H15 · bandejas: N15</t>
   </si>
   <si>
     <t xml:space="preserve">   Carro porta-bandejas: cilindros soldados → prueba hidráulica</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B37 y B42; Pulmones fila 16</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros A42:B42 (lugar de 1 m² del carro de 1,3 × 0,7 m) y B37 (3 bandejas) · cantidad: Pulmones S16 (¿puede parar el que entrega?: Z16)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga R47 (máq.) y S47 (turnos)</t>
   </si>
   <si>
     <t xml:space="preserve">   Medidor de espesores</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga R50 (máq.) y S50 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Granalladora AirBlast G-100</t>
   </si>
   <si>
@@ -677,18 +731,27 @@
     <t xml:space="preserve">   Carro porta-bandejas: cilindros granallados → pintura en polvo + horno</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B37 y B42; Pulmones fila 19</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros A42:B42 (lugar de 1 m² del carro de 1,3 × 0,7 m) y B37 (3 bandejas) · cantidad: Pulmones S19 (¿puede parar el que entrega?: Z19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga R51 (máq.) y S51 (turnos)</t>
   </si>
   <si>
     <t xml:space="preserve">   Puesto de detección de defectos</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga R52 (máq.) y S52 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Puesto de corrección de defectos</t>
   </si>
   <si>
     <t xml:space="preserve">Cotización Firesafer (sanding machine)</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga R53 (máq.) y S53 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Horno (precalentamiento y curado)</t>
   </si>
   <si>
@@ -716,19 +779,22 @@
     <t xml:space="preserve">Estante: parados en bandejas, un modelo por bandeja; máx. 488 u en 7 bandejas o cajones</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B7:B9; Pulmones fila 19</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros B7 (frente 1.200), B8 (fondo 600) y B9 (alto 2.000) · módulos: Pulmones O19 · máximo: H19 · bandejas: N19</t>
   </si>
   <si>
     <t xml:space="preserve">   Carro porta-bandejas: cilindros vacíos pintados → embalaje y paletizado</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B37 y B42; Pulmones fila 20</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros A42:B42 (lugar de 1 m² del carro de 1,3 × 0,7 m) y B37 (3 bandejas) · cantidad: Pulmones S20 (¿puede parar el que entrega?: Z20)</t>
   </si>
   <si>
     <t xml:space="preserve">   Carro porta-bandejas: cilindros pintados para cargar → carga de polvo</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B37 y B42; Pulmones fila 21</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros A42:B42 (lugar de 1 m² del carro de 1,3 × 0,7 m) y B37 (3 bandejas) · cantidad: Pulmones S21 (¿puede parar el que entrega?: Z21)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga R54 (máq.) y S54 (turnos)</t>
   </si>
   <si>
     <t xml:space="preserve">   Cargadora de polvo Yukon M-000121</t>
@@ -746,13 +812,16 @@
     <t xml:space="preserve">Estante: parados en bandejas, un modelo por bandeja; máx. 330 u en 11 bandejas o cajones</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B7:B9; Pulmones fila 21</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros B7 (frente 1.200), B8 (fondo 600) y B9 (alto 2.000) · módulos: Pulmones O21 · máximo: H21 · bandejas: N21</t>
   </si>
   <si>
     <t xml:space="preserve">   Carro porta-bandejas: cilindros cargados de polvo → ensamblaje</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B37 y B42; Pulmones fila 22</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros A42:B42 (lugar de 1 m² del carro de 1,3 × 0,7 m) y B37 (3 bandejas) · cantidad: Pulmones S22 (¿puede parar el que entrega?: Z22)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga R55 (máq.) y S55 (turnos)</t>
   </si>
   <si>
     <t xml:space="preserve">   Roscadora de manómetro y tubo Firesafer FS-NGNP</t>
@@ -767,13 +836,16 @@
     <t xml:space="preserve">Estante: parados en bandejas, un modelo por bandeja; máx. 183 u en 9 bandejas o cajones</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B7:B9; Pulmones fila 22</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros B7 (frente 1.200), B8 (fondo 600) y B9 (alto 2.000) · módulos: Pulmones O22 · máximo: H22 · bandejas: N22</t>
   </si>
   <si>
     <t xml:space="preserve">   Carro porta-bandejas: matafuegos armados → presurización</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B37 y B42; Pulmones fila 23</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros A42:B42 (lugar de 1 m² del carro de 1,3 × 0,7 m) y B37 (3 bandejas) · cantidad: Pulmones S23 (¿puede parar el que entrega?: Z23)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga R56 (máq.) y S56 (turnos)</t>
   </si>
   <si>
     <t xml:space="preserve">   Pinza de presurización Yukon M-000150</t>
@@ -794,13 +866,16 @@
     <t xml:space="preserve">Estante: parados en bandejas, un modelo por bandeja; máx. 168 u en 7 bandejas o cajones</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B7:B9; Pulmones fila 23</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros B7 (frente 1.200), B8 (fondo 600) y B9 (alto 2.000) · módulos: Pulmones O23 · máximo: H23 · bandejas: N23</t>
   </si>
   <si>
     <t xml:space="preserve">   Carro porta-bandejas: matafuegos presurizados → control de calidad</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B37 y B42; Pulmones fila 24</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros A42:B42 (lugar de 1 m² del carro de 1,3 × 0,7 m) y B37 (3 bandejas) · cantidad: Pulmones S24 (¿puede parar el que entrega?: Z24)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga R57 (máq.) y S57 (turnos)</t>
   </si>
   <si>
     <t xml:space="preserve">   Tanque de ensayo de pérdidas Firesafer FS-SS100</t>
@@ -821,13 +896,16 @@
     <t xml:space="preserve">Estante: parados en bandejas, un modelo por bandeja; máx. 161 u en 3 bandejas o cajones</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B7:B9; Pulmones fila 24</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros B7 (frente 1.200), B8 (fondo 600) y B9 (alto 2.000) · módulos: Pulmones O24 · máximo: H24 · bandejas: N24</t>
   </si>
   <si>
     <t xml:space="preserve">   Carro porta-bandejas: matafuegos ensayados → etiquetado</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B37 y B42; Pulmones fila 25</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros A42:B42 (lugar de 1 m² del carro de 1,3 × 0,7 m) y B37 (3 bandejas) · cantidad: Pulmones S25 (¿puede parar el que entrega?: Z25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga R58 (máq.) y S58 (turnos)</t>
   </si>
   <si>
     <t xml:space="preserve">   Etiquetadora</t>
@@ -842,13 +920,16 @@
     <t xml:space="preserve">Estante: parados en bandejas, un modelo por bandeja; máx. 241 u en 8 bandejas o cajones</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B7:B9; Pulmones fila 25</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros B7 (frente 1.200), B8 (fondo 600) y B9 (alto 2.000) · módulos: Pulmones O25 · máximo: H25 · bandejas: N25</t>
   </si>
   <si>
     <t xml:space="preserve">   Carro porta-bandejas: matafuegos etiquetados → embalaje y paletizado</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B37 y B42; Pulmones fila 26</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros A42:B42 (lugar de 1 m² del carro de 1,3 × 0,7 m) y B37 (3 bandejas) · cantidad: Pulmones S26 (¿puede parar el que entrega?: Z26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga R59 (máq.) y S59 (turnos)</t>
   </si>
   <si>
     <t xml:space="preserve">   Envolvedora EDOS PS 5</t>
@@ -872,12 +953,15 @@
     <t xml:space="preserve">Estante: parados en bandejas, un modelo por bandeja; máx. 421 u en 5 bandejas o cajones</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B7:B9; Pulmones fila 20</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros B7 (frente 1.200), B8 (fondo 600) y B9 (alto 2.000) · módulos: Pulmones O20 · máximo: H20 · bandejas: N20</t>
   </si>
   <si>
     <t xml:space="preserve">CARROS — lo que va dentro de cada puesto</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M77 (máq.) y N77 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Roladora de carros</t>
   </si>
   <si>
@@ -890,7 +974,10 @@
     <t xml:space="preserve">Sobre la mesa móvil de la guillotina, apilados (tanda de corte); máx. 52 recipientes; huella = m² de Pulmones ÷ 1,4 de circulación</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Carros fila 6</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Carros J6 (m²), H6 (máximo) e I6 (cómo espera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M78 (máq.) y N78 (turnos)</t>
   </si>
   <si>
     <t xml:space="preserve">   Virador de punteo</t>
@@ -902,7 +989,10 @@
     <t xml:space="preserve">Piso demarcado de 1,8 × 1,2 m al pie del punteo, paradas; máx. 2 recipientes; huella = m² de Pulmones ÷ 1,4 de circulación</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Carros fila 7</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Carros J7 (m²), H7 (máximo) e I7 (cómo espera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M79 (máq.) y N79 (turnos)</t>
   </si>
   <si>
     <t xml:space="preserve">   Soldadora longitudinal Dragon ZH-1300</t>
@@ -923,6 +1013,9 @@
     <t xml:space="preserve">Son medidas del embalaje, no de la máquina</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M80 (máq.) y N80 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Soldadora de cupla</t>
   </si>
   <si>
@@ -932,7 +1025,10 @@
     <t xml:space="preserve">En el carro canasto entre la soldadura de cupla y el armado; máx. 13 recipientes; huella = m² de Pulmones ÷ 1,4 de circulación</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Carros fila 9</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Carros J9 (m²), H9 (máximo) e I9 (cómo espera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M81 (máq.) y N81 (turnos)</t>
   </si>
   <si>
     <t xml:space="preserve">   Virador de armado</t>
@@ -944,7 +1040,10 @@
     <t xml:space="preserve">Piso demarcado al pie del armado (7), parados; máx. 11 recipientes; huella = m² de Pulmones ÷ 1,4 de circulación</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Carros fila 8</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Carros J8 (m²), H8 (máximo) e I8 (cómo espera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M82 (máq.) y N82 (turnos)</t>
   </si>
   <si>
     <t xml:space="preserve">   Virador de accesorios</t>
@@ -956,19 +1055,28 @@
     <t xml:space="preserve">Piso demarcado al pie de accesorios (8), parados; máx. 1 recipientes; huella = m² de Pulmones ÷ 1,4 de circulación</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Carros fila 10</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Carros J10 (m²), H10 (máximo) e I10 (cómo espera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M83 (máq.) y N83 (turnos)</t>
   </si>
   <si>
     <t xml:space="preserve">   Equipos de fabricación de accesorios</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M86 (máq.) y N86 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Piso demarcado: recipientes esperando la pintura (pulmón)</t>
   </si>
   <si>
     <t xml:space="preserve">Espera del pintor: piso demarcado junto al portón, parados con un taco atrás; máx. 29 recipientes; huella = m² de Pulmones ÷ 1,4 de circulación</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Carros fila 11</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Carros J11 (m²), H11 (máximo) e I11 (cómo espera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M87 (máq.) y N87 (turnos)</t>
   </si>
   <si>
     <t xml:space="preserve">   Piso demarcado: carros pintados (pulmón)</t>
@@ -977,18 +1085,30 @@
     <t xml:space="preserve">Piso demarcado de pintados: sin ruedas, parados sobre un taco de madera; máx. 29 recipientes; huella = m² de Pulmones ÷ 1,4 de circulación</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Carros fila 13</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Carros J13 (m²), H13 (máximo) e I13 (cómo espera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M88 (máq.) y N88 (turnos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M89 (máq.) y N89 (turnos)</t>
   </si>
   <si>
     <t xml:space="preserve">   Montaje, manga, precinto y etiquetado</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M90 (máq.) y N90 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Calidad: pérdidas, inspección final y ensayos de lote</t>
   </si>
   <si>
     <t xml:space="preserve">RECARGAS — lo que va dentro de cada puesto</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga F104 (máq.) y G104 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Equipo de recepción y registro</t>
   </si>
   <si>
@@ -998,15 +1118,24 @@
     <t xml:space="preserve">28 equipos por jaula; equipos en el puesto por ley de Little</t>
   </si>
   <si>
-    <t xml:space="preserve">Balanceo, Carga (jaulas) y Parametros (U_JAULA)</t>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M104 (jaulas) y L104 (equipos) · jaula 1,2 × 1,0 m y 28 equipos: Parametros A52:B52</t>
   </si>
   <si>
     <t xml:space="preserve">Alto de la jaula</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga F105 (máq.) y G105 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Equipo de inspección visual</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M105 (jaulas) y L105 (equipos) · jaula 1,2 × 1,0 m y 28 equipos: Parametros A52:B52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga F106 (máq.) y G106 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Recuperadora / cargadora de polvo Firesafer FS-ZR01</t>
   </si>
   <si>
@@ -1019,88 +1148,211 @@
     <t xml:space="preserve">Opción por función: confirmar. Alternativa FS-SDP-1 sin medidas</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M106 (jaulas) y L106 (equipos) · jaula 1,2 × 1,0 m y 28 equipos: Parametros A52:B52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga F107 (máq.) y G107 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Equipo de descarga a descarte (abc, bc y clase d)</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M107 (jaulas) y L107 (equipos) · jaula 1,2 × 1,0 m y 28 equipos: Parametros A52:B52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga F108 (máq.) y G108 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Cargadora de agua y espuma Firesafer FS-SJML01</t>
   </si>
   <si>
     <t xml:space="preserve">Opción por función: confirmar</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M108 (jaulas) y L108 (equipos) · jaula 1,2 × 1,0 m y 28 equipos: Parametros A52:B52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga F109 (máq.) y G109 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Cargadora de CO₂ Firesafer FS-CO2E</t>
   </si>
   <si>
     <t xml:space="preserve">Opción por función: confirmar. Alternativa FS-CO2M 0,70 × 0,55 × 0,60</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M109 (jaulas) y L109 (equipos) · jaula 1,2 × 1,0 m y 28 equipos: Parametros A52:B52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga F110 (máq.) y G110 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Cargadora de agente limpio Firesafer FS-FM2</t>
   </si>
   <si>
     <t xml:space="preserve">Sin medidas en el catálogo</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M110 (jaulas) y L110 (equipos) · jaula 1,2 × 1,0 m y 28 equipos: Parametros A52:B52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga F111 (máq.) y G111 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Equipo de desarme y limpieza</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M111 (jaulas) y L111 (equipos) · jaula 1,2 × 1,0 m y 28 equipos: Parametros A52:B52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga F112 (máq.) y G112 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Equipo de desarme e inspección interior</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M112 (jaulas) y L112 (equipos) · jaula 1,2 × 1,0 m y 28 equipos: Parametros A52:B52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga F113 (máq.) y G113 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Equipo de laboratorio</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M113 (jaulas) y L113 (equipos) · jaula 1,2 × 1,0 m y 28 equipos: Parametros A52:B52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga F114 (máq.) y G114 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Bomba de PH Firesafer FS-HPT1</t>
   </si>
   <si>
     <t xml:space="preserve">   Banco de PH de 3 puestos Firesafer FS-HPT1</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M114 (jaulas) y L114 (equipos) · jaula 1,2 × 1,0 m y 28 equipos: Parametros A52:B52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga F115 (máq.) y G115 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Secadora de 4 bocas Firesafer FS-D4</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M115 (jaulas) y L115 (equipos) · jaula 1,2 × 1,0 m y 28 equipos: Parametros A52:B52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga F116 (máq.) y G116 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Equipo de inspección interior con videoscopio</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M116 (jaulas) y L116 (equipos) · jaula 1,2 × 1,0 m y 28 equipos: Parametros A52:B52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga F117 (máq.) y G117 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Equipo de pintura</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M117 (jaulas) y L117 (equipos) · jaula 1,2 × 1,0 m y 28 equipos: Parametros A52:B52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga F118 (máq.) y G118 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alternativa Firesafer FS-ZR01 0,80 × 0,40 × 1,35</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M118 (jaulas) y L118 (equipos) · jaula 1,2 × 1,0 m y 28 equipos: Parametros A52:B52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga F119 (máq.) y G119 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Morsa manual Firesafer FS-MC</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M119 (jaulas) y L119 (equipos) · jaula 1,2 × 1,0 m y 28 equipos: Parametros A52:B52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga F120 (máq.) y G120 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Presurizadora de N₂ Firesafer FS-N2</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M120 (jaulas) y L120 (equipos) · jaula 1,2 × 1,0 m y 28 equipos: Parametros A52:B52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga F121 (máq.) y G121 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Equipo de ensamblaje y presurización</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M121 (jaulas) y L121 (equipos) · jaula 1,2 × 1,0 m y 28 equipos: Parametros A52:B52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga F122 (máq.) y G122 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Equipo de control de peso (co₂ y halogenados sin recarga)</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M122 (jaulas) y L122 (equipos) · jaula 1,2 × 1,0 m y 28 equipos: Parametros A52:B52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga F123 (máq.) y G123 (turnos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M123 (jaulas) y L123 (equipos) · jaula 1,2 × 1,0 m y 28 equipos: Parametros A52:B52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga F124 (máq.) y G124 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Equipo de precinto, etiqueta y despacho</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M124 (jaulas) y L124 (equipos) · jaula 1,2 × 1,0 m y 28 equipos: Parametros A52:B52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga F125 (máq.) y G125 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Equipo de inutilización y disposición final</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M125 (jaulas) y L125 (equipos) · jaula 1,2 × 1,0 m y 28 equipos: Parametros A52:B52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga F126 (máq.) y G126 (turnos)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Equipo de ph de mangueras (co₂ y rodantes)</t>
   </si>
   <si>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M126 (jaulas) y L126 (equipos) · jaula 1,2 × 1,0 m y 28 equipos: Parametros A52:B52</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Pulmón de recepción (lote retirado que espera entrar)</t>
   </si>
   <si>
     <t xml:space="preserve">½ día de recargas, 271 equipos</t>
   </si>
   <si>
-    <t xml:space="preserve">Balanceo, Carga fila 128</t>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M128 (10 jaulas) y L128 (271 equipos) · jaula: Parametros A52:B52</t>
   </si>
   <si>
     <t xml:space="preserve">   Pulmón de despacho (recargados listos para el recorrido)</t>
   </si>
   <si>
-    <t xml:space="preserve">Balanceo, Carga fila 129</t>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga M129 (10 jaulas) y L129 (271 equipos) · jaula: Parametros A52:B52</t>
   </si>
   <si>
     <t xml:space="preserve">PULMONES — qué se junta entre puestos, cómo espera y cuántos carros</t>
@@ -1508,7 +1760,7 @@
     <t xml:space="preserve">jaulas de 28 equipos (ley de Little por puesto)</t>
   </si>
   <si>
-    <t xml:space="preserve">Balanceo, Carga filas 104 a 130</t>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Carga filas 104 a 130</t>
   </si>
   <si>
     <t xml:space="preserve">Pulmón de entrada</t>
@@ -1568,7 +1820,7 @@
     <t xml:space="preserve">Primer nivel a 100 mm del piso; el último no pasa de 1.600 mm (se carga sin escalera). Entre niveles: alto de la pieza + 100 mm para meter la mano + 40 mm de la bandeja. 1 bandeja o 3 cajones por nivel.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B7:B13</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros B7:B13</t>
   </si>
   <si>
     <t xml:space="preserve">Bandeja metálica</t>
@@ -1580,7 +1832,7 @@
     <t xml:space="preserve">Chapa plegada de 2 mm con borde de 30 mm. Rueda del carro al estante sobre carriles de rodillos. Un solo modelo por bandeja.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B19:B22</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros B19:B22</t>
   </si>
   <si>
     <t xml:space="preserve">Cajón plástico</t>
@@ -1592,7 +1844,7 @@
     <t xml:space="preserve">Interior 560 × 360 × 280 mm (pared y fondo de 20 mm). Fondos y cúpulas en columnas anidadas con 5 mm de luz.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B23:B30</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros B23:B30</t>
   </si>
   <si>
     <t xml:space="preserve">Carro porta-bandejas (tránsito)</t>
@@ -1607,7 +1859,7 @@
     <t xml:space="preserve">3 niveles a la misma altura que los 3 primeros del estante: la bandeja pasa deslizando del carro al estante.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B37, B42</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros B37, B42</t>
   </si>
   <si>
     <t xml:space="preserve">Carro de 12 cajones (tránsito)</t>
@@ -1622,7 +1874,7 @@
     <t xml:space="preserve">4 niveles de 3 cajones de 600 × 400, a la altura de los niveles del estante de cajones (100 / 500 / 900 / 1.300 mm).</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B38</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros B38</t>
   </si>
   <si>
     <t xml:space="preserve">Soporte fijo junto al puesto que entrega</t>
@@ -1637,7 +1889,7 @@
     <t xml:space="preserve">Donde queda la bandeja que se está llenando mientras el carro viaja.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B39</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros B39</t>
   </si>
   <si>
     <t xml:space="preserve">Rack selectivo (supermercado de fondos y cúpulas)</t>
@@ -1649,7 +1901,7 @@
     <t xml:space="preserve">Vano de 2,7 m, 3 pallets de 800 de frente por nivel. Primer nivel a 400 mm (picking a mano entre 0,55 y 1,45 m); arriba, reserva.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B53:B58</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros B53:B58</t>
   </si>
   <si>
     <t xml:space="preserve">Pallet de cajones (fondos o cúpulas)</t>
@@ -1661,7 +1913,7 @@
     <t xml:space="preserve">4 cajones por capa (2 × 2) y 3 capas. Un solo modelo por pallet.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulmones, Parametros B53</t>
+    <t xml:space="preserve">PULMONES-FLAMA2035 › Parametros B53</t>
   </si>
   <si>
     <t xml:space="preserve">Jaula de recargas</t>
@@ -1676,7 +1928,7 @@
     <t xml:space="preserve">Paletizable.</t>
   </si>
   <si>
-    <t xml:space="preserve">Balanceo, Parametros (U_JAULA) y Carga A131</t>
+    <t xml:space="preserve">Balanceo-FLAMA2035 › Parametros (U_JAULA) y Carga A131</t>
   </si>
   <si>
     <t xml:space="preserve">2) CÓMO SE CARGA CADA PIEZA (por modelo)</t>
@@ -1844,7 +2096,7 @@
     <t xml:space="preserve">sueltas en el cajón (Pulmones, Unidades fila 48; límite 20 kg)</t>
   </si>
   <si>
-    <t xml:space="preserve">Fuente: Pulmones, hojas Unidades y Datos (pesos, Ø y altos de cada modelo). Altura de los niveles = 100 mm + n × (alto de la pieza + 100 mm + 40 mm de bandeja).</t>
+    <t xml:space="preserve">Fuente: PULMONES-FLAMA2035, hojas Unidades y Datos (pesos, Ø y altos de cada modelo). Altura de los niveles = 100 mm + n × (alto de la pieza + 100 mm + 40 mm de bandeja).</t>
   </si>
 </sst>
 </file>
@@ -2343,7 +2595,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -2388,7 +2640,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
@@ -2410,6 +2662,14 @@
       </c>
       <c r="B8" s="2" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -2437,31 +2697,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B5" s="8" t="n">
         <f aca="false">Manuales!F5</f>
@@ -2470,7 +2730,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B6" s="8" t="n">
         <f aca="false">Manuales!F12</f>
@@ -2479,7 +2739,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B7" s="8" t="n">
         <f aca="false">Manuales!F15</f>
@@ -2488,7 +2748,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B8" s="8" t="n">
         <f aca="false">Manuales!F20</f>
@@ -2497,7 +2757,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B9" s="8" t="n">
         <f aca="false">Manuales!F24</f>
@@ -2506,7 +2766,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B10" s="8" t="n">
         <f aca="false">Manuales!F29</f>
@@ -2515,7 +2775,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B11" s="8" t="n">
         <f aca="false">Manuales!F32</f>
@@ -2524,7 +2784,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B12" s="8" t="n">
         <f aca="false">Manuales!F38</f>
@@ -2533,7 +2793,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B13" s="8" t="n">
         <f aca="false">Manuales!F42</f>
@@ -2542,7 +2802,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B14" s="8" t="n">
         <f aca="false">Manuales!F48</f>
@@ -2551,7 +2811,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B15" s="8" t="n">
         <f aca="false">Manuales!F51</f>
@@ -2560,7 +2820,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B16" s="8" t="n">
         <f aca="false">Manuales!F55</f>
@@ -2569,7 +2829,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B17" s="8" t="n">
         <f aca="false">Manuales!F58</f>
@@ -2578,7 +2838,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B18" s="8" t="n">
         <f aca="false">Manuales!F61</f>
@@ -2587,7 +2847,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B19" s="8" t="n">
         <f aca="false">Manuales!F68</f>
@@ -2596,7 +2856,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B20" s="8" t="n">
         <f aca="false">Manuales!F73</f>
@@ -2605,7 +2865,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B21" s="8" t="n">
         <f aca="false">Manuales!F78</f>
@@ -2614,7 +2874,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B22" s="8" t="n">
         <f aca="false">Manuales!F83</f>
@@ -2623,7 +2883,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B23" s="8" t="n">
         <f aca="false">Manuales!F88</f>
@@ -2632,7 +2892,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B24" s="8" t="n">
         <f aca="false">Manuales!F93</f>
@@ -2641,7 +2901,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B25" s="10" t="n">
         <f aca="false">SUM(B5:B24)</f>
@@ -2650,13 +2910,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B27" s="7"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B28" s="8" t="n">
         <f aca="false">Carros!F5</f>
@@ -2665,7 +2925,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B29" s="8" t="n">
         <f aca="false">Carros!F9</f>
@@ -2674,7 +2934,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B30" s="8" t="n">
         <f aca="false">Carros!F13</f>
@@ -2683,7 +2943,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B31" s="8" t="n">
         <f aca="false">Carros!F17</f>
@@ -2692,7 +2952,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B32" s="8" t="n">
         <f aca="false">Carros!F21</f>
@@ -2701,7 +2961,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B33" s="8" t="n">
         <f aca="false">Carros!F25</f>
@@ -2710,7 +2970,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B34" s="8" t="n">
         <f aca="false">Carros!F29</f>
@@ -2719,7 +2979,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B35" s="8" t="n">
         <f aca="false">Carros!F32</f>
@@ -2728,7 +2988,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B36" s="8" t="n">
         <f aca="false">Carros!F35</f>
@@ -2737,7 +2997,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B37" s="8" t="n">
         <f aca="false">Carros!F38</f>
@@ -2746,7 +3006,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B38" s="8" t="n">
         <f aca="false">Carros!F41</f>
@@ -2755,7 +3015,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B39" s="8" t="n">
         <f aca="false">Carros!F44</f>
@@ -2764,7 +3024,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B40" s="10" t="n">
         <f aca="false">SUM(B28:B39)</f>
@@ -2773,13 +3033,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B42" s="7"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B43" s="8" t="n">
         <f aca="false">Recargas!F5</f>
@@ -2788,7 +3048,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B44" s="8" t="n">
         <f aca="false">Recargas!F9</f>
@@ -2797,7 +3057,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B45" s="8" t="n">
         <f aca="false">Recargas!F13</f>
@@ -2806,7 +3066,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B46" s="8" t="n">
         <f aca="false">Recargas!F17</f>
@@ -2815,7 +3075,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B47" s="8" t="n">
         <f aca="false">Recargas!F21</f>
@@ -2824,7 +3084,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B48" s="8" t="n">
         <f aca="false">Recargas!F25</f>
@@ -2833,7 +3093,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B49" s="8" t="n">
         <f aca="false">Recargas!F29</f>
@@ -2842,7 +3102,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B50" s="8" t="n">
         <f aca="false">Recargas!F33</f>
@@ -2851,7 +3111,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B51" s="8" t="n">
         <f aca="false">Recargas!F37</f>
@@ -2860,7 +3120,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B52" s="8" t="n">
         <f aca="false">Recargas!F41</f>
@@ -2869,7 +3129,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B53" s="8" t="n">
         <f aca="false">Recargas!F45</f>
@@ -2878,7 +3138,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B54" s="8" t="n">
         <f aca="false">Recargas!F50</f>
@@ -2887,7 +3147,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B55" s="8" t="n">
         <f aca="false">Recargas!F54</f>
@@ -2896,7 +3156,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B56" s="8" t="n">
         <f aca="false">Recargas!F58</f>
@@ -2905,7 +3165,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B57" s="8" t="n">
         <f aca="false">Recargas!F62</f>
@@ -2914,7 +3174,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B58" s="8" t="n">
         <f aca="false">Recargas!F66</f>
@@ -2923,7 +3183,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B59" s="8" t="n">
         <f aca="false">Recargas!F70</f>
@@ -2932,7 +3192,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B60" s="8" t="n">
         <f aca="false">Recargas!F74</f>
@@ -2941,7 +3201,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B61" s="8" t="n">
         <f aca="false">Recargas!F78</f>
@@ -2950,7 +3210,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B62" s="8" t="n">
         <f aca="false">Recargas!F82</f>
@@ -2959,7 +3219,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B63" s="8" t="n">
         <f aca="false">Recargas!F86</f>
@@ -2968,7 +3228,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B64" s="8" t="n">
         <f aca="false">Recargas!F90</f>
@@ -2977,7 +3237,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B65" s="8" t="n">
         <f aca="false">Recargas!F94</f>
@@ -2986,7 +3246,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B66" s="8" t="n">
         <f aca="false">Recargas!F98</f>
@@ -2995,7 +3255,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B67" s="10" t="n">
         <f aca="false">SUM(B43:B66)</f>
@@ -3004,13 +3264,13 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B69" s="7"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B70" s="8" t="n">
         <f aca="false">Compartidos!G5</f>
@@ -3019,7 +3279,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B71" s="8" t="n">
         <f aca="false">Compartidos!G8</f>
@@ -3028,7 +3288,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B72" s="8" t="n">
         <f aca="false">Compartidos!G13</f>
@@ -3037,7 +3297,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B73" s="8" t="n">
         <f aca="false">Compartidos!G17</f>
@@ -3046,7 +3306,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B74" s="8" t="n">
         <f aca="false">Compartidos!G22</f>
@@ -3055,7 +3315,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B75" s="10" t="n">
         <f aca="false">SUM(B70:B74)</f>
@@ -3064,7 +3324,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B77" s="11" t="n">
         <f aca="false">B25+B40+B67+B75</f>
@@ -3102,49 +3362,49 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -3156,40 +3416,42 @@
         <v>0</v>
       </c>
       <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
+      <c r="I5" s="7" t="s">
+        <v>103</v>
+      </c>
       <c r="J5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G6" s="15"/>
       <c r="H6" s="12"/>
       <c r="I6" s="12" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -3201,71 +3463,73 @@
         <v>0.91</v>
       </c>
       <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
+      <c r="I8" s="7" t="s">
+        <v>109</v>
+      </c>
       <c r="J8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="J9" s="17" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="J10" s="17" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C11" s="12" t="n">
         <v>1</v>
@@ -3277,25 +3541,25 @@
         <v>1.3</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G11" s="18" t="n">
         <f aca="false">C11*D11*E11</f>
         <v>0.91</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -3307,15 +3571,17 @@
         <v>4.035</v>
       </c>
       <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
+      <c r="I13" s="7" t="s">
+        <v>121</v>
+      </c>
       <c r="J13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>2</v>
@@ -3334,21 +3600,21 @@
         <v>1.875</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J14" s="17" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C15" s="12" t="n">
         <v>3</v>
@@ -3367,16 +3633,16 @@
         <v>2.16</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="J15" s="14"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -3388,15 +3654,17 @@
         <v>3.87</v>
       </c>
       <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
+      <c r="I17" s="7" t="s">
+        <v>129</v>
+      </c>
       <c r="J17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>2</v>
@@ -3415,21 +3683,21 @@
         <v>0.76</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>1</v>
@@ -3448,21 +3716,21 @@
         <v>0.38</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="J19" s="17" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C20" s="12" t="n">
         <v>3</v>
@@ -3474,25 +3742,25 @@
         <v>1.3</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G20" s="18" t="n">
         <f aca="false">C20*D20*E20</f>
         <v>2.73</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -3504,65 +3772,67 @@
         <v>2.73</v>
       </c>
       <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
+      <c r="I22" s="7" t="s">
+        <v>138</v>
+      </c>
       <c r="J22" s="7"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="17" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="17" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C25" s="12" t="n">
         <v>3</v>
@@ -3574,20 +3844,20 @@
         <v>1.3</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G25" s="18" t="n">
         <f aca="false">C25*D25*E25</f>
         <v>2.73</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -3620,46 +3890,46 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -3670,64 +3940,66 @@
         <v>8.3</v>
       </c>
       <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
+      <c r="H5" s="7" t="s">
+        <v>145</v>
+      </c>
       <c r="I5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>2</v>
@@ -3739,25 +4011,25 @@
         <v>2.7</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F8" s="8" t="n">
         <f aca="false">B8*C8*D8</f>
         <v>6.48</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="I8" s="17" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
@@ -3769,25 +4041,25 @@
         <v>1.3</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F9" s="8" t="n">
         <f aca="false">B9*C9*D9</f>
         <v>0.91</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="I9" s="17" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B10" s="12" t="n">
         <v>1</v>
@@ -3799,25 +4071,25 @@
         <v>1.3</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F10" s="18" t="n">
         <f aca="false">B10*C10*D10</f>
         <v>0.91</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -3828,35 +4100,37 @@
         <v>0</v>
       </c>
       <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
+      <c r="H12" s="7" t="s">
+        <v>164</v>
+      </c>
       <c r="I12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B13" s="12" t="n">
         <v>2</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F13" s="15"/>
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
       <c r="I13" s="14" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -3867,12 +4141,14 @@
         <v>4.03</v>
       </c>
       <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
+      <c r="H15" s="7" t="s">
+        <v>166</v>
+      </c>
       <c r="I15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>1</v>
@@ -3891,18 +4167,18 @@
         <v>1.68</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="I16" s="17" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>2</v>
@@ -3921,16 +4197,16 @@
         <v>1.44</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="I17" s="17"/>
     </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="B18" s="12" t="n">
         <v>1</v>
@@ -3942,25 +4218,25 @@
         <v>1.3</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F18" s="18" t="n">
         <f aca="false">B18*C18*D18</f>
         <v>0.91</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -3971,12 +4247,14 @@
         <v>3.25</v>
       </c>
       <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
+      <c r="H20" s="7" t="s">
+        <v>176</v>
+      </c>
       <c r="I20" s="7"/>
     </row>
     <row r="21" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
@@ -3995,18 +4273,18 @@
         <v>2.34</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="I21" s="17" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="B22" s="12" t="n">
         <v>1</v>
@@ -4018,25 +4296,25 @@
         <v>1.3</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F22" s="18" t="n">
         <f aca="false">B22*C22*D22</f>
         <v>0.91</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -4047,38 +4325,40 @@
         <v>5.95</v>
       </c>
       <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
+      <c r="H24" s="7" t="s">
+        <v>183</v>
+      </c>
       <c r="I24" s="7"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="I25" s="17" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>7</v>
@@ -4097,16 +4377,16 @@
         <v>5.04</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="I26" s="17"/>
     </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="B27" s="12" t="n">
         <v>1</v>
@@ -4118,25 +4398,25 @@
         <v>1.3</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F27" s="18" t="n">
         <f aca="false">B27*C27*D27</f>
         <v>0.91</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -4147,37 +4427,39 @@
         <v>0</v>
       </c>
       <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
+      <c r="H29" s="7" t="s">
+        <v>193</v>
+      </c>
       <c r="I29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="B30" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F30" s="15"/>
       <c r="G30" s="12"/>
       <c r="H30" s="12" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -4188,38 +4470,40 @@
         <v>5.23</v>
       </c>
       <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
+      <c r="H32" s="7" t="s">
+        <v>196</v>
+      </c>
       <c r="I32" s="7"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="I33" s="17" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>4</v>
@@ -4238,16 +4522,16 @@
         <v>2.88</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="I34" s="17"/>
     </row>
     <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>2</v>
@@ -4266,16 +4550,16 @@
         <v>1.44</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="I35" s="17"/>
     </row>
-    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="B36" s="12" t="n">
         <v>1</v>
@@ -4287,25 +4571,25 @@
         <v>1.3</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F36" s="18" t="n">
         <f aca="false">B36*C36*D36</f>
         <v>0.91</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -4316,36 +4600,38 @@
         <v>0.91</v>
       </c>
       <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
+      <c r="H38" s="7" t="s">
+        <v>209</v>
+      </c>
       <c r="I38" s="7"/>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="I39" s="17" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="B40" s="12" t="n">
         <v>1</v>
@@ -4357,25 +4643,25 @@
         <v>1.3</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F40" s="18" t="n">
         <f aca="false">B40*C40*D40</f>
         <v>0.91</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="I40" s="14" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -4386,38 +4672,40 @@
         <v>10.31</v>
       </c>
       <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
+      <c r="H42" s="7" t="s">
+        <v>214</v>
+      </c>
       <c r="I42" s="7"/>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>1</v>
@@ -4436,16 +4724,16 @@
         <v>0.72</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="I44" s="17"/>
     </row>
-    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>7</v>
@@ -4464,16 +4752,16 @@
         <v>5.04</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="I45" s="17"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="B46" s="12" t="n">
         <v>5</v>
@@ -4485,25 +4773,25 @@
         <v>1.3</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F46" s="18" t="n">
         <f aca="false">B46*C46*D46</f>
         <v>4.55</v>
       </c>
       <c r="G46" s="12" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="I46" s="14" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -4514,35 +4802,37 @@
         <v>0</v>
       </c>
       <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
+      <c r="H48" s="7" t="s">
+        <v>227</v>
+      </c>
       <c r="I48" s="7"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="B49" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F49" s="15"/>
       <c r="G49" s="12"/>
       <c r="H49" s="12"/>
       <c r="I49" s="14" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
@@ -4553,12 +4843,14 @@
         <v>6.76</v>
       </c>
       <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
+      <c r="H51" s="7" t="s">
+        <v>229</v>
+      </c>
       <c r="I51" s="7"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>1</v>
@@ -4578,15 +4870,15 @@
       </c>
       <c r="G52" s="2"/>
       <c r="H52" s="2" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="I52" s="17" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="B53" s="12" t="n">
         <v>1</v>
@@ -4598,25 +4890,25 @@
         <v>1.3</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F53" s="18" t="n">
         <f aca="false">B53*C53*D53</f>
         <v>0.91</v>
       </c>
       <c r="G53" s="12" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="I53" s="14" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
@@ -4627,35 +4919,37 @@
         <v>0</v>
       </c>
       <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
+      <c r="H55" s="7" t="s">
+        <v>235</v>
+      </c>
       <c r="I55" s="7"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="B56" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F56" s="15"/>
       <c r="G56" s="12"/>
       <c r="H56" s="12"/>
       <c r="I56" s="14" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
@@ -4666,37 +4960,39 @@
         <v>0</v>
       </c>
       <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
+      <c r="H58" s="7" t="s">
+        <v>237</v>
+      </c>
       <c r="I58" s="7"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="B59" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F59" s="15"/>
       <c r="G59" s="12"/>
       <c r="H59" s="12" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="I59" s="14" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B61" s="7"/>
       <c r="C61" s="7"/>
@@ -4707,12 +5003,14 @@
         <v>35.54</v>
       </c>
       <c r="G61" s="7"/>
-      <c r="H61" s="7"/>
+      <c r="H61" s="7" t="s">
+        <v>240</v>
+      </c>
       <c r="I61" s="7"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="B62" s="2" t="n">
         <v>2</v>
@@ -4731,18 +5029,18 @@
         <v>29.28</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="I62" s="17" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>1</v>
@@ -4761,18 +5059,18 @@
         <v>3</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>2</v>
@@ -4791,16 +5089,16 @@
         <v>1.44</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="I64" s="17"/>
     </row>
-    <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>1</v>
@@ -4812,25 +5110,25 @@
         <v>1.3</v>
       </c>
       <c r="E65" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F65" s="8" t="n">
         <f aca="false">B65*C65*D65</f>
         <v>0.91</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="I65" s="17" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="12" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="B66" s="12" t="n">
         <v>1</v>
@@ -4842,25 +5140,25 @@
         <v>1.3</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F66" s="18" t="n">
         <f aca="false">B66*C66*D66</f>
         <v>0.91</v>
       </c>
       <c r="G66" s="12" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H66" s="12" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="I66" s="14" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B68" s="7"/>
       <c r="C68" s="7"/>
@@ -4871,12 +5169,14 @@
         <v>4.1062</v>
       </c>
       <c r="G68" s="7"/>
-      <c r="H68" s="7"/>
+      <c r="H68" s="7" t="s">
+        <v>255</v>
+      </c>
       <c r="I68" s="7"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>1</v>
@@ -4896,15 +5196,15 @@
       </c>
       <c r="G69" s="2"/>
       <c r="H69" s="2" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="I69" s="17" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>4</v>
@@ -4923,16 +5223,16 @@
         <v>2.88</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="I70" s="17"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="12" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="B71" s="12" t="n">
         <v>1</v>
@@ -4944,25 +5244,25 @@
         <v>1.3</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F71" s="18" t="n">
         <f aca="false">B71*C71*D71</f>
         <v>0.91</v>
       </c>
       <c r="G71" s="12" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H71" s="12" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="I71" s="14" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
@@ -4973,12 +5273,14 @@
         <v>3.395</v>
       </c>
       <c r="G73" s="7"/>
-      <c r="H73" s="7"/>
+      <c r="H73" s="7" t="s">
+        <v>264</v>
+      </c>
       <c r="I73" s="7"/>
     </row>
     <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>1</v>
@@ -4998,13 +5300,13 @@
       </c>
       <c r="G74" s="2"/>
       <c r="H74" s="2" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="I74" s="17"/>
     </row>
-    <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>3</v>
@@ -5023,16 +5325,16 @@
         <v>2.16</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="I75" s="17"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="B76" s="12" t="n">
         <v>1</v>
@@ -5044,25 +5346,25 @@
         <v>1.3</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F76" s="18" t="n">
         <f aca="false">B76*C76*D76</f>
         <v>0.91</v>
       </c>
       <c r="G76" s="12" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H76" s="12" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="I76" s="14" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
@@ -5073,38 +5375,40 @@
         <v>3.07</v>
       </c>
       <c r="G78" s="7"/>
-      <c r="H78" s="7"/>
+      <c r="H78" s="7" t="s">
+        <v>272</v>
+      </c>
       <c r="I78" s="7"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C79" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D79" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E79" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="I79" s="17" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>3</v>
@@ -5123,16 +5427,16 @@
         <v>2.16</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="I80" s="17"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="12" t="s">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="B81" s="12" t="n">
         <v>1</v>
@@ -5144,25 +5448,25 @@
         <v>1.3</v>
       </c>
       <c r="E81" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F81" s="18" t="n">
         <f aca="false">B81*C81*D81</f>
         <v>0.91</v>
       </c>
       <c r="G81" s="12" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H81" s="12" t="s">
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="I81" s="14" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
@@ -5173,12 +5477,14 @@
         <v>3.43</v>
       </c>
       <c r="G83" s="7"/>
-      <c r="H83" s="7"/>
+      <c r="H83" s="7" t="s">
+        <v>282</v>
+      </c>
       <c r="I83" s="7"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
-        <v>258</v>
+        <v>283</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>1</v>
@@ -5197,18 +5503,18 @@
         <v>1.8</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="I84" s="17" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>1</v>
@@ -5227,16 +5533,16 @@
         <v>0.72</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>263</v>
+        <v>288</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="I85" s="17"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="12" t="s">
-        <v>265</v>
+        <v>290</v>
       </c>
       <c r="B86" s="12" t="n">
         <v>1</v>
@@ -5248,25 +5554,25 @@
         <v>1.3</v>
       </c>
       <c r="E86" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F86" s="18" t="n">
         <f aca="false">B86*C86*D86</f>
         <v>0.91</v>
       </c>
       <c r="G86" s="12" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H86" s="12" t="s">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="I86" s="14" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
@@ -5277,36 +5583,38 @@
         <v>3.07</v>
       </c>
       <c r="G88" s="7"/>
-      <c r="H88" s="7"/>
+      <c r="H88" s="7" t="s">
+        <v>292</v>
+      </c>
       <c r="I88" s="7"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="s">
-        <v>267</v>
+        <v>293</v>
       </c>
       <c r="B89" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C89" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D89" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E89" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G89" s="2"/>
       <c r="H89" s="2" t="s">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="I89" s="17" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
-        <v>269</v>
+        <v>295</v>
       </c>
       <c r="B90" s="2" t="n">
         <v>3</v>
@@ -5325,16 +5633,16 @@
         <v>2.16</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>270</v>
+        <v>296</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>271</v>
+        <v>297</v>
       </c>
       <c r="I90" s="17"/>
     </row>
-    <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="12" t="s">
-        <v>272</v>
+        <v>298</v>
       </c>
       <c r="B91" s="12" t="n">
         <v>1</v>
@@ -5346,25 +5654,25 @@
         <v>1.3</v>
       </c>
       <c r="E91" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F91" s="18" t="n">
         <f aca="false">B91*C91*D91</f>
         <v>0.91</v>
       </c>
       <c r="G91" s="12" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H91" s="12" t="s">
-        <v>273</v>
+        <v>299</v>
       </c>
       <c r="I91" s="14" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B93" s="7"/>
       <c r="C93" s="7"/>
@@ -5375,12 +5683,14 @@
         <v>8.8084</v>
       </c>
       <c r="G93" s="7"/>
-      <c r="H93" s="7"/>
+      <c r="H93" s="7" t="s">
+        <v>300</v>
+      </c>
       <c r="I93" s="7"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="B94" s="2" t="n">
         <v>1</v>
@@ -5399,16 +5709,16 @@
         <v>4.5</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>275</v>
+        <v>302</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="I94" s="17"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>277</v>
+        <v>304</v>
       </c>
       <c r="B95" s="2" t="n">
         <v>1</v>
@@ -5428,15 +5738,15 @@
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="2" t="s">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="I95" s="17" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="12" t="s">
-        <v>279</v>
+        <v>306</v>
       </c>
       <c r="B96" s="12" t="n">
         <v>2</v>
@@ -5455,10 +5765,10 @@
         <v>1.44</v>
       </c>
       <c r="G96" s="12" t="s">
-        <v>280</v>
+        <v>307</v>
       </c>
       <c r="H96" s="12" t="s">
-        <v>281</v>
+        <v>308</v>
       </c>
       <c r="I96" s="14"/>
     </row>
@@ -5492,46 +5802,46 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>282</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -5542,34 +5852,36 @@
         <v>5.25414285714286</v>
       </c>
       <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
+      <c r="H5" s="7" t="s">
+        <v>310</v>
+      </c>
       <c r="I5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>283</v>
+        <v>311</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="17" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>284</v>
+        <v>312</v>
       </c>
       <c r="B7" s="12" t="n">
         <v>1</v>
@@ -5577,23 +5889,23 @@
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
       <c r="E7" s="12" t="s">
-        <v>285</v>
+        <v>313</v>
       </c>
       <c r="F7" s="18" t="n">
         <f aca="false">7.3558/1.4</f>
         <v>5.25414285714286</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>286</v>
+        <v>314</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>287</v>
+        <v>315</v>
       </c>
       <c r="I7" s="14"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -5604,34 +5916,36 @@
         <v>0.352785714285714</v>
       </c>
       <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
+      <c r="H9" s="7" t="s">
+        <v>316</v>
+      </c>
       <c r="I9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>288</v>
+        <v>317</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="17" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>289</v>
+        <v>318</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>1</v>
@@ -5639,23 +5953,23 @@
       <c r="C11" s="18"/>
       <c r="D11" s="18"/>
       <c r="E11" s="12" t="s">
-        <v>285</v>
+        <v>313</v>
       </c>
       <c r="F11" s="18" t="n">
         <f aca="false">0.4939/1.4</f>
         <v>0.352785714285714</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>290</v>
+        <v>319</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>291</v>
+        <v>320</v>
       </c>
       <c r="I11" s="14"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -5666,12 +5980,14 @@
         <v>3.0036</v>
       </c>
       <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
+      <c r="H13" s="7" t="s">
+        <v>321</v>
+      </c>
       <c r="I13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
@@ -5690,16 +6006,16 @@
         <v>2.622</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>293</v>
+        <v>323</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>294</v>
+        <v>324</v>
       </c>
       <c r="I14" s="17"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>295</v>
+        <v>325</v>
       </c>
       <c r="B15" s="12" t="n">
         <v>1</v>
@@ -5718,18 +6034,18 @@
         <v>0.3816</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>296</v>
+        <v>326</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>294</v>
+        <v>324</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -5740,34 +6056,36 @@
         <v>0.471642857142857</v>
       </c>
       <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
+      <c r="H17" s="7" t="s">
+        <v>328</v>
+      </c>
       <c r="I17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>298</v>
+        <v>329</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="17" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>299</v>
+        <v>330</v>
       </c>
       <c r="B19" s="12" t="n">
         <v>1</v>
@@ -5775,23 +6093,23 @@
       <c r="C19" s="18"/>
       <c r="D19" s="18"/>
       <c r="E19" s="12" t="s">
-        <v>285</v>
+        <v>313</v>
       </c>
       <c r="F19" s="18" t="n">
         <f aca="false">0.6603/1.4</f>
         <v>0.471642857142857</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>300</v>
+        <v>331</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>301</v>
+        <v>332</v>
       </c>
       <c r="I19" s="14"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -5802,34 +6120,36 @@
         <v>2.19521428571429</v>
       </c>
       <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
+      <c r="H21" s="7" t="s">
+        <v>333</v>
+      </c>
       <c r="I21" s="7"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>302</v>
+        <v>334</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="17" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>303</v>
+        <v>335</v>
       </c>
       <c r="B23" s="12" t="n">
         <v>1</v>
@@ -5837,23 +6157,23 @@
       <c r="C23" s="18"/>
       <c r="D23" s="18"/>
       <c r="E23" s="12" t="s">
-        <v>285</v>
+        <v>313</v>
       </c>
       <c r="F23" s="18" t="n">
         <f aca="false">3.0733/1.4</f>
         <v>2.19521428571429</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>304</v>
+        <v>336</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>305</v>
+        <v>337</v>
       </c>
       <c r="I23" s="14"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -5864,34 +6184,36 @@
         <v>0.176428571428571</v>
       </c>
       <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
+      <c r="H25" s="7" t="s">
+        <v>338</v>
+      </c>
       <c r="I25" s="7"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>306</v>
+        <v>339</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="17" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>307</v>
+        <v>340</v>
       </c>
       <c r="B27" s="12" t="n">
         <v>1</v>
@@ -5899,23 +6221,23 @@
       <c r="C27" s="18"/>
       <c r="D27" s="18"/>
       <c r="E27" s="12" t="s">
-        <v>285</v>
+        <v>313</v>
       </c>
       <c r="F27" s="18" t="n">
         <f aca="false">0.247/1.4</f>
         <v>0.176428571428571</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>308</v>
+        <v>341</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>309</v>
+        <v>342</v>
       </c>
       <c r="I27" s="14"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -5926,35 +6248,37 @@
         <v>0</v>
       </c>
       <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
+      <c r="H29" s="7" t="s">
+        <v>343</v>
+      </c>
       <c r="I29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>310</v>
+        <v>344</v>
       </c>
       <c r="B30" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F30" s="15"/>
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
       <c r="I30" s="14" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -5965,12 +6289,14 @@
         <v>12.65</v>
       </c>
       <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
+      <c r="H32" s="7" t="s">
+        <v>345</v>
+      </c>
       <c r="I32" s="7"/>
     </row>
     <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>311</v>
+        <v>346</v>
       </c>
       <c r="B33" s="12" t="n">
         <v>1</v>
@@ -5978,23 +6304,23 @@
       <c r="C33" s="18"/>
       <c r="D33" s="18"/>
       <c r="E33" s="12" t="s">
-        <v>285</v>
+        <v>313</v>
       </c>
       <c r="F33" s="18" t="n">
         <f aca="false">17.71/1.4</f>
         <v>12.65</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>312</v>
+        <v>347</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>313</v>
+        <v>348</v>
       </c>
       <c r="I33" s="14"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -6005,12 +6331,14 @@
         <v>12.65</v>
       </c>
       <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
+      <c r="H35" s="7" t="s">
+        <v>349</v>
+      </c>
       <c r="I35" s="7"/>
     </row>
     <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>314</v>
+        <v>350</v>
       </c>
       <c r="B36" s="12" t="n">
         <v>1</v>
@@ -6018,23 +6346,23 @@
       <c r="C36" s="18"/>
       <c r="D36" s="18"/>
       <c r="E36" s="12" t="s">
-        <v>285</v>
+        <v>313</v>
       </c>
       <c r="F36" s="18" t="n">
         <f aca="false">17.71/1.4</f>
         <v>12.65</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>315</v>
+        <v>351</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>316</v>
+        <v>352</v>
       </c>
       <c r="I36" s="14"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -6045,12 +6373,14 @@
         <v>0.3162</v>
       </c>
       <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
+      <c r="H38" s="7" t="s">
+        <v>353</v>
+      </c>
       <c r="I38" s="7"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="B39" s="12" t="n">
         <v>1</v>
@@ -6070,13 +6400,13 @@
       </c>
       <c r="G39" s="12"/>
       <c r="H39" s="12" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="I39" s="14"/>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
@@ -6087,35 +6417,37 @@
         <v>0</v>
       </c>
       <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
+      <c r="H41" s="7" t="s">
+        <v>354</v>
+      </c>
       <c r="I41" s="7"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>317</v>
+        <v>355</v>
       </c>
       <c r="B42" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F42" s="15"/>
       <c r="G42" s="12"/>
       <c r="H42" s="12"/>
       <c r="I42" s="14" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
@@ -6126,30 +6458,32 @@
         <v>0</v>
       </c>
       <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
+      <c r="H44" s="7" t="s">
+        <v>356</v>
+      </c>
       <c r="I44" s="7"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>318</v>
+        <v>357</v>
       </c>
       <c r="B45" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F45" s="15"/>
       <c r="G45" s="12"/>
       <c r="H45" s="12"/>
       <c r="I45" s="14" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -6182,46 +6516,46 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -6232,34 +6566,36 @@
         <v>2.4</v>
       </c>
       <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
+      <c r="H5" s="7" t="s">
+        <v>359</v>
+      </c>
       <c r="I5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="17" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="B7" s="12" t="n">
         <v>2</v>
@@ -6271,25 +6607,25 @@
         <v>1.2</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F7" s="18" t="n">
         <f aca="false">B7*C7*D7</f>
         <v>2.4</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>323</v>
+        <v>363</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -6300,34 +6636,36 @@
         <v>1.2</v>
       </c>
       <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
+      <c r="H9" s="7" t="s">
+        <v>365</v>
+      </c>
       <c r="I9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>325</v>
+        <v>366</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="17" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>1</v>
@@ -6339,25 +6677,25 @@
         <v>1.2</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F11" s="18" t="n">
         <f aca="false">B11*C11*D11</f>
         <v>1.2</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>323</v>
+        <v>367</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -6368,12 +6706,14 @@
         <v>1.52</v>
       </c>
       <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
+      <c r="H13" s="7" t="s">
+        <v>368</v>
+      </c>
       <c r="I13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>326</v>
+        <v>369</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
@@ -6392,18 +6732,18 @@
         <v>0.32</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>327</v>
+        <v>370</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>328</v>
+        <v>371</v>
       </c>
       <c r="I14" s="17" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="B15" s="12" t="n">
         <v>1</v>
@@ -6415,25 +6755,25 @@
         <v>1.2</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F15" s="18" t="n">
         <f aca="false">B15*C15*D15</f>
         <v>1.2</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>323</v>
+        <v>373</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -6444,34 +6784,36 @@
         <v>1.2</v>
       </c>
       <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
+      <c r="H17" s="7" t="s">
+        <v>374</v>
+      </c>
       <c r="I17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="17" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="B19" s="12" t="n">
         <v>1</v>
@@ -6483,25 +6825,25 @@
         <v>1.2</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F19" s="18" t="n">
         <f aca="false">B19*C19*D19</f>
         <v>1.2</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>323</v>
+        <v>376</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -6512,12 +6854,14 @@
         <v>1.548</v>
       </c>
       <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
+      <c r="H21" s="7" t="s">
+        <v>377</v>
+      </c>
       <c r="I21" s="7"/>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>331</v>
+        <v>378</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
@@ -6537,15 +6881,15 @@
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2" t="s">
-        <v>328</v>
+        <v>371</v>
       </c>
       <c r="I22" s="17" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="B23" s="12" t="n">
         <v>1</v>
@@ -6557,25 +6901,25 @@
         <v>1.2</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F23" s="18" t="n">
         <f aca="false">B23*C23*D23</f>
         <v>1.2</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>323</v>
+        <v>380</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -6586,12 +6930,14 @@
         <v>1.5575</v>
       </c>
       <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
+      <c r="H25" s="7" t="s">
+        <v>381</v>
+      </c>
       <c r="I25" s="7"/>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>333</v>
+        <v>382</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
@@ -6611,15 +6957,15 @@
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2" t="s">
-        <v>328</v>
+        <v>371</v>
       </c>
       <c r="I26" s="17" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="B27" s="12" t="n">
         <v>1</v>
@@ -6631,25 +6977,25 @@
         <v>1.2</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F27" s="18" t="n">
         <f aca="false">B27*C27*D27</f>
         <v>1.2</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>323</v>
+        <v>384</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -6660,36 +7006,38 @@
         <v>1.2</v>
       </c>
       <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
+      <c r="H29" s="7" t="s">
+        <v>385</v>
+      </c>
       <c r="I29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>335</v>
+        <v>386</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2" t="s">
-        <v>328</v>
+        <v>371</v>
       </c>
       <c r="I30" s="17" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="B31" s="12" t="n">
         <v>1</v>
@@ -6701,25 +7049,25 @@
         <v>1.2</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F31" s="18" t="n">
         <f aca="false">B31*C31*D31</f>
         <v>1.2</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
@@ -6730,34 +7078,36 @@
         <v>1.2</v>
       </c>
       <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
+      <c r="H33" s="7" t="s">
+        <v>389</v>
+      </c>
       <c r="I33" s="7"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>337</v>
+        <v>390</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="17" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="B35" s="12" t="n">
         <v>1</v>
@@ -6769,25 +7119,25 @@
         <v>1.2</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F35" s="18" t="n">
         <f aca="false">B35*C35*D35</f>
         <v>1.2</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>323</v>
+        <v>391</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>324</v>
+        <v>364</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -6798,34 +7148,36 @@
         <v>1.2</v>
       </c>
       <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
+      <c r="H37" s="7" t="s">
+        <v>392</v>
+      </c>
       <c r="I37" s="7"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>338</v>
+        <v>393</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="17" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="B39" s="12" t="n">
         <v>1</v>
@@ -6837,25 +7189,25 @@
         <v>1.2</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F39" s="18" t="n">
         <f aca="false">B39*C39*D39</f>
         <v>1.2</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>323</v>
+        <v>394</v>
       </c>
       <c r="I39" s="14" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
@@ -6866,34 +7218,36 @@
         <v>1.2</v>
       </c>
       <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
+      <c r="H41" s="7" t="s">
+        <v>395</v>
+      </c>
       <c r="I41" s="7"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>339</v>
+        <v>396</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="17" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="B43" s="12" t="n">
         <v>1</v>
@@ -6905,25 +7259,25 @@
         <v>1.2</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F43" s="18" t="n">
         <f aca="false">B43*C43*D43</f>
         <v>1.2</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>323</v>
+        <v>397</v>
       </c>
       <c r="I43" s="14" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
@@ -6934,12 +7288,14 @@
         <v>2.3143</v>
       </c>
       <c r="G45" s="7"/>
-      <c r="H45" s="7"/>
+      <c r="H45" s="7" t="s">
+        <v>398</v>
+      </c>
       <c r="I45" s="7"/>
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>340</v>
+        <v>399</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>1</v>
@@ -6959,15 +7315,15 @@
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2" t="s">
-        <v>328</v>
+        <v>371</v>
       </c>
       <c r="I46" s="17" t="s">
-        <v>332</v>
+        <v>379</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>341</v>
+        <v>400</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>1</v>
@@ -6987,15 +7343,15 @@
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2" t="s">
-        <v>328</v>
+        <v>371</v>
       </c>
       <c r="I47" s="17" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="B48" s="12" t="n">
         <v>1</v>
@@ -7007,25 +7363,25 @@
         <v>1.2</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F48" s="18" t="n">
         <f aca="false">B48*C48*D48</f>
         <v>1.2</v>
       </c>
       <c r="G48" s="12" t="s">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>323</v>
+        <v>401</v>
       </c>
       <c r="I48" s="14" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
@@ -7036,12 +7392,14 @@
         <v>1.66</v>
       </c>
       <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
+      <c r="H50" s="7" t="s">
+        <v>402</v>
+      </c>
       <c r="I50" s="7"/>
     </row>
     <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>342</v>
+        <v>403</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>1</v>
@@ -7061,15 +7419,15 @@
       </c>
       <c r="G51" s="2"/>
       <c r="H51" s="2" t="s">
-        <v>328</v>
+        <v>371</v>
       </c>
       <c r="I51" s="17" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="B52" s="12" t="n">
         <v>1</v>
@@ -7081,25 +7439,25 @@
         <v>1.2</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F52" s="18" t="n">
         <f aca="false">B52*C52*D52</f>
         <v>1.2</v>
       </c>
       <c r="G52" s="12" t="s">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>323</v>
+        <v>404</v>
       </c>
       <c r="I52" s="14" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
@@ -7110,34 +7468,36 @@
         <v>1.2</v>
       </c>
       <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
+      <c r="H54" s="7" t="s">
+        <v>405</v>
+      </c>
       <c r="I54" s="7"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>343</v>
+        <v>406</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="17" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="B56" s="12" t="n">
         <v>1</v>
@@ -7149,25 +7509,25 @@
         <v>1.2</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F56" s="18" t="n">
         <f aca="false">B56*C56*D56</f>
         <v>1.2</v>
       </c>
       <c r="G56" s="12" t="s">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>323</v>
+        <v>407</v>
       </c>
       <c r="I56" s="14" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
@@ -7178,34 +7538,36 @@
         <v>1.2</v>
       </c>
       <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
+      <c r="H58" s="7" t="s">
+        <v>408</v>
+      </c>
       <c r="I58" s="7"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>344</v>
+        <v>409</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D59" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E59" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
       <c r="I59" s="17" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="B60" s="12" t="n">
         <v>1</v>
@@ -7217,25 +7579,25 @@
         <v>1.2</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F60" s="18" t="n">
         <f aca="false">B60*C60*D60</f>
         <v>1.2</v>
       </c>
       <c r="G60" s="12" t="s">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>323</v>
+        <v>410</v>
       </c>
       <c r="I60" s="14" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B62" s="7"/>
       <c r="C62" s="7"/>
@@ -7246,12 +7608,14 @@
         <v>1.8324</v>
       </c>
       <c r="G62" s="7"/>
-      <c r="H62" s="7"/>
+      <c r="H62" s="7" t="s">
+        <v>411</v>
+      </c>
       <c r="I62" s="7"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>2</v>
@@ -7271,15 +7635,15 @@
       </c>
       <c r="G63" s="2"/>
       <c r="H63" s="2" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="B64" s="12" t="n">
         <v>1</v>
@@ -7291,25 +7655,25 @@
         <v>1.2</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F64" s="18" t="n">
         <f aca="false">B64*C64*D64</f>
         <v>1.2</v>
       </c>
       <c r="G64" s="12" t="s">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="H64" s="12" t="s">
-        <v>323</v>
+        <v>413</v>
       </c>
       <c r="I64" s="14" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B66" s="7"/>
       <c r="C66" s="7"/>
@@ -7320,12 +7684,14 @@
         <v>1.732</v>
       </c>
       <c r="G66" s="7"/>
-      <c r="H66" s="7"/>
+      <c r="H66" s="7" t="s">
+        <v>414</v>
+      </c>
       <c r="I66" s="7"/>
     </row>
     <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>346</v>
+        <v>415</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>2</v>
@@ -7345,15 +7711,15 @@
       </c>
       <c r="G67" s="2"/>
       <c r="H67" s="2" t="s">
-        <v>328</v>
+        <v>371</v>
       </c>
       <c r="I67" s="17" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="12" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="B68" s="12" t="n">
         <v>1</v>
@@ -7365,25 +7731,25 @@
         <v>1.2</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F68" s="18" t="n">
         <f aca="false">B68*C68*D68</f>
         <v>1.2</v>
       </c>
       <c r="G68" s="12" t="s">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>323</v>
+        <v>416</v>
       </c>
       <c r="I68" s="14" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B70" s="7"/>
       <c r="C70" s="7"/>
@@ -7394,12 +7760,14 @@
         <v>1.4925</v>
       </c>
       <c r="G70" s="7"/>
-      <c r="H70" s="7"/>
+      <c r="H70" s="7" t="s">
+        <v>417</v>
+      </c>
       <c r="I70" s="7"/>
     </row>
     <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>347</v>
+        <v>418</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>1</v>
@@ -7419,15 +7787,15 @@
       </c>
       <c r="G71" s="2"/>
       <c r="H71" s="2" t="s">
-        <v>328</v>
+        <v>371</v>
       </c>
       <c r="I71" s="17" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="12" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="B72" s="12" t="n">
         <v>1</v>
@@ -7439,25 +7807,25 @@
         <v>1.2</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F72" s="18" t="n">
         <f aca="false">B72*C72*D72</f>
         <v>1.2</v>
       </c>
       <c r="G72" s="12" t="s">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="H72" s="12" t="s">
-        <v>323</v>
+        <v>419</v>
       </c>
       <c r="I72" s="14" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
@@ -7468,34 +7836,36 @@
         <v>1.2</v>
       </c>
       <c r="G74" s="7"/>
-      <c r="H74" s="7"/>
+      <c r="H74" s="7" t="s">
+        <v>420</v>
+      </c>
       <c r="I74" s="7"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>348</v>
+        <v>421</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D75" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E75" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
       <c r="I75" s="17" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="B76" s="12" t="n">
         <v>1</v>
@@ -7507,25 +7877,25 @@
         <v>1.2</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F76" s="18" t="n">
         <f aca="false">B76*C76*D76</f>
         <v>1.2</v>
       </c>
       <c r="G76" s="12" t="s">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="H76" s="12" t="s">
-        <v>323</v>
+        <v>422</v>
       </c>
       <c r="I76" s="14" t="s">
-        <v>324</v>
+        <v>364</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
@@ -7536,34 +7906,36 @@
         <v>1.2</v>
       </c>
       <c r="G78" s="7"/>
-      <c r="H78" s="7"/>
+      <c r="H78" s="7" t="s">
+        <v>423</v>
+      </c>
       <c r="I78" s="7"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>349</v>
+        <v>424</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C79" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D79" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E79" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
       <c r="I79" s="17" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="B80" s="12" t="n">
         <v>1</v>
@@ -7575,25 +7947,25 @@
         <v>1.2</v>
       </c>
       <c r="E80" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F80" s="18" t="n">
         <f aca="false">B80*C80*D80</f>
         <v>1.2</v>
       </c>
       <c r="G80" s="12" t="s">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="H80" s="12" t="s">
-        <v>323</v>
+        <v>425</v>
       </c>
       <c r="I80" s="14" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
@@ -7604,12 +7976,14 @@
         <v>6</v>
       </c>
       <c r="G82" s="7"/>
-      <c r="H82" s="7"/>
+      <c r="H82" s="7" t="s">
+        <v>426</v>
+      </c>
       <c r="I82" s="7"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2" t="s">
-        <v>258</v>
+        <v>283</v>
       </c>
       <c r="B83" s="2" t="n">
         <v>2</v>
@@ -7629,15 +8003,15 @@
       </c>
       <c r="G83" s="2"/>
       <c r="H83" s="2" t="s">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="I83" s="17" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="12" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="B84" s="12" t="n">
         <v>2</v>
@@ -7649,25 +8023,25 @@
         <v>1.2</v>
       </c>
       <c r="E84" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F84" s="18" t="n">
         <f aca="false">B84*C84*D84</f>
         <v>2.4</v>
       </c>
       <c r="G84" s="12" t="s">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="H84" s="12" t="s">
-        <v>323</v>
+        <v>427</v>
       </c>
       <c r="I84" s="14" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
@@ -7678,34 +8052,36 @@
         <v>1.2</v>
       </c>
       <c r="G86" s="7"/>
-      <c r="H86" s="7"/>
+      <c r="H86" s="7" t="s">
+        <v>428</v>
+      </c>
       <c r="I86" s="7"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
-        <v>350</v>
+        <v>429</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C87" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D87" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E87" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
       <c r="I87" s="17" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="12" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="B88" s="12" t="n">
         <v>1</v>
@@ -7717,25 +8093,25 @@
         <v>1.2</v>
       </c>
       <c r="E88" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F88" s="18" t="n">
         <f aca="false">B88*C88*D88</f>
         <v>1.2</v>
       </c>
       <c r="G88" s="12" t="s">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="H88" s="12" t="s">
-        <v>323</v>
+        <v>430</v>
       </c>
       <c r="I88" s="14" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B90" s="7"/>
       <c r="C90" s="7"/>
@@ -7746,34 +8122,36 @@
         <v>1.2</v>
       </c>
       <c r="G90" s="7"/>
-      <c r="H90" s="7"/>
+      <c r="H90" s="7" t="s">
+        <v>431</v>
+      </c>
       <c r="I90" s="7"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
-        <v>351</v>
+        <v>432</v>
       </c>
       <c r="B91" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C91" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D91" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E91" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
       <c r="I91" s="17" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="12" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="B92" s="12" t="n">
         <v>1</v>
@@ -7785,25 +8163,25 @@
         <v>1.2</v>
       </c>
       <c r="E92" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F92" s="18" t="n">
         <f aca="false">B92*C92*D92</f>
         <v>1.2</v>
       </c>
       <c r="G92" s="12" t="s">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="H92" s="12" t="s">
-        <v>323</v>
+        <v>433</v>
       </c>
       <c r="I92" s="14" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B94" s="7"/>
       <c r="C94" s="7"/>
@@ -7814,34 +8192,36 @@
         <v>1.2</v>
       </c>
       <c r="G94" s="7"/>
-      <c r="H94" s="7"/>
+      <c r="H94" s="7" t="s">
+        <v>434</v>
+      </c>
       <c r="I94" s="7"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>352</v>
+        <v>435</v>
       </c>
       <c r="B95" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C95" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D95" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E95" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
       <c r="I95" s="17" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="12" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="B96" s="12" t="n">
         <v>1</v>
@@ -7853,25 +8233,25 @@
         <v>1.2</v>
       </c>
       <c r="E96" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F96" s="18" t="n">
         <f aca="false">B96*C96*D96</f>
         <v>1.2</v>
       </c>
       <c r="G96" s="12" t="s">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="H96" s="12" t="s">
-        <v>323</v>
+        <v>436</v>
       </c>
       <c r="I96" s="14" t="s">
-        <v>324</v>
+        <v>364</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
@@ -7885,9 +8265,9 @@
       <c r="H98" s="7"/>
       <c r="I98" s="7"/>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
-        <v>353</v>
+        <v>437</v>
       </c>
       <c r="B99" s="2" t="n">
         <v>10</v>
@@ -7899,25 +8279,25 @@
         <v>1.2</v>
       </c>
       <c r="E99" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F99" s="8" t="n">
         <f aca="false">B99*C99*D99</f>
         <v>12</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>354</v>
+        <v>438</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>355</v>
+        <v>439</v>
       </c>
       <c r="I99" s="17" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="12" t="s">
-        <v>356</v>
+        <v>440</v>
       </c>
       <c r="B100" s="12" t="n">
         <v>10</v>
@@ -7929,20 +8309,20 @@
         <v>1.2</v>
       </c>
       <c r="E100" s="14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F100" s="18" t="n">
         <f aca="false">B100*C100*D100</f>
         <v>12</v>
       </c>
       <c r="G100" s="12" t="s">
-        <v>354</v>
+        <v>438</v>
       </c>
       <c r="H100" s="12" t="s">
-        <v>357</v>
+        <v>441</v>
       </c>
       <c r="I100" s="14" t="s">
-        <v>324</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -7977,12 +8357,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>358</v>
+        <v>442</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="19" t="s">
-        <v>359</v>
+        <v>443</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -7999,48 +8379,48 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>360</v>
+        <v>444</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>361</v>
+        <v>445</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>362</v>
+        <v>446</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>363</v>
+        <v>447</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>364</v>
+        <v>448</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>365</v>
+        <v>449</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>366</v>
+        <v>450</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>367</v>
+        <v>451</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>368</v>
+        <v>452</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>369</v>
+        <v>453</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>370</v>
+        <v>454</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>371</v>
+        <v>455</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>372</v>
+        <v>456</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -8057,19 +8437,19 @@
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>373</v>
+        <v>457</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>374</v>
+        <v>458</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>375</v>
+        <v>459</v>
       </c>
       <c r="D6" s="20" t="n">
         <v>90</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>376</v>
+        <v>460</v>
       </c>
       <c r="F6" s="20" t="n">
         <v>0</v>
@@ -8081,7 +8461,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>377</v>
+        <v>461</v>
       </c>
       <c r="J6" s="8" t="n">
         <v>0</v>
@@ -8097,19 +8477,19 @@
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>378</v>
+        <v>462</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>379</v>
+        <v>463</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>380</v>
+        <v>464</v>
       </c>
       <c r="D7" s="20" t="n">
         <v>1505</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>381</v>
+        <v>465</v>
       </c>
       <c r="F7" s="20" t="n">
         <v>15</v>
@@ -8121,7 +8501,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>382</v>
+        <v>466</v>
       </c>
       <c r="J7" s="8" t="n">
         <v>5.32</v>
@@ -8137,19 +8517,19 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>383</v>
+        <v>467</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>384</v>
+        <v>468</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>385</v>
+        <v>469</v>
       </c>
       <c r="D8" s="20" t="n">
         <v>607</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>386</v>
+        <v>470</v>
       </c>
       <c r="F8" s="20" t="n">
         <v>20</v>
@@ -8161,7 +8541,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>382</v>
+        <v>466</v>
       </c>
       <c r="J8" s="8" t="n">
         <v>11.08</v>
@@ -8177,19 +8557,19 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>387</v>
+        <v>471</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>388</v>
+        <v>472</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>389</v>
+        <v>473</v>
       </c>
       <c r="D9" s="20" t="n">
         <v>405</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>386</v>
+        <v>470</v>
       </c>
       <c r="F9" s="20" t="n">
         <v>10</v>
@@ -8201,7 +8581,7 @@
         <v>2</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>390</v>
+        <v>474</v>
       </c>
       <c r="J9" s="8" t="n">
         <v>6.76</v>
@@ -8214,24 +8594,24 @@
         <v>6.76</v>
       </c>
       <c r="M9" s="17" t="s">
-        <v>391</v>
+        <v>475</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>392</v>
+        <v>476</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>393</v>
+        <v>477</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>394</v>
+        <v>478</v>
       </c>
       <c r="D10" s="20" t="n">
         <v>6609</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>395</v>
+        <v>479</v>
       </c>
       <c r="F10" s="20" t="n">
         <v>65</v>
@@ -8243,7 +8623,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>382</v>
+        <v>466</v>
       </c>
       <c r="J10" s="8" t="n">
         <v>11.38</v>
@@ -8259,19 +8639,19 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>396</v>
+        <v>480</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>397</v>
+        <v>481</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>398</v>
+        <v>482</v>
       </c>
       <c r="D11" s="20" t="n">
         <v>6765</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>395</v>
+        <v>479</v>
       </c>
       <c r="F11" s="20" t="n">
         <v>80</v>
@@ -8283,7 +8663,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>382</v>
+        <v>466</v>
       </c>
       <c r="J11" s="8" t="n">
         <v>12.31</v>
@@ -8299,19 +8679,19 @@
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>399</v>
+        <v>483</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>400</v>
+        <v>484</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>401</v>
+        <v>485</v>
       </c>
       <c r="D12" s="20" t="n">
         <v>201</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>402</v>
+        <v>486</v>
       </c>
       <c r="F12" s="20" t="n">
         <v>0</v>
@@ -8323,7 +8703,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>377</v>
+        <v>461</v>
       </c>
       <c r="J12" s="8" t="n">
         <v>0</v>
@@ -8339,19 +8719,19 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>403</v>
+        <v>487</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>404</v>
+        <v>488</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>405</v>
+        <v>489</v>
       </c>
       <c r="D13" s="20" t="n">
         <v>407</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>406</v>
+        <v>490</v>
       </c>
       <c r="F13" s="20" t="n">
         <v>9</v>
@@ -8363,7 +8743,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>382</v>
+        <v>466</v>
       </c>
       <c r="J13" s="8" t="n">
         <v>2.44</v>
@@ -8379,19 +8759,19 @@
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>407</v>
+        <v>491</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>408</v>
+        <v>492</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>409</v>
+        <v>493</v>
       </c>
       <c r="D14" s="20" t="n">
         <v>315</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>410</v>
+        <v>494</v>
       </c>
       <c r="F14" s="20" t="n">
         <v>3</v>
@@ -8403,7 +8783,7 @@
         <v>2</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>411</v>
+        <v>495</v>
       </c>
       <c r="J14" s="8" t="n">
         <v>2</v>
@@ -8416,24 +8796,24 @@
         <v>1</v>
       </c>
       <c r="M14" s="17" t="s">
-        <v>412</v>
+        <v>496</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>413</v>
+        <v>497</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>414</v>
+        <v>498</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>405</v>
+        <v>489</v>
       </c>
       <c r="D15" s="20" t="n">
         <v>691</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>386</v>
+        <v>470</v>
       </c>
       <c r="F15" s="20" t="n">
         <v>21</v>
@@ -8445,7 +8825,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>382</v>
+        <v>466</v>
       </c>
       <c r="J15" s="8" t="n">
         <v>11.08</v>
@@ -8461,19 +8841,19 @@
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>415</v>
+        <v>499</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>416</v>
+        <v>500</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>417</v>
+        <v>501</v>
       </c>
       <c r="D16" s="20" t="n">
         <v>371</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>410</v>
+        <v>494</v>
       </c>
       <c r="F16" s="20" t="n">
         <v>11</v>
@@ -8485,7 +8865,7 @@
         <v>5</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>418</v>
+        <v>502</v>
       </c>
       <c r="J16" s="8" t="n">
         <v>5</v>
@@ -8498,24 +8878,24 @@
         <v>5</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>419</v>
+        <v>503</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>420</v>
+        <v>504</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>421</v>
+        <v>505</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>422</v>
+        <v>506</v>
       </c>
       <c r="D17" s="20" t="n">
         <v>346</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>410</v>
+        <v>494</v>
       </c>
       <c r="F17" s="20" t="n">
         <v>5</v>
@@ -8527,7 +8907,7 @@
         <v>3</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>423</v>
+        <v>507</v>
       </c>
       <c r="J17" s="8" t="n">
         <v>3</v>
@@ -8540,24 +8920,24 @@
         <v>3</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>419</v>
+        <v>503</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>424</v>
+        <v>508</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>425</v>
+        <v>509</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>426</v>
+        <v>510</v>
       </c>
       <c r="D18" s="20" t="n">
         <v>336</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>410</v>
+        <v>494</v>
       </c>
       <c r="F18" s="20" t="n">
         <v>6</v>
@@ -8569,7 +8949,7 @@
         <v>3</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>427</v>
+        <v>511</v>
       </c>
       <c r="J18" s="8" t="n">
         <v>3</v>
@@ -8582,24 +8962,24 @@
         <v>3</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>419</v>
+        <v>503</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>428</v>
+        <v>512</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>429</v>
+        <v>513</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>430</v>
+        <v>514</v>
       </c>
       <c r="D19" s="20" t="n">
         <v>488</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>386</v>
+        <v>470</v>
       </c>
       <c r="F19" s="20" t="n">
         <v>7</v>
@@ -8611,7 +8991,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>382</v>
+        <v>466</v>
       </c>
       <c r="J19" s="8" t="n">
         <v>3.88</v>
@@ -8627,19 +9007,19 @@
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>431</v>
+        <v>515</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>432</v>
+        <v>516</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>433</v>
+        <v>517</v>
       </c>
       <c r="D20" s="20" t="n">
         <v>421</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>386</v>
+        <v>470</v>
       </c>
       <c r="F20" s="20" t="n">
         <v>5</v>
@@ -8651,7 +9031,7 @@
         <v>2</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>434</v>
+        <v>518</v>
       </c>
       <c r="J20" s="8" t="n">
         <v>3.88</v>
@@ -8664,24 +9044,24 @@
         <v>3.88</v>
       </c>
       <c r="M20" s="17" t="s">
-        <v>391</v>
+        <v>475</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>435</v>
+        <v>519</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>436</v>
+        <v>520</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>437</v>
+        <v>521</v>
       </c>
       <c r="D21" s="20" t="n">
         <v>330</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>386</v>
+        <v>470</v>
       </c>
       <c r="F21" s="20" t="n">
         <v>11</v>
@@ -8693,7 +9073,7 @@
         <v>2</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>434</v>
+        <v>518</v>
       </c>
       <c r="J21" s="8" t="n">
         <v>6.76</v>
@@ -8706,24 +9086,24 @@
         <v>6.76</v>
       </c>
       <c r="M21" s="17" t="s">
-        <v>391</v>
+        <v>475</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>438</v>
+        <v>522</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>439</v>
+        <v>523</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>440</v>
+        <v>524</v>
       </c>
       <c r="D22" s="20" t="n">
         <v>183</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>386</v>
+        <v>470</v>
       </c>
       <c r="F22" s="20" t="n">
         <v>9</v>
@@ -8735,7 +9115,7 @@
         <v>1</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>382</v>
+        <v>466</v>
       </c>
       <c r="J22" s="8" t="n">
         <v>5.32</v>
@@ -8751,19 +9131,19 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>441</v>
+        <v>525</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>442</v>
+        <v>526</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>443</v>
+        <v>527</v>
       </c>
       <c r="D23" s="20" t="n">
         <v>168</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>386</v>
+        <v>470</v>
       </c>
       <c r="F23" s="20" t="n">
         <v>7</v>
@@ -8775,7 +9155,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>382</v>
+        <v>466</v>
       </c>
       <c r="J23" s="8" t="n">
         <v>5.32</v>
@@ -8791,19 +9171,19 @@
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>444</v>
+        <v>528</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>445</v>
+        <v>529</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>446</v>
+        <v>530</v>
       </c>
       <c r="D24" s="20" t="n">
         <v>161</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>386</v>
+        <v>470</v>
       </c>
       <c r="F24" s="20" t="n">
         <v>3</v>
@@ -8815,7 +9195,7 @@
         <v>1</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>382</v>
+        <v>466</v>
       </c>
       <c r="J24" s="8" t="n">
         <v>2.44</v>
@@ -8831,19 +9211,19 @@
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>447</v>
+        <v>531</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>448</v>
+        <v>532</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>449</v>
+        <v>533</v>
       </c>
       <c r="D25" s="20" t="n">
         <v>241</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>386</v>
+        <v>470</v>
       </c>
       <c r="F25" s="20" t="n">
         <v>8</v>
@@ -8855,7 +9235,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>382</v>
+        <v>466</v>
       </c>
       <c r="J25" s="8" t="n">
         <v>5.32</v>
@@ -8871,19 +9251,19 @@
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>450</v>
+        <v>534</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>451</v>
+        <v>535</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>433</v>
+        <v>517</v>
       </c>
       <c r="D26" s="20" t="n">
         <v>161</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>410</v>
+        <v>494</v>
       </c>
       <c r="F26" s="20" t="n">
         <v>3</v>
@@ -8895,7 +9275,7 @@
         <v>2</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>411</v>
+        <v>495</v>
       </c>
       <c r="J26" s="8" t="n">
         <v>2</v>
@@ -8908,12 +9288,12 @@
         <v>1</v>
       </c>
       <c r="M26" s="17" t="s">
-        <v>412</v>
+        <v>496</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>452</v>
+        <v>536</v>
       </c>
       <c r="F27" s="21" t="n">
         <f aca="false">SUM(F6:F26)</f>
@@ -8942,12 +9322,12 @@
     </row>
     <row r="28" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="22" t="s">
-        <v>453</v>
+        <v>537</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -8964,22 +9344,22 @@
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>454</v>
+        <v>538</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>455</v>
+        <v>539</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>456</v>
+        <v>540</v>
       </c>
       <c r="D31" s="20" t="n">
         <v>52</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>457</v>
+        <v>541</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>458</v>
+        <v>542</v>
       </c>
       <c r="J31" s="8" t="n">
         <v>7.36</v>
@@ -8991,22 +9371,22 @@
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>383</v>
+        <v>467</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>459</v>
+        <v>543</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>460</v>
+        <v>544</v>
       </c>
       <c r="D32" s="20" t="n">
         <v>2</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>461</v>
+        <v>545</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>462</v>
+        <v>546</v>
       </c>
       <c r="J32" s="8" t="n">
         <v>0.49</v>
@@ -9018,22 +9398,22 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>387</v>
+        <v>471</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>463</v>
+        <v>547</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>464</v>
+        <v>548</v>
       </c>
       <c r="D33" s="20" t="n">
         <v>11</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>465</v>
+        <v>549</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>466</v>
+        <v>550</v>
       </c>
       <c r="J33" s="8" t="n">
         <v>3.07</v>
@@ -9045,22 +9425,22 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>467</v>
+        <v>551</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>468</v>
+        <v>552</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>469</v>
+        <v>553</v>
       </c>
       <c r="D34" s="20" t="n">
         <v>13</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>470</v>
+        <v>554</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>471</v>
+        <v>555</v>
       </c>
       <c r="J34" s="8" t="n">
         <v>0.66</v>
@@ -9072,22 +9452,22 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>472</v>
+        <v>556</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>473</v>
+        <v>557</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>474</v>
+        <v>558</v>
       </c>
       <c r="D35" s="20" t="n">
         <v>1</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>475</v>
+        <v>559</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>476</v>
+        <v>560</v>
       </c>
       <c r="J35" s="8" t="n">
         <v>0.25</v>
@@ -9099,22 +9479,22 @@
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>477</v>
+        <v>561</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>478</v>
+        <v>562</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>479</v>
+        <v>563</v>
       </c>
       <c r="D36" s="20" t="n">
         <v>29</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>480</v>
+        <v>564</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>481</v>
+        <v>565</v>
       </c>
       <c r="J36" s="8" t="n">
         <v>17.71</v>
@@ -9126,22 +9506,22 @@
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>482</v>
+        <v>566</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>483</v>
+        <v>567</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>484</v>
+        <v>568</v>
       </c>
       <c r="D37" s="20" t="n">
         <v>29</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>485</v>
+        <v>569</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>486</v>
+        <v>570</v>
       </c>
       <c r="J37" s="8" t="n">
         <v>17.71</v>
@@ -9153,7 +9533,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>487</v>
+        <v>571</v>
       </c>
       <c r="J38" s="10" t="n">
         <f aca="false">SUM(J31:J37)</f>
@@ -9166,12 +9546,12 @@
     </row>
     <row r="39" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="22" t="s">
-        <v>488</v>
+        <v>572</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
@@ -9188,25 +9568,25 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>489</v>
+        <v>573</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>490</v>
+        <v>574</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>491</v>
+        <v>575</v>
       </c>
       <c r="D42" s="20" t="n">
         <v>238</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>492</v>
+        <v>576</v>
       </c>
       <c r="F42" s="20" t="n">
         <v>25</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>493</v>
+        <v>577</v>
       </c>
       <c r="J42" s="8" t="n">
         <v>60</v>
@@ -9219,25 +9599,25 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>494</v>
+        <v>578</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>495</v>
+        <v>579</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>494</v>
+        <v>578</v>
       </c>
       <c r="D43" s="20" t="n">
         <v>271</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>496</v>
+        <v>580</v>
       </c>
       <c r="F43" s="20" t="n">
         <v>10</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>493</v>
+        <v>577</v>
       </c>
       <c r="J43" s="8" t="n">
         <v>24</v>
@@ -9250,25 +9630,25 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>497</v>
+        <v>581</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>498</v>
+        <v>582</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>497</v>
+        <v>581</v>
       </c>
       <c r="D44" s="20" t="n">
         <v>271</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>496</v>
+        <v>580</v>
       </c>
       <c r="F44" s="20" t="n">
         <v>10</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>493</v>
+        <v>577</v>
       </c>
       <c r="J44" s="8" t="n">
         <v>24</v>
@@ -9281,7 +9661,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>499</v>
+        <v>583</v>
       </c>
       <c r="J45" s="10" t="n">
         <f aca="false">SUM(J42:J44)</f>
@@ -9328,43 +9708,43 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>500</v>
+        <v>584</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>501</v>
+        <v>585</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>502</v>
+        <v>586</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>503</v>
+        <v>587</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>504</v>
+        <v>588</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>505</v>
+        <v>589</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>506</v>
+        <v>590</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>507</v>
+        <v>591</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>508</v>
+        <v>592</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>509</v>
+        <v>593</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1200</v>
@@ -9376,21 +9756,21 @@
         <v>2000</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>510</v>
+        <v>594</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>511</v>
+        <v>595</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>512</v>
+        <v>596</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>513</v>
+        <v>597</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>514</v>
+        <v>598</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>1200</v>
@@ -9402,21 +9782,21 @@
         <v>40</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>285</v>
+        <v>313</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>515</v>
+        <v>599</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>516</v>
+        <v>600</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>517</v>
+        <v>601</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>518</v>
+        <v>602</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>600</v>
@@ -9428,21 +9808,21 @@
         <v>300</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>285</v>
+        <v>313</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>519</v>
+        <v>603</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>520</v>
+        <v>604</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>522</v>
+        <v>606</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1300</v>
@@ -9451,24 +9831,24 @@
         <v>700</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>523</v>
+        <v>607</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>524</v>
+        <v>608</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>525</v>
+        <v>609</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>526</v>
+        <v>610</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>527</v>
+        <v>611</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>1300</v>
@@ -9477,24 +9857,24 @@
         <v>700</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>528</v>
+        <v>612</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>529</v>
+        <v>613</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>530</v>
+        <v>614</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>532</v>
+        <v>616</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>1200</v>
@@ -9503,24 +9883,24 @@
         <v>600</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>533</v>
+        <v>617</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>534</v>
+        <v>618</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>535</v>
+        <v>619</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>536</v>
+        <v>620</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>537</v>
+        <v>621</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>2700</v>
@@ -9529,24 +9909,24 @@
         <v>1200</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>523</v>
+        <v>607</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>538</v>
+        <v>622</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>539</v>
+        <v>623</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>541</v>
+        <v>625</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>1200</v>
@@ -9558,21 +9938,21 @@
         <v>1045</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>542</v>
+        <v>626</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>529</v>
+        <v>613</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>543</v>
+        <v>627</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>545</v>
+        <v>629</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>1200</v>
@@ -9581,67 +9961,67 @@
         <v>1000</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>546</v>
+        <v>630</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>547</v>
+        <v>631</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>548</v>
+        <v>632</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>549</v>
+        <v>633</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>550</v>
+        <v>634</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>551</v>
+        <v>635</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>552</v>
+        <v>636</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>553</v>
+        <v>637</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>554</v>
+        <v>638</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>555</v>
+        <v>639</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>556</v>
+        <v>640</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>557</v>
+        <v>641</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>558</v>
+        <v>642</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>559</v>
+        <v>643</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>560</v>
+        <v>644</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>561</v>
+        <v>645</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>562</v>
+        <v>646</v>
       </c>
       <c r="D17" s="20" t="n">
         <v>254</v>
@@ -9653,7 +10033,7 @@
         <v>229</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>563</v>
+        <v>647</v>
       </c>
       <c r="H17" s="20" t="n">
         <v>1270</v>
@@ -9665,10 +10045,10 @@
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
-        <v>564</v>
+        <v>648</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>565</v>
+        <v>649</v>
       </c>
       <c r="D18" s="20" t="n">
         <v>147</v>
@@ -9680,7 +10060,7 @@
         <v>184</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>566</v>
+        <v>650</v>
       </c>
       <c r="H18" s="20" t="n">
         <v>735</v>
@@ -9692,10 +10072,10 @@
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
-        <v>567</v>
+        <v>651</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>568</v>
+        <v>652</v>
       </c>
       <c r="D19" s="20" t="n">
         <v>76</v>
@@ -9707,7 +10087,7 @@
         <v>122</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>569</v>
+        <v>653</v>
       </c>
       <c r="H19" s="20" t="n">
         <v>456</v>
@@ -9719,10 +10099,10 @@
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12"/>
       <c r="B20" s="12" t="s">
-        <v>570</v>
+        <v>654</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>571</v>
+        <v>655</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>34</v>
@@ -9734,7 +10114,7 @@
         <v>68</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>572</v>
+        <v>656</v>
       </c>
       <c r="H20" s="24" t="n">
         <v>272</v>
@@ -9745,13 +10125,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>573</v>
+        <v>657</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>561</v>
+        <v>645</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>574</v>
+        <v>658</v>
       </c>
       <c r="D21" s="20" t="n">
         <v>105</v>
@@ -9763,7 +10143,7 @@
         <v>297.5</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>575</v>
+        <v>659</v>
       </c>
       <c r="H21" s="20" t="n">
         <v>420</v>
@@ -9775,10 +10155,10 @@
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
-        <v>564</v>
+        <v>648</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>576</v>
+        <v>660</v>
       </c>
       <c r="D22" s="20" t="n">
         <v>36</v>
@@ -9790,7 +10170,7 @@
         <v>333</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>577</v>
+        <v>661</v>
       </c>
       <c r="H22" s="20" t="n">
         <v>144</v>
@@ -9802,10 +10182,10 @@
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
-        <v>567</v>
+        <v>651</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>578</v>
+        <v>662</v>
       </c>
       <c r="D23" s="20" t="n">
         <v>21</v>
@@ -9817,7 +10197,7 @@
         <v>414</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>579</v>
+        <v>663</v>
       </c>
       <c r="H23" s="20" t="n">
         <v>63</v>
@@ -9829,10 +10209,10 @@
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12"/>
       <c r="B24" s="12" t="s">
-        <v>570</v>
+        <v>654</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>580</v>
+        <v>664</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>18</v>
@@ -9844,7 +10224,7 @@
         <v>582</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>581</v>
+        <v>665</v>
       </c>
       <c r="H24" s="24" t="n">
         <v>54</v>
@@ -9855,13 +10235,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>582</v>
+        <v>666</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>561</v>
+        <v>645</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>574</v>
+        <v>658</v>
       </c>
       <c r="D25" s="20" t="n">
         <v>105</v>
@@ -9873,7 +10253,7 @@
         <v>297.5</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>575</v>
+        <v>659</v>
       </c>
       <c r="H25" s="20" t="n">
         <v>420</v>
@@ -9885,10 +10265,10 @@
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
       <c r="B26" s="2" t="s">
-        <v>564</v>
+        <v>648</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>576</v>
+        <v>660</v>
       </c>
       <c r="D26" s="20" t="n">
         <v>36</v>
@@ -9900,7 +10280,7 @@
         <v>333</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>577</v>
+        <v>661</v>
       </c>
       <c r="H26" s="20" t="n">
         <v>144</v>
@@ -9912,10 +10292,10 @@
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
-        <v>567</v>
+        <v>651</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>578</v>
+        <v>662</v>
       </c>
       <c r="D27" s="20" t="n">
         <v>21</v>
@@ -9927,7 +10307,7 @@
         <v>414</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>579</v>
+        <v>663</v>
       </c>
       <c r="H27" s="20" t="n">
         <v>63</v>
@@ -9939,10 +10319,10 @@
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12"/>
       <c r="B28" s="12" t="s">
-        <v>570</v>
+        <v>654</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>580</v>
+        <v>664</v>
       </c>
       <c r="D28" s="24" t="n">
         <v>18</v>
@@ -9954,7 +10334,7 @@
         <v>582</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>581</v>
+        <v>665</v>
       </c>
       <c r="H28" s="24" t="n">
         <v>54</v>
@@ -9965,13 +10345,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>583</v>
+        <v>667</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>561</v>
+        <v>645</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>584</v>
+        <v>668</v>
       </c>
       <c r="D29" s="20" t="n">
         <v>72</v>
@@ -9983,7 +10363,7 @@
         <v>390</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>585</v>
+        <v>669</v>
       </c>
       <c r="H29" s="20" t="n">
         <v>216</v>
@@ -9995,10 +10375,10 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
-        <v>564</v>
+        <v>648</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>586</v>
+        <v>670</v>
       </c>
       <c r="D30" s="20" t="n">
         <v>34</v>
@@ -10010,7 +10390,7 @@
         <v>415</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>587</v>
+        <v>671</v>
       </c>
       <c r="H30" s="20" t="n">
         <v>102</v>
@@ -10022,10 +10402,10 @@
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
-        <v>567</v>
+        <v>651</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>588</v>
+        <v>672</v>
       </c>
       <c r="D31" s="20" t="n">
         <v>18</v>
@@ -10037,7 +10417,7 @@
         <v>495</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>589</v>
+        <v>673</v>
       </c>
       <c r="H31" s="20" t="n">
         <v>54</v>
@@ -10049,10 +10429,10 @@
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12"/>
       <c r="B32" s="12" t="s">
-        <v>570</v>
+        <v>654</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>590</v>
+        <v>674</v>
       </c>
       <c r="D32" s="24" t="n">
         <v>9</v>
@@ -10064,7 +10444,7 @@
         <v>665</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>591</v>
+        <v>675</v>
       </c>
       <c r="H32" s="24" t="n">
         <v>18</v>
@@ -10073,18 +10453,18 @@
         <v>27</v>
       </c>
       <c r="J32" s="17" t="s">
-        <v>592</v>
+        <v>676</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>593</v>
+        <v>677</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>561</v>
+        <v>645</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>594</v>
+        <v>678</v>
       </c>
       <c r="D33" s="20" t="n">
         <v>288</v>
@@ -10096,7 +10476,7 @@
         <v>300</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>595</v>
+        <v>679</v>
       </c>
       <c r="H33" s="20" t="n">
         <v>3456</v>
@@ -10108,10 +10488,10 @@
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2"/>
       <c r="B34" s="2" t="s">
-        <v>564</v>
+        <v>648</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>596</v>
+        <v>680</v>
       </c>
       <c r="D34" s="20" t="n">
         <v>88</v>
@@ -10123,7 +10503,7 @@
         <v>300</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>595</v>
+        <v>679</v>
       </c>
       <c r="H34" s="20" t="n">
         <v>1056</v>
@@ -10135,10 +10515,10 @@
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2"/>
       <c r="B35" s="2" t="s">
-        <v>567</v>
+        <v>651</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>597</v>
+        <v>681</v>
       </c>
       <c r="D35" s="20" t="n">
         <v>48</v>
@@ -10150,7 +10530,7 @@
         <v>300</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>595</v>
+        <v>679</v>
       </c>
       <c r="H35" s="20" t="n">
         <v>576</v>
@@ -10162,10 +10542,10 @@
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12"/>
       <c r="B36" s="12" t="s">
-        <v>570</v>
+        <v>654</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>598</v>
+        <v>682</v>
       </c>
       <c r="D36" s="24" t="n">
         <v>27</v>
@@ -10177,7 +10557,7 @@
         <v>300</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>595</v>
+        <v>679</v>
       </c>
       <c r="H36" s="24" t="n">
         <v>324</v>
@@ -10188,13 +10568,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
-        <v>599</v>
+        <v>683</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>561</v>
+        <v>645</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>594</v>
+        <v>678</v>
       </c>
       <c r="D37" s="20" t="n">
         <v>288</v>
@@ -10206,7 +10586,7 @@
         <v>300</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>595</v>
+        <v>679</v>
       </c>
       <c r="H37" s="20" t="n">
         <v>3456</v>
@@ -10218,10 +10598,10 @@
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2"/>
       <c r="B38" s="2" t="s">
-        <v>564</v>
+        <v>648</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>600</v>
+        <v>684</v>
       </c>
       <c r="D38" s="20" t="n">
         <v>80</v>
@@ -10233,7 +10613,7 @@
         <v>300</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>595</v>
+        <v>679</v>
       </c>
       <c r="H38" s="20" t="n">
         <v>960</v>
@@ -10245,10 +10625,10 @@
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2"/>
       <c r="B39" s="2" t="s">
-        <v>567</v>
+        <v>651</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>601</v>
+        <v>685</v>
       </c>
       <c r="D39" s="20" t="n">
         <v>36</v>
@@ -10260,7 +10640,7 @@
         <v>300</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>595</v>
+        <v>679</v>
       </c>
       <c r="H39" s="20" t="n">
         <v>432</v>
@@ -10272,10 +10652,10 @@
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12"/>
       <c r="B40" s="12" t="s">
-        <v>570</v>
+        <v>654</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>602</v>
+        <v>686</v>
       </c>
       <c r="D40" s="24" t="n">
         <v>21</v>
@@ -10287,7 +10667,7 @@
         <v>300</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>595</v>
+        <v>679</v>
       </c>
       <c r="H40" s="24" t="n">
         <v>252</v>
@@ -10298,13 +10678,13 @@
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>603</v>
+        <v>687</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>561</v>
+        <v>645</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>604</v>
+        <v>688</v>
       </c>
       <c r="D41" s="20" t="n">
         <v>100</v>
@@ -10316,7 +10696,7 @@
         <v>300</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>595</v>
+        <v>679</v>
       </c>
       <c r="H41" s="20" t="n">
         <v>1200</v>
@@ -10328,10 +10708,10 @@
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2"/>
       <c r="B42" s="2" t="s">
-        <v>564</v>
+        <v>648</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>604</v>
+        <v>688</v>
       </c>
       <c r="D42" s="20" t="n">
         <v>40</v>
@@ -10343,7 +10723,7 @@
         <v>300</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>595</v>
+        <v>679</v>
       </c>
       <c r="H42" s="20" t="n">
         <v>480</v>
@@ -10355,10 +10735,10 @@
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2"/>
       <c r="B43" s="2" t="s">
-        <v>567</v>
+        <v>651</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>604</v>
+        <v>688</v>
       </c>
       <c r="D43" s="20" t="n">
         <v>30</v>
@@ -10370,7 +10750,7 @@
         <v>300</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>595</v>
+        <v>679</v>
       </c>
       <c r="H43" s="20" t="n">
         <v>360</v>
@@ -10382,10 +10762,10 @@
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12"/>
       <c r="B44" s="12" t="s">
-        <v>570</v>
+        <v>654</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>604</v>
+        <v>688</v>
       </c>
       <c r="D44" s="24" t="n">
         <v>19</v>
@@ -10397,7 +10777,7 @@
         <v>300</v>
       </c>
       <c r="G44" s="12" t="s">
-        <v>595</v>
+        <v>679</v>
       </c>
       <c r="H44" s="24" t="n">
         <v>228</v>
@@ -10408,7 +10788,7 @@
     </row>
     <row r="46" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="22" t="s">
-        <v>605</v>
+        <v>689</v>
       </c>
     </row>
   </sheetData>

--- a/dimensiones/dimensiones_puestos.xlsx
+++ b/dimensiones/dimensiones_puestos.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="698">
   <si>
     <t xml:space="preserve">RESUMEN — huella de lo que va en cada puesto (sin circulación)</t>
   </si>
@@ -289,31 +289,34 @@
     <t xml:space="preserve">Manuales: Balanceo-FLAMA2035 › Carga R35 (máq.) y S35 (turnos) · Carros: Carga M75 (máq.) y N75 (turnos)</t>
   </si>
   <si>
-    <t xml:space="preserve">   Guillotina 1</t>
+    <t xml:space="preserve">   Guillotina 1 Ermaksan HGS 2600-6</t>
   </si>
   <si>
     <t xml:space="preserve">Los dos</t>
   </si>
   <si>
-    <t xml:space="preserve">equivalente: guillotina hidráulica 6 × 3.200 Yawei HSS 6-3200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cotización Molinari HG 6 × 3200; medidas: manmonthly.com.au, Yawei HSS 6-3200 (3.850 × 1.630 × 1.950 mm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Molinari no da medidas y no se encontraron en internet; la de Machcenter es una imagen. Sin el tope trasero</t>
+    <t xml:space="preserve">corte 2.600 mm, chapa hasta 6 mm, 5.000 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Máquina: Balanceo-FLAMA2035 › Lotes A22 · medidas: exapro.com y resale.info n.º 164666861 (ERMAK HGS 2600 × 6: 3.395 × 1.880 × 1.550 mm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medidas de avisos de venta del mismo modelo: confirmar con Ermaksan. Sin el tope trasero</t>
   </si>
   <si>
     <t xml:space="preserve">Manuales: Balanceo-FLAMA2035 › Carga R36 (máq.) y S36 (turnos) · Carros: Carga M75 (máq.) y N75 (turnos)</t>
   </si>
   <si>
-    <t xml:space="preserve">   Guillotina 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cotización Firesafer (sheet shearing machine); medidas: manmonthly.com.au, Yawei HSS 6-3200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Firesafer no da medidas. Sin el tope trasero</t>
+    <t xml:space="preserve">   Guillotina 2 QC12Y 6 × 2500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">corte 2.500 mm, chapa hasta 6 mm, 4.800 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Máquina: Balanceo-FLAMA2035 › Lotes A23 · medidas: goldsupplier.com/provide/p106252035.html (QC12Y-6X2500: 3.100 × 1.620 × 1.600 mm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medidas de la ficha del fabricante chino (LIWANG): confirmar con el proveedor. Sin el tope trasero</t>
   </si>
   <si>
     <t xml:space="preserve">   Mesa elevadora 2 = pulmón de franjas</t>
@@ -430,16 +433,16 @@
     <t xml:space="preserve">Balanceo-FLAMA2035 › Carga R37 (máq.) y S37 (turnos)</t>
   </si>
   <si>
-    <t xml:space="preserve">   Prensa de embutido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">equivalente: prensa de 4 columnas 300 t Y33-300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catálogo Firesafer (FS Cylinder Production), Y33-300: 1.100 × 900 × 2.100 mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las cotizaciones Shimeq PHM 300 y Firesafer Power Press no dan medidas; se toma la Y33-300 del catálogo Firesafer. Shimeq da mesa 1.800 × 1.300: confirmar</t>
+    <t xml:space="preserve">   Prensa Sangiacomo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sangiacomo T130 R CE: 130 t, mesa 1.200 × 700 mm, 10.000 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Máquina: Balanceo-FLAMA2035 › Lotes A42 · medidas: exapro.com/sp/sangiacomo-t130rce-19888 (1.600 × 1.300 × 3.320 mm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fran no dice el modelo ni el tonelaje: se toma la T130 R. Confirmar modelo</t>
   </si>
   <si>
     <t xml:space="preserve">   Desbobinador CENA TC-400</t>
@@ -2644,7 +2647,7 @@
       </c>
       <c r="B5" s="6" t="n">
         <f aca="false">Manuales!F5</f>
-        <v>10.93</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2824,7 +2827,7 @@
       </c>
       <c r="B25" s="8" t="n">
         <f aca="false">SUM(B5:B24)</f>
-        <v>113.620675</v>
+        <v>114.710675</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3193,7 +3196,7 @@
       </c>
       <c r="B70" s="6" t="n">
         <f aca="false">Compartidos!G5</f>
-        <v>6.2755</v>
+        <v>6.3826</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3202,7 +3205,7 @@
       </c>
       <c r="B71" s="6" t="n">
         <f aca="false">Compartidos!G8</f>
-        <v>10.4355</v>
+        <v>9.182</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3238,7 +3241,7 @@
       </c>
       <c r="B75" s="8" t="n">
         <f aca="false">SUM(B70:B74)</f>
-        <v>29.656</v>
+        <v>28.5096</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3247,7 +3250,7 @@
       </c>
       <c r="B77" s="9" t="n">
         <f aca="false">B25+B40+B67+B75</f>
-        <v>246.675689285714</v>
+        <v>246.619289285714</v>
       </c>
     </row>
   </sheetData>
@@ -3332,7 +3335,7 @@
       <c r="F5" s="4"/>
       <c r="G5" s="9" t="n">
         <f aca="false">SUM(G6:G6)</f>
-        <v>6.2755</v>
+        <v>6.3826</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4" t="s">
@@ -3351,17 +3354,17 @@
         <v>1</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>3.85</v>
+        <v>3.395</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="G6" s="11" t="n">
         <f aca="false">C6*D6*E6</f>
-        <v>6.2755</v>
+        <v>6.3826</v>
       </c>
       <c r="H6" s="10" t="s">
         <v>89</v>
@@ -3384,7 +3387,7 @@
       <c r="F8" s="4"/>
       <c r="G8" s="9" t="n">
         <f aca="false">SUM(G9:G11)</f>
-        <v>10.4355</v>
+        <v>9.182</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4" t="s">
@@ -3392,7 +3395,7 @@
       </c>
       <c r="J8" s="4"/>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>93</v>
       </c>
@@ -3403,31 +3406,31 @@
         <v>1</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="G9" s="6" t="n">
         <f aca="false">C9*D9*E9</f>
-        <v>6.2755</v>
+        <v>5.022</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>88</v>
@@ -3449,18 +3452,18 @@
         <v>3.25</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>88</v>
@@ -3475,20 +3478,20 @@
         <v>1.3</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G11" s="11" t="n">
         <f aca="false">C11*D11*E11</f>
         <v>0.91</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3506,13 +3509,13 @@
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>88</v>
@@ -3534,18 +3537,18 @@
         <v>1.875</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>88</v>
@@ -3567,10 +3570,10 @@
         <v>2.16</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J15" s="12"/>
     </row>
@@ -3589,13 +3592,13 @@
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>88</v>
@@ -3617,18 +3620,18 @@
         <v>0.76</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>88</v>
@@ -3650,18 +3653,18 @@
         <v>0.38</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>88</v>
@@ -3676,20 +3679,20 @@
         <v>1.3</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G20" s="11" t="n">
         <f aca="false">C20*D20*E20</f>
         <v>2.73</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3707,13 +3710,13 @@
       </c>
       <c r="H22" s="4"/>
       <c r="I22" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>88</v>
@@ -3735,18 +3738,18 @@
         <v>1.848</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>88</v>
@@ -3769,15 +3772,15 @@
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>88</v>
@@ -3792,20 +3795,20 @@
         <v>1.3</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G25" s="11" t="n">
         <f aca="false">C25*D25*E25</f>
         <v>2.73</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -3838,7 +3841,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3885,47 +3888,47 @@
       <c r="E5" s="4"/>
       <c r="F5" s="9" t="n">
         <f aca="false">SUM(F6:F11)</f>
-        <v>10.93</v>
+        <v>12.02</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>2.1</v>
+        <v>3.32</v>
       </c>
       <c r="F6" s="6" t="n">
         <f aca="false">B6*C6*D6</f>
-        <v>0.99</v>
+        <v>2.08</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>1</v>
@@ -3944,18 +3947,18 @@
         <v>1.2</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B8" s="5" t="n">
         <v>1</v>
@@ -3974,18 +3977,18 @@
         <v>0.44</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B9" s="5" t="n">
         <v>2</v>
@@ -3997,25 +4000,25 @@
         <v>2.7</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F9" s="6" t="n">
         <f aca="false">B9*C9*D9</f>
         <v>6.48</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>1</v>
@@ -4027,25 +4030,25 @@
         <v>1.3</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F10" s="6" t="n">
         <f aca="false">B10*C10*D10</f>
         <v>0.91</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B11" s="10" t="n">
         <v>1</v>
@@ -4057,20 +4060,20 @@
         <v>1.3</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F11" s="11" t="n">
         <f aca="false">B11*C11*D11</f>
         <v>0.91</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4087,31 +4090,31 @@
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>2</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F14" s="15"/>
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
       <c r="I14" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4128,13 +4131,13 @@
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B17" s="5" t="n">
         <v>1</v>
@@ -4153,18 +4156,18 @@
         <v>1.68</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B18" s="5" t="n">
         <v>2</v>
@@ -4183,16 +4186,16 @@
         <v>1.44</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B19" s="10" t="n">
         <v>1</v>
@@ -4204,20 +4207,20 @@
         <v>1.3</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F19" s="11" t="n">
         <f aca="false">B19*C19*D19</f>
         <v>0.91</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4234,13 +4237,13 @@
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B22" s="5" t="n">
         <v>1</v>
@@ -4259,18 +4262,18 @@
         <v>2.34</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B23" s="10" t="n">
         <v>1</v>
@@ -4282,20 +4285,20 @@
         <v>1.3</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F23" s="11" t="n">
         <f aca="false">B23*C23*D23</f>
         <v>0.91</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4312,13 +4315,13 @@
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B26" s="5" t="n">
         <v>1</v>
@@ -4337,18 +4340,18 @@
         <v>1.32</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B27" s="5" t="n">
         <v>7</v>
@@ -4367,16 +4370,16 @@
         <v>5.04</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B28" s="10" t="n">
         <v>1</v>
@@ -4388,20 +4391,20 @@
         <v>1.3</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F28" s="11" t="n">
         <f aca="false">B28*C28*D28</f>
         <v>0.91</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4418,13 +4421,13 @@
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I30" s="4"/>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B31" s="10" t="n">
         <v>1</v>
@@ -4443,13 +4446,13 @@
         <v>1.32</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4466,13 +4469,13 @@
       </c>
       <c r="G33" s="4"/>
       <c r="H33" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I33" s="4"/>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B34" s="5" t="n">
         <v>1</v>
@@ -4491,18 +4494,18 @@
         <v>1.058575</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B35" s="5" t="n">
         <v>4</v>
@@ -4521,16 +4524,16 @@
         <v>2.88</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I35" s="13"/>
     </row>
     <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B36" s="5" t="n">
         <v>2</v>
@@ -4549,16 +4552,16 @@
         <v>1.44</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I36" s="13"/>
     </row>
     <row r="37" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B37" s="10" t="n">
         <v>1</v>
@@ -4570,20 +4573,20 @@
         <v>1.3</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F37" s="11" t="n">
         <f aca="false">B37*C37*D37</f>
         <v>0.91</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4600,13 +4603,13 @@
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B40" s="5" t="n">
         <v>1</v>
@@ -4625,18 +4628,18 @@
         <v>0.84</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B41" s="10" t="n">
         <v>1</v>
@@ -4648,20 +4651,20 @@
         <v>1.3</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F41" s="11" t="n">
         <f aca="false">B41*C41*D41</f>
         <v>0.91</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I41" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4678,39 +4681,39 @@
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I43" s="4"/>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B44" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B45" s="5" t="n">
         <v>1</v>
@@ -4729,16 +4732,16 @@
         <v>0.72</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I45" s="13"/>
     </row>
     <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B46" s="5" t="n">
         <v>7</v>
@@ -4757,16 +4760,16 @@
         <v>5.04</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I46" s="13"/>
     </row>
     <row r="47" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B47" s="10" t="n">
         <v>5</v>
@@ -4778,20 +4781,20 @@
         <v>1.3</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F47" s="11" t="n">
         <f aca="false">B47*C47*D47</f>
         <v>4.55</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I47" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4808,31 +4811,31 @@
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I49" s="4"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B50" s="10" t="n">
         <v>1</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F50" s="15"/>
       <c r="G50" s="10"/>
       <c r="H50" s="10"/>
       <c r="I50" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4849,13 +4852,13 @@
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I52" s="4"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B53" s="5" t="n">
         <v>1</v>
@@ -4875,15 +4878,15 @@
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I53" s="13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B54" s="10" t="n">
         <v>1</v>
@@ -4895,20 +4898,20 @@
         <v>1.3</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F54" s="11" t="n">
         <f aca="false">B54*C54*D54</f>
         <v>0.91</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I54" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4925,31 +4928,31 @@
       </c>
       <c r="G56" s="4"/>
       <c r="H56" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I56" s="4"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B57" s="10" t="n">
         <v>1</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F57" s="15"/>
       <c r="G57" s="10"/>
       <c r="H57" s="10"/>
       <c r="I57" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4966,33 +4969,33 @@
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I59" s="4"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B60" s="10" t="n">
         <v>1</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F60" s="15"/>
       <c r="G60" s="10"/>
       <c r="H60" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I60" s="12" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5009,13 +5012,13 @@
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I62" s="4"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B63" s="5" t="n">
         <v>2</v>
@@ -5034,18 +5037,18 @@
         <v>29.28</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I63" s="13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B64" s="5" t="n">
         <v>1</v>
@@ -5064,18 +5067,18 @@
         <v>3</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I64" s="13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B65" s="5" t="n">
         <v>2</v>
@@ -5094,16 +5097,16 @@
         <v>1.44</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I65" s="13"/>
     </row>
     <row r="66" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B66" s="5" t="n">
         <v>1</v>
@@ -5115,25 +5118,25 @@
         <v>1.3</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F66" s="6" t="n">
         <f aca="false">B66*C66*D66</f>
         <v>0.91</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B67" s="10" t="n">
         <v>1</v>
@@ -5145,20 +5148,20 @@
         <v>1.3</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F67" s="11" t="n">
         <f aca="false">B67*C67*D67</f>
         <v>0.91</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I67" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5175,13 +5178,13 @@
       </c>
       <c r="G69" s="4"/>
       <c r="H69" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I69" s="4"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B70" s="5" t="n">
         <v>1</v>
@@ -5201,15 +5204,15 @@
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I70" s="13" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B71" s="5" t="n">
         <v>4</v>
@@ -5228,16 +5231,16 @@
         <v>2.88</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I71" s="13"/>
     </row>
     <row r="72" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B72" s="10" t="n">
         <v>1</v>
@@ -5249,20 +5252,20 @@
         <v>1.3</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F72" s="11" t="n">
         <f aca="false">B72*C72*D72</f>
         <v>0.91</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H72" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I72" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5279,13 +5282,13 @@
       </c>
       <c r="G74" s="4"/>
       <c r="H74" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I74" s="4"/>
     </row>
     <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B75" s="5" t="n">
         <v>1</v>
@@ -5305,13 +5308,13 @@
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I75" s="13"/>
     </row>
     <row r="76" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B76" s="5" t="n">
         <v>3</v>
@@ -5330,16 +5333,16 @@
         <v>2.16</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I76" s="13"/>
     </row>
     <row r="77" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B77" s="10" t="n">
         <v>1</v>
@@ -5351,20 +5354,20 @@
         <v>1.3</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F77" s="11" t="n">
         <f aca="false">B77*C77*D77</f>
         <v>0.91</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I77" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5381,39 +5384,39 @@
       </c>
       <c r="G79" s="4"/>
       <c r="H79" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I79" s="4"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B80" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C80" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D80" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I80" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B81" s="5" t="n">
         <v>3</v>
@@ -5432,16 +5435,16 @@
         <v>2.16</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I81" s="13"/>
     </row>
     <row r="82" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B82" s="10" t="n">
         <v>1</v>
@@ -5453,20 +5456,20 @@
         <v>1.3</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F82" s="11" t="n">
         <f aca="false">B82*C82*D82</f>
         <v>0.91</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H82" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I82" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5483,13 +5486,13 @@
       </c>
       <c r="G84" s="4"/>
       <c r="H84" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I84" s="4"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B85" s="5" t="n">
         <v>1</v>
@@ -5508,18 +5511,18 @@
         <v>1.8</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I85" s="13" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B86" s="5" t="n">
         <v>1</v>
@@ -5538,16 +5541,16 @@
         <v>0.72</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I86" s="13"/>
     </row>
     <row r="87" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B87" s="10" t="n">
         <v>1</v>
@@ -5559,20 +5562,20 @@
         <v>1.3</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F87" s="11" t="n">
         <f aca="false">B87*C87*D87</f>
         <v>0.91</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I87" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5589,13 +5592,13 @@
       </c>
       <c r="G89" s="4"/>
       <c r="H89" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I89" s="4"/>
     </row>
     <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B90" s="5" t="n">
         <v>1</v>
@@ -5614,18 +5617,18 @@
         <v>0.2925</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I90" s="13" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B91" s="5" t="n">
         <v>3</v>
@@ -5644,16 +5647,16 @@
         <v>2.16</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I91" s="13"/>
     </row>
     <row r="92" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B92" s="10" t="n">
         <v>1</v>
@@ -5665,20 +5668,20 @@
         <v>1.3</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F92" s="11" t="n">
         <f aca="false">B92*C92*D92</f>
         <v>0.91</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H92" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I92" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5695,13 +5698,13 @@
       </c>
       <c r="G94" s="4"/>
       <c r="H94" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I94" s="4"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B95" s="5" t="n">
         <v>1</v>
@@ -5720,16 +5723,16 @@
         <v>4.5</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I95" s="13"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B96" s="5" t="n">
         <v>1</v>
@@ -5749,15 +5752,15 @@
       </c>
       <c r="G96" s="5"/>
       <c r="H96" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I96" s="13" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B97" s="10" t="n">
         <v>2</v>
@@ -5776,10 +5779,10 @@
         <v>1.44</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I97" s="12"/>
     </row>
@@ -5813,7 +5816,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5864,13 +5867,13 @@
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>1</v>
@@ -5889,18 +5892,18 @@
         <v>4.0051</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B7" s="10" t="n">
         <v>1</v>
@@ -5908,17 +5911,17 @@
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
       <c r="E7" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F7" s="11" t="n">
         <f aca="false">7.3558/1.4</f>
         <v>5.25414285714286</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I7" s="12"/>
     </row>
@@ -5936,13 +5939,13 @@
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>1</v>
@@ -5961,18 +5964,18 @@
         <v>0.1504</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B11" s="5" t="n">
         <v>1</v>
@@ -5992,13 +5995,13 @@
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B12" s="10" t="n">
         <v>1</v>
@@ -6006,17 +6009,17 @@
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
       <c r="E12" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F12" s="11" t="n">
         <f aca="false">0.4939/1.4</f>
         <v>0.352785714285714</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I12" s="12"/>
     </row>
@@ -6034,13 +6037,13 @@
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B15" s="5" t="n">
         <v>1</v>
@@ -6059,16 +6062,16 @@
         <v>2.622</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I15" s="13"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B16" s="10" t="n">
         <v>1</v>
@@ -6087,13 +6090,13 @@
         <v>0.3816</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6110,35 +6113,35 @@
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B20" s="10" t="n">
         <v>1</v>
@@ -6146,17 +6149,17 @@
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
       <c r="E20" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F20" s="11" t="n">
         <f aca="false">0.6603/1.4</f>
         <v>0.471642857142857</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I20" s="12"/>
     </row>
@@ -6174,13 +6177,13 @@
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B23" s="5" t="n">
         <v>1</v>
@@ -6199,18 +6202,18 @@
         <v>0.1504</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B24" s="5" t="n">
         <v>1</v>
@@ -6230,13 +6233,13 @@
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I24" s="13"/>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B25" s="10" t="n">
         <v>1</v>
@@ -6244,17 +6247,17 @@
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F25" s="11" t="n">
         <f aca="false">3.0733/1.4</f>
         <v>2.19521428571429</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I25" s="12"/>
     </row>
@@ -6272,13 +6275,13 @@
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B28" s="5" t="n">
         <v>1</v>
@@ -6297,18 +6300,18 @@
         <v>0.1504</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>1</v>
@@ -6328,13 +6331,13 @@
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B30" s="10" t="n">
         <v>1</v>
@@ -6342,17 +6345,17 @@
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
       <c r="E30" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F30" s="11" t="n">
         <f aca="false">0.247/1.4</f>
         <v>0.176428571428571</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -6370,31 +6373,31 @@
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I32" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B33" s="10" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F33" s="15"/>
       <c r="G33" s="10"/>
       <c r="H33" s="10"/>
       <c r="I33" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6411,13 +6414,13 @@
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I35" s="4"/>
     </row>
     <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B36" s="10" t="n">
         <v>1</v>
@@ -6425,17 +6428,17 @@
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
       <c r="E36" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F36" s="11" t="n">
         <f aca="false">17.71/1.4</f>
         <v>12.65</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I36" s="12"/>
     </row>
@@ -6453,13 +6456,13 @@
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I38" s="4"/>
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B39" s="10" t="n">
         <v>1</v>
@@ -6467,17 +6470,17 @@
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
       <c r="E39" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F39" s="11" t="n">
         <f aca="false">17.71/1.4</f>
         <v>12.65</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I39" s="12"/>
     </row>
@@ -6495,13 +6498,13 @@
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="I41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B42" s="10" t="n">
         <v>1</v>
@@ -6521,7 +6524,7 @@
       </c>
       <c r="G42" s="10"/>
       <c r="H42" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I42" s="12"/>
     </row>
@@ -6539,31 +6542,31 @@
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I44" s="4"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B45" s="10" t="n">
         <v>1</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F45" s="15"/>
       <c r="G45" s="10"/>
       <c r="H45" s="10"/>
       <c r="I45" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6580,31 +6583,31 @@
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I47" s="4"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B48" s="10" t="n">
         <v>1</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F48" s="15"/>
       <c r="G48" s="10"/>
       <c r="H48" s="10"/>
       <c r="I48" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -6637,7 +6640,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6688,35 +6691,35 @@
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B7" s="10" t="n">
         <v>2</v>
@@ -6728,20 +6731,20 @@
         <v>1.2</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F7" s="11" t="n">
         <f aca="false">B7*C7*D7</f>
         <v>2.4</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6758,35 +6761,35 @@
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
       <c r="I10" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B11" s="10" t="n">
         <v>1</v>
@@ -6798,20 +6801,20 @@
         <v>1.2</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F11" s="11" t="n">
         <f aca="false">B11*C11*D11</f>
         <v>1.2</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6828,13 +6831,13 @@
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="I13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B14" s="5" t="n">
         <v>1</v>
@@ -6853,18 +6856,18 @@
         <v>0.32</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B15" s="10" t="n">
         <v>1</v>
@@ -6876,20 +6879,20 @@
         <v>1.2</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F15" s="11" t="n">
         <f aca="false">B15*C15*D15</f>
         <v>1.2</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6906,35 +6909,35 @@
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B18" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
       <c r="I18" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B19" s="10" t="n">
         <v>1</v>
@@ -6946,20 +6949,20 @@
         <v>1.2</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F19" s="11" t="n">
         <f aca="false">B19*C19*D19</f>
         <v>1.2</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6976,13 +6979,13 @@
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B22" s="5" t="n">
         <v>1</v>
@@ -7002,15 +7005,15 @@
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B23" s="10" t="n">
         <v>1</v>
@@ -7022,20 +7025,20 @@
         <v>1.2</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F23" s="11" t="n">
         <f aca="false">B23*C23*D23</f>
         <v>1.2</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7052,13 +7055,13 @@
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B26" s="5" t="n">
         <v>1</v>
@@ -7078,15 +7081,15 @@
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B27" s="10" t="n">
         <v>1</v>
@@ -7098,20 +7101,20 @@
         <v>1.2</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F27" s="11" t="n">
         <f aca="false">B27*C27*D27</f>
         <v>1.2</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7128,37 +7131,37 @@
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B31" s="10" t="n">
         <v>1</v>
@@ -7170,20 +7173,20 @@
         <v>1.2</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F31" s="11" t="n">
         <f aca="false">B31*C31*D31</f>
         <v>1.2</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7200,35 +7203,35 @@
       </c>
       <c r="G33" s="4"/>
       <c r="H33" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I33" s="4"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B34" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
       <c r="I34" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B35" s="10" t="n">
         <v>1</v>
@@ -7240,20 +7243,20 @@
         <v>1.2</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F35" s="11" t="n">
         <f aca="false">B35*C35*D35</f>
         <v>1.2</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7270,35 +7273,35 @@
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B38" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
       <c r="I38" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B39" s="10" t="n">
         <v>1</v>
@@ -7310,20 +7313,20 @@
         <v>1.2</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F39" s="11" t="n">
         <f aca="false">B39*C39*D39</f>
         <v>1.2</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7340,35 +7343,35 @@
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="I41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B42" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B43" s="10" t="n">
         <v>1</v>
@@ -7380,20 +7383,20 @@
         <v>1.2</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F43" s="11" t="n">
         <f aca="false">B43*C43*D43</f>
         <v>1.2</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7410,13 +7413,13 @@
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="I45" s="4"/>
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B46" s="5" t="n">
         <v>1</v>
@@ -7436,15 +7439,15 @@
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B47" s="5" t="n">
         <v>1</v>
@@ -7464,15 +7467,15 @@
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I47" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B48" s="10" t="n">
         <v>1</v>
@@ -7484,20 +7487,20 @@
         <v>1.2</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F48" s="11" t="n">
         <f aca="false">B48*C48*D48</f>
         <v>1.2</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I48" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7514,13 +7517,13 @@
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="I50" s="4"/>
     </row>
     <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B51" s="5" t="n">
         <v>1</v>
@@ -7540,15 +7543,15 @@
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I51" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B52" s="10" t="n">
         <v>1</v>
@@ -7560,20 +7563,20 @@
         <v>1.2</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F52" s="11" t="n">
         <f aca="false">B52*C52*D52</f>
         <v>1.2</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I52" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7590,35 +7593,35 @@
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="I54" s="4"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B55" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B56" s="10" t="n">
         <v>1</v>
@@ -7630,20 +7633,20 @@
         <v>1.2</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F56" s="11" t="n">
         <f aca="false">B56*C56*D56</f>
         <v>1.2</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="I56" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7660,35 +7663,35 @@
       </c>
       <c r="G58" s="4"/>
       <c r="H58" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="I58" s="4"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B59" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D59" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B60" s="10" t="n">
         <v>1</v>
@@ -7700,20 +7703,20 @@
         <v>1.2</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F60" s="11" t="n">
         <f aca="false">B60*C60*D60</f>
         <v>1.2</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I60" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7730,13 +7733,13 @@
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="I62" s="4"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B63" s="5" t="n">
         <v>2</v>
@@ -7756,15 +7759,15 @@
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I63" s="13" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B64" s="10" t="n">
         <v>1</v>
@@ -7776,20 +7779,20 @@
         <v>1.2</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F64" s="11" t="n">
         <f aca="false">B64*C64*D64</f>
         <v>1.2</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="I64" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7806,13 +7809,13 @@
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I66" s="4"/>
     </row>
     <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B67" s="5" t="n">
         <v>2</v>
@@ -7832,15 +7835,15 @@
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I67" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B68" s="10" t="n">
         <v>1</v>
@@ -7852,20 +7855,20 @@
         <v>1.2</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F68" s="11" t="n">
         <f aca="false">B68*C68*D68</f>
         <v>1.2</v>
       </c>
       <c r="G68" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H68" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="I68" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7882,13 +7885,13 @@
       </c>
       <c r="G70" s="4"/>
       <c r="H70" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I70" s="4"/>
     </row>
     <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B71" s="5" t="n">
         <v>1</v>
@@ -7908,15 +7911,15 @@
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I71" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B72" s="10" t="n">
         <v>1</v>
@@ -7928,20 +7931,20 @@
         <v>1.2</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F72" s="11" t="n">
         <f aca="false">B72*C72*D72</f>
         <v>1.2</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H72" s="10" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I72" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7958,35 +7961,35 @@
       </c>
       <c r="G74" s="4"/>
       <c r="H74" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I74" s="4"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B75" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D75" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
       <c r="I75" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B76" s="10" t="n">
         <v>1</v>
@@ -7998,20 +8001,20 @@
         <v>1.2</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F76" s="11" t="n">
         <f aca="false">B76*C76*D76</f>
         <v>1.2</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H76" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I76" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8028,35 +8031,35 @@
       </c>
       <c r="G78" s="4"/>
       <c r="H78" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="I78" s="4"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B79" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C79" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D79" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
       <c r="I79" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B80" s="10" t="n">
         <v>1</v>
@@ -8068,20 +8071,20 @@
         <v>1.2</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F80" s="11" t="n">
         <f aca="false">B80*C80*D80</f>
         <v>1.2</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H80" s="10" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I80" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8098,13 +8101,13 @@
       </c>
       <c r="G82" s="4"/>
       <c r="H82" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="I82" s="4"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B83" s="5" t="n">
         <v>2</v>
@@ -8124,15 +8127,15 @@
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I83" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B84" s="10" t="n">
         <v>2</v>
@@ -8144,20 +8147,20 @@
         <v>1.2</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F84" s="11" t="n">
         <f aca="false">B84*C84*D84</f>
         <v>2.4</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H84" s="10" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I84" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8174,35 +8177,35 @@
       </c>
       <c r="G86" s="4"/>
       <c r="H86" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="I86" s="4"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="5" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B87" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C87" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D87" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
       <c r="I87" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B88" s="10" t="n">
         <v>1</v>
@@ -8214,20 +8217,20 @@
         <v>1.2</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F88" s="11" t="n">
         <f aca="false">B88*C88*D88</f>
         <v>1.2</v>
       </c>
       <c r="G88" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H88" s="10" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="I88" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8244,35 +8247,35 @@
       </c>
       <c r="G90" s="4"/>
       <c r="H90" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="I90" s="4"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="5" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B91" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C91" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D91" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G91" s="5"/>
       <c r="H91" s="5"/>
       <c r="I91" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B92" s="10" t="n">
         <v>1</v>
@@ -8284,20 +8287,20 @@
         <v>1.2</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F92" s="11" t="n">
         <f aca="false">B92*C92*D92</f>
         <v>1.2</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H92" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I92" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8314,35 +8317,35 @@
       </c>
       <c r="G94" s="4"/>
       <c r="H94" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="I94" s="4"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="5" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B95" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C95" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D95" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G95" s="5"/>
       <c r="H95" s="5"/>
       <c r="I95" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B96" s="10" t="n">
         <v>1</v>
@@ -8354,20 +8357,20 @@
         <v>1.2</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F96" s="11" t="n">
         <f aca="false">B96*C96*D96</f>
         <v>1.2</v>
       </c>
       <c r="G96" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H96" s="10" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="I96" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8388,7 +8391,7 @@
     </row>
     <row r="99" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B99" s="5" t="n">
         <v>10</v>
@@ -8400,25 +8403,25 @@
         <v>1.2</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F99" s="6" t="n">
         <f aca="false">B99*C99*D99</f>
         <v>12</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="I99" s="13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="10" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B100" s="10" t="n">
         <v>10</v>
@@ -8430,20 +8433,20 @@
         <v>1.2</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F100" s="11" t="n">
         <f aca="false">B100*C100*D100</f>
         <v>12</v>
       </c>
       <c r="G100" s="10" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H100" s="10" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="I100" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -8478,12 +8481,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
@@ -8500,43 +8503,43 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8558,19 +8561,19 @@
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D6" s="18" t="n">
         <v>90</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F6" s="18" t="n">
         <v>0</v>
@@ -8582,7 +8585,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>0</v>
@@ -8598,19 +8601,19 @@
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D7" s="18" t="n">
         <v>1505</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F7" s="18" t="n">
         <v>15</v>
@@ -8622,7 +8625,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>5.32</v>
@@ -8638,19 +8641,19 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D8" s="18" t="n">
         <v>607</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F8" s="18" t="n">
         <v>20</v>
@@ -8662,7 +8665,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>11.08</v>
@@ -8678,19 +8681,19 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D9" s="18" t="n">
         <v>405</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F9" s="18" t="n">
         <v>10</v>
@@ -8702,7 +8705,7 @@
         <v>2</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>6.76</v>
@@ -8715,24 +8718,24 @@
         <v>6.76</v>
       </c>
       <c r="M9" s="13" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D10" s="18" t="n">
         <v>6609</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F10" s="18" t="n">
         <v>65</v>
@@ -8744,7 +8747,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>11.38</v>
@@ -8760,19 +8763,19 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D11" s="18" t="n">
         <v>6765</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F11" s="18" t="n">
         <v>80</v>
@@ -8784,7 +8787,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J11" s="6" t="n">
         <v>12.31</v>
@@ -8800,19 +8803,19 @@
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D12" s="18" t="n">
         <v>201</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F12" s="18" t="n">
         <v>0</v>
@@ -8824,7 +8827,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>0</v>
@@ -8840,19 +8843,19 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D13" s="18" t="n">
         <v>407</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F13" s="18" t="n">
         <v>9</v>
@@ -8864,7 +8867,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J13" s="6" t="n">
         <v>2.44</v>
@@ -8880,19 +8883,19 @@
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D14" s="18" t="n">
         <v>315</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F14" s="18" t="n">
         <v>3</v>
@@ -8904,7 +8907,7 @@
         <v>2</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J14" s="6" t="n">
         <v>2</v>
@@ -8917,24 +8920,24 @@
         <v>1</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D15" s="18" t="n">
         <v>691</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F15" s="18" t="n">
         <v>21</v>
@@ -8946,7 +8949,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>11.08</v>
@@ -8962,19 +8965,19 @@
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D16" s="18" t="n">
         <v>371</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F16" s="18" t="n">
         <v>11</v>
@@ -8986,7 +8989,7 @@
         <v>5</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>5</v>
@@ -8999,24 +9002,24 @@
         <v>5</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D17" s="18" t="n">
         <v>346</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F17" s="18" t="n">
         <v>5</v>
@@ -9028,7 +9031,7 @@
         <v>3</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J17" s="6" t="n">
         <v>3</v>
@@ -9041,24 +9044,24 @@
         <v>3</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D18" s="18" t="n">
         <v>336</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F18" s="18" t="n">
         <v>6</v>
@@ -9070,7 +9073,7 @@
         <v>3</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="J18" s="6" t="n">
         <v>3</v>
@@ -9083,24 +9086,24 @@
         <v>3</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D19" s="18" t="n">
         <v>488</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F19" s="18" t="n">
         <v>7</v>
@@ -9112,7 +9115,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>3.88</v>
@@ -9128,19 +9131,19 @@
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D20" s="18" t="n">
         <v>421</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F20" s="18" t="n">
         <v>5</v>
@@ -9152,7 +9155,7 @@
         <v>2</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="J20" s="6" t="n">
         <v>3.88</v>
@@ -9165,24 +9168,24 @@
         <v>3.88</v>
       </c>
       <c r="M20" s="13" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D21" s="18" t="n">
         <v>330</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F21" s="18" t="n">
         <v>11</v>
@@ -9194,7 +9197,7 @@
         <v>2</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="J21" s="6" t="n">
         <v>6.76</v>
@@ -9207,24 +9210,24 @@
         <v>6.76</v>
       </c>
       <c r="M21" s="13" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D22" s="18" t="n">
         <v>183</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F22" s="18" t="n">
         <v>9</v>
@@ -9236,7 +9239,7 @@
         <v>1</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J22" s="6" t="n">
         <v>5.32</v>
@@ -9252,19 +9255,19 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D23" s="18" t="n">
         <v>168</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F23" s="18" t="n">
         <v>7</v>
@@ -9276,7 +9279,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J23" s="6" t="n">
         <v>5.32</v>
@@ -9292,19 +9295,19 @@
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D24" s="18" t="n">
         <v>161</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F24" s="18" t="n">
         <v>3</v>
@@ -9316,7 +9319,7 @@
         <v>1</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J24" s="6" t="n">
         <v>2.44</v>
@@ -9332,19 +9335,19 @@
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D25" s="18" t="n">
         <v>241</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F25" s="18" t="n">
         <v>8</v>
@@ -9356,7 +9359,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J25" s="6" t="n">
         <v>5.32</v>
@@ -9372,19 +9375,19 @@
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D26" s="18" t="n">
         <v>161</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F26" s="18" t="n">
         <v>3</v>
@@ -9396,7 +9399,7 @@
         <v>2</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J26" s="6" t="n">
         <v>2</v>
@@ -9409,12 +9412,12 @@
         <v>1</v>
       </c>
       <c r="M26" s="13" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F27" s="19" t="n">
         <f aca="false">SUM(F6:F26)</f>
@@ -9443,7 +9446,7 @@
     </row>
     <row r="28" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="20" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9465,22 +9468,22 @@
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D31" s="18" t="n">
         <v>52</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J31" s="6" t="n">
         <v>7.36</v>
@@ -9492,22 +9495,22 @@
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D32" s="18" t="n">
         <v>2</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="J32" s="6" t="n">
         <v>0.49</v>
@@ -9519,22 +9522,22 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D33" s="18" t="n">
         <v>11</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="J33" s="6" t="n">
         <v>3.07</v>
@@ -9546,22 +9549,22 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D34" s="18" t="n">
         <v>13</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="J34" s="6" t="n">
         <v>0.66</v>
@@ -9573,22 +9576,22 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D35" s="18" t="n">
         <v>1</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J35" s="6" t="n">
         <v>0.25</v>
@@ -9600,22 +9603,22 @@
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D36" s="18" t="n">
         <v>29</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="J36" s="6" t="n">
         <v>17.71</v>
@@ -9627,22 +9630,22 @@
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D37" s="18" t="n">
         <v>29</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="J37" s="6" t="n">
         <v>17.71</v>
@@ -9654,7 +9657,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="J38" s="8" t="n">
         <f aca="false">SUM(J31:J37)</f>
@@ -9667,7 +9670,7 @@
     </row>
     <row r="39" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="20" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9689,25 +9692,25 @@
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D42" s="18" t="n">
         <v>238</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F42" s="18" t="n">
         <v>25</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="J42" s="6" t="n">
         <v>60</v>
@@ -9720,25 +9723,25 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B43" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>586</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>585</v>
       </c>
       <c r="D43" s="18" t="n">
         <v>271</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="F43" s="18" t="n">
         <v>10</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="J43" s="6" t="n">
         <v>24</v>
@@ -9751,25 +9754,25 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B44" s="5" t="s">
+        <v>590</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>589</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>588</v>
       </c>
       <c r="D44" s="18" t="n">
         <v>271</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="F44" s="18" t="n">
         <v>10</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="J44" s="6" t="n">
         <v>24</v>
@@ -9782,7 +9785,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="J45" s="8" t="n">
         <f aca="false">SUM(J42:J44)</f>
@@ -9829,35 +9832,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>84</v>
@@ -9865,7 +9868,7 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>1200</v>
@@ -9877,21 +9880,21 @@
         <v>2000</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>1200</v>
@@ -9903,21 +9906,21 @@
         <v>40</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>600</v>
@@ -9929,21 +9932,21 @@
         <v>300</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B8" s="5" t="n">
         <v>1300</v>
@@ -9952,24 +9955,24 @@
         <v>700</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B9" s="5" t="n">
         <v>1300</v>
@@ -9978,24 +9981,24 @@
         <v>700</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>1200</v>
@@ -10004,24 +10007,24 @@
         <v>600</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B11" s="5" t="n">
         <v>2700</v>
@@ -10030,24 +10033,24 @@
         <v>1200</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B12" s="5" t="n">
         <v>1200</v>
@@ -10059,21 +10062,21 @@
         <v>1045</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B13" s="5" t="n">
         <v>1200</v>
@@ -10082,53 +10085,53 @@
         <v>1000</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>85</v>
@@ -10136,13 +10139,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D17" s="18" t="n">
         <v>254</v>
@@ -10154,7 +10157,7 @@
         <v>229</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H17" s="18" t="n">
         <v>1270</v>
@@ -10166,10 +10169,10 @@
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5"/>
       <c r="B18" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D18" s="18" t="n">
         <v>147</v>
@@ -10181,7 +10184,7 @@
         <v>184</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H18" s="18" t="n">
         <v>735</v>
@@ -10193,10 +10196,10 @@
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5"/>
       <c r="B19" s="5" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D19" s="18" t="n">
         <v>76</v>
@@ -10208,7 +10211,7 @@
         <v>122</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H19" s="18" t="n">
         <v>456</v>
@@ -10220,10 +10223,10 @@
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10"/>
       <c r="B20" s="10" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D20" s="22" t="n">
         <v>34</v>
@@ -10235,7 +10238,7 @@
         <v>68</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H20" s="22" t="n">
         <v>272</v>
@@ -10246,13 +10249,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D21" s="18" t="n">
         <v>105</v>
@@ -10264,7 +10267,7 @@
         <v>297.5</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H21" s="18" t="n">
         <v>420</v>
@@ -10276,10 +10279,10 @@
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5"/>
       <c r="B22" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D22" s="18" t="n">
         <v>36</v>
@@ -10291,7 +10294,7 @@
         <v>333</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H22" s="18" t="n">
         <v>144</v>
@@ -10303,10 +10306,10 @@
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5"/>
       <c r="B23" s="5" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D23" s="18" t="n">
         <v>21</v>
@@ -10318,7 +10321,7 @@
         <v>414</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H23" s="18" t="n">
         <v>63</v>
@@ -10330,10 +10333,10 @@
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10"/>
       <c r="B24" s="10" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D24" s="22" t="n">
         <v>18</v>
@@ -10345,7 +10348,7 @@
         <v>582</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H24" s="22" t="n">
         <v>54</v>
@@ -10356,13 +10359,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D25" s="18" t="n">
         <v>105</v>
@@ -10374,7 +10377,7 @@
         <v>297.5</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H25" s="18" t="n">
         <v>420</v>
@@ -10386,10 +10389,10 @@
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5"/>
       <c r="B26" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D26" s="18" t="n">
         <v>36</v>
@@ -10401,7 +10404,7 @@
         <v>333</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H26" s="18" t="n">
         <v>144</v>
@@ -10413,10 +10416,10 @@
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5"/>
       <c r="B27" s="5" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D27" s="18" t="n">
         <v>21</v>
@@ -10428,7 +10431,7 @@
         <v>414</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H27" s="18" t="n">
         <v>63</v>
@@ -10440,10 +10443,10 @@
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10"/>
       <c r="B28" s="10" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D28" s="22" t="n">
         <v>18</v>
@@ -10455,7 +10458,7 @@
         <v>582</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H28" s="22" t="n">
         <v>54</v>
@@ -10466,13 +10469,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D29" s="18" t="n">
         <v>72</v>
@@ -10484,7 +10487,7 @@
         <v>390</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H29" s="18" t="n">
         <v>216</v>
@@ -10496,10 +10499,10 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5"/>
       <c r="B30" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D30" s="18" t="n">
         <v>34</v>
@@ -10511,7 +10514,7 @@
         <v>415</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H30" s="18" t="n">
         <v>102</v>
@@ -10523,10 +10526,10 @@
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5"/>
       <c r="B31" s="5" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D31" s="18" t="n">
         <v>18</v>
@@ -10538,7 +10541,7 @@
         <v>495</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H31" s="18" t="n">
         <v>54</v>
@@ -10550,10 +10553,10 @@
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10"/>
       <c r="B32" s="10" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D32" s="22" t="n">
         <v>9</v>
@@ -10565,7 +10568,7 @@
         <v>665</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H32" s="22" t="n">
         <v>18</v>
@@ -10574,18 +10577,18 @@
         <v>27</v>
       </c>
       <c r="J32" s="13" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D33" s="18" t="n">
         <v>288</v>
@@ -10597,7 +10600,7 @@
         <v>300</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H33" s="18" t="n">
         <v>3456</v>
@@ -10609,10 +10612,10 @@
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5"/>
       <c r="B34" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D34" s="18" t="n">
         <v>88</v>
@@ -10624,7 +10627,7 @@
         <v>300</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H34" s="18" t="n">
         <v>1056</v>
@@ -10636,10 +10639,10 @@
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5"/>
       <c r="B35" s="5" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D35" s="18" t="n">
         <v>48</v>
@@ -10651,7 +10654,7 @@
         <v>300</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H35" s="18" t="n">
         <v>576</v>
@@ -10663,10 +10666,10 @@
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10"/>
       <c r="B36" s="10" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D36" s="22" t="n">
         <v>27</v>
@@ -10678,7 +10681,7 @@
         <v>300</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H36" s="22" t="n">
         <v>324</v>
@@ -10689,13 +10692,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D37" s="18" t="n">
         <v>288</v>
@@ -10707,7 +10710,7 @@
         <v>300</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H37" s="18" t="n">
         <v>3456</v>
@@ -10719,10 +10722,10 @@
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5"/>
       <c r="B38" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D38" s="18" t="n">
         <v>80</v>
@@ -10734,7 +10737,7 @@
         <v>300</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H38" s="18" t="n">
         <v>960</v>
@@ -10746,10 +10749,10 @@
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5"/>
       <c r="B39" s="5" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D39" s="18" t="n">
         <v>36</v>
@@ -10761,7 +10764,7 @@
         <v>300</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H39" s="18" t="n">
         <v>432</v>
@@ -10773,10 +10776,10 @@
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10"/>
       <c r="B40" s="10" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D40" s="22" t="n">
         <v>21</v>
@@ -10788,7 +10791,7 @@
         <v>300</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H40" s="22" t="n">
         <v>252</v>
@@ -10799,13 +10802,13 @@
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D41" s="18" t="n">
         <v>100</v>
@@ -10817,7 +10820,7 @@
         <v>300</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H41" s="18" t="n">
         <v>1200</v>
@@ -10829,10 +10832,10 @@
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5"/>
       <c r="B42" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D42" s="18" t="n">
         <v>40</v>
@@ -10844,7 +10847,7 @@
         <v>300</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H42" s="18" t="n">
         <v>480</v>
@@ -10856,10 +10859,10 @@
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5"/>
       <c r="B43" s="5" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D43" s="18" t="n">
         <v>30</v>
@@ -10871,7 +10874,7 @@
         <v>300</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H43" s="18" t="n">
         <v>360</v>
@@ -10883,10 +10886,10 @@
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10"/>
       <c r="B44" s="10" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D44" s="22" t="n">
         <v>19</v>
@@ -10898,7 +10901,7 @@
         <v>300</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H44" s="22" t="n">
         <v>228</v>
@@ -10909,7 +10912,7 @@
     </row>
     <row r="46" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="20" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
   </sheetData>
